--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -1,742 +1,762 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755148A4-CA0B-47F4-BFF5-2688322257A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
-  <si>
-    <t xml:space="preserve">Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">League</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Winning_Bid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Musiala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bundesliga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Club Soccer Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florian Wirtz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premier League</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Club Soccer Top 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bryan Mbeumo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Acuna Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Verstappen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorsports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscar Piastri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja'Marr Chase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bijan Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puka Nacua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor McDavid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NHL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan MacKinnon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cale Makar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leon Draisaitl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novak Djokovic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tennis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iga Swiatek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manchester United</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liverpool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Men's Intl Soccer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intl Soccer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Women's Intl Soccer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSU Tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCAA Baseball</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indiana Hoosiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCAAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon Ducks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gonzaga Bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCAAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seattle Seahawks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detroit Lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colorado Avalanche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florian Thauvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ligue 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicolás Fernández</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esteban Lepaul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petar Musa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jude Bellingham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Liga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bukayo Saka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raphinha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cole Palmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pete Alonso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yordan Alvarez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Brunson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luka Doncic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shai Gilgeous-Alexander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahmyr Gibbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Herbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikita Kucherov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scottie Scheffler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viktor Hovland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flavio Cobolli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borussia Dortmund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paris FC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB Leipzig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago Fire FC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atlético Madrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deportivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leeds United</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kansas City Royals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Diego Padres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philadelphia 76ers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memphis Grizzlies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ohio State Buckeyes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arkansas Razorbacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebraska Cornhuskers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCAAW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles Rams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New England Patriots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carolina Hurricanes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montreal Canadiens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lionel Messi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ousmane Dembélé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferran Torres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serhou Guirassy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Younes Ebnoutalib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erling Haaland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lamine Yamal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kylian Mbappé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruno Fernandes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shohei Ohtani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Skenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Caminero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pete Crow-Armstrong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrea Kimi Antonelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denny Hamlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NASCAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikola Jokic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cade Cunningham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donovan Mitchell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey McBride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian McCaffrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Jefferson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brock Bowers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auston Matthews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xander Schauffele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collin Morikawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jannik Sinner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coco Gauff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mirra Andreeva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paris Saint-Germain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayern Munich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internazionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serie A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS Roma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juventus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma City Thunder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York Knicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Carolina Tar Heels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCAA Softball</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Madison Dukes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida Gators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saint Mary's Gaels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UConn Huskies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maryland Terrapins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baltimore Ravens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Francisco 49ers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida Panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vegas Golden Knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Kane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granit Xhaka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilson Isidor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nordi Mukiele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Pulisic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vinícius Júnior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Judge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gunnar Henderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bobby Witt Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LeBron James</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Curry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giannis Antetokounmpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derrick Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Smith-Njigba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Mahomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arthur Fils</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jessica Pegula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefanos Tsitsipas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS Monaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marseille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunderland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Madrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ipswich Town</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aston Villa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Athletics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Red Sox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden State Warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Celtics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas Longhorns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Wildcats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michigan Wolverines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buffalo Bills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philadelphia Eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washington Capitals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Folarin Balogun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Olise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luis Díaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Igor Thiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julián Álvarez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kevin McGonigle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dillon Dingler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Larson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Wembanyama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anthony Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kawhi Leonard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Dybantsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lamar Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiyah Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drake Maye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Omarion Hampton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macklin Celebrini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sidney Crosby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Guentzel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evgeni Malkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rory McIlroy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Daly II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos Alcaraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aryna Sabalenka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Shelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nashville SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VfB Stuttgart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayer Leverkusen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manchester City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barcelona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago White Sox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleveland Guardians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denver Nuggets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washington Wizards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Virginia Mountaineers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notre Dame Fighting Irish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penn State Nittany Lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michigan State Spartans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St. John's Red Storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fairfield Stags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pittsburgh Penguins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Jose Sharks</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="239">
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Asset_Type</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>League</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Winning_Bid</t>
+  </si>
+  <si>
+    <t>JM</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Jamal Musiala</t>
+  </si>
+  <si>
+    <t>Bundesliga</t>
+  </si>
+  <si>
+    <t>Club Soccer Other</t>
+  </si>
+  <si>
+    <t>Florian Wirtz</t>
+  </si>
+  <si>
+    <t>Premier League</t>
+  </si>
+  <si>
+    <t>Club Soccer Top 3</t>
+  </si>
+  <si>
+    <t>Bryan Mbeumo</t>
+  </si>
+  <si>
+    <t>Ronald Acuna Jr.</t>
+  </si>
+  <si>
+    <t>MLB</t>
+  </si>
+  <si>
+    <t>Max Verstappen</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Motorsports</t>
+  </si>
+  <si>
+    <t>Oscar Piastri</t>
+  </si>
+  <si>
+    <t>Ja'Marr Chase</t>
+  </si>
+  <si>
+    <t>NFL</t>
+  </si>
+  <si>
+    <t>Bijan Robinson</t>
+  </si>
+  <si>
+    <t>Puka Nacua</t>
+  </si>
+  <si>
+    <t>Connor McDavid</t>
+  </si>
+  <si>
+    <t>NHL</t>
+  </si>
+  <si>
+    <t>Nathan MacKinnon</t>
+  </si>
+  <si>
+    <t>Cale Makar</t>
+  </si>
+  <si>
+    <t>Leon Draisaitl</t>
+  </si>
+  <si>
+    <t>Novak Djokovic</t>
+  </si>
+  <si>
+    <t>Tennis</t>
+  </si>
+  <si>
+    <t>Iga Swiatek</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Men's Intl Soccer</t>
+  </si>
+  <si>
+    <t>Intl Soccer</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Women's Intl Soccer</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>LSU Tigers</t>
+  </si>
+  <si>
+    <t>NCAA Baseball</t>
+  </si>
+  <si>
+    <t>Indiana Hoosiers</t>
+  </si>
+  <si>
+    <t>NCAAF</t>
+  </si>
+  <si>
+    <t>Oregon Ducks</t>
+  </si>
+  <si>
+    <t>Gonzaga Bulldogs</t>
+  </si>
+  <si>
+    <t>NCAAM</t>
+  </si>
+  <si>
+    <t>Seattle Seahawks</t>
+  </si>
+  <si>
+    <t>Detroit Lions</t>
+  </si>
+  <si>
+    <t>Colorado Avalanche</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>Florian Thauvin</t>
+  </si>
+  <si>
+    <t>Ligue 1</t>
+  </si>
+  <si>
+    <t>Nicolás Fernández</t>
+  </si>
+  <si>
+    <t>MLS</t>
+  </si>
+  <si>
+    <t>Esteban Lepaul</t>
+  </si>
+  <si>
+    <t>Petar Musa</t>
+  </si>
+  <si>
+    <t>Jude Bellingham</t>
+  </si>
+  <si>
+    <t>La Liga</t>
+  </si>
+  <si>
+    <t>Bukayo Saka</t>
+  </si>
+  <si>
+    <t>Raphinha</t>
+  </si>
+  <si>
+    <t>Cole Palmer</t>
+  </si>
+  <si>
+    <t>Pete Alonso</t>
+  </si>
+  <si>
+    <t>Yordan Alvarez</t>
+  </si>
+  <si>
+    <t>Jalen Brunson</t>
+  </si>
+  <si>
+    <t>NBA</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Shai Gilgeous-Alexander</t>
+  </si>
+  <si>
+    <t>Jahmyr Gibbs</t>
+  </si>
+  <si>
+    <t>Justin Herbert</t>
+  </si>
+  <si>
+    <t>Nikita Kucherov</t>
+  </si>
+  <si>
+    <t>Scottie Scheffler</t>
+  </si>
+  <si>
+    <t>PGA</t>
+  </si>
+  <si>
+    <t>Viktor Hovland</t>
+  </si>
+  <si>
+    <t>Flavio Cobolli</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Paris FC</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Chicago Fire FC</t>
+  </si>
+  <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
+    <t>Deportivo</t>
+  </si>
+  <si>
+    <t>Leeds United</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Kansas City Royals</t>
+  </si>
+  <si>
+    <t>San Diego Padres</t>
+  </si>
+  <si>
+    <t>Philadelphia 76ers</t>
+  </si>
+  <si>
+    <t>Memphis Grizzlies</t>
+  </si>
+  <si>
+    <t>Ohio State Buckeyes</t>
+  </si>
+  <si>
+    <t>Arkansas Razorbacks</t>
+  </si>
+  <si>
+    <t>Nebraska Cornhuskers</t>
+  </si>
+  <si>
+    <t>NCAAW</t>
+  </si>
+  <si>
+    <t>Los Angeles Rams</t>
+  </si>
+  <si>
+    <t>New England Patriots</t>
+  </si>
+  <si>
+    <t>Carolina Hurricanes</t>
+  </si>
+  <si>
+    <t>Montreal Canadiens</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Lionel Messi</t>
+  </si>
+  <si>
+    <t>Ousmane Dembélé</t>
+  </si>
+  <si>
+    <t>Ferran Torres</t>
+  </si>
+  <si>
+    <t>Serhou Guirassy</t>
+  </si>
+  <si>
+    <t>Younes Ebnoutalib</t>
+  </si>
+  <si>
+    <t>Erling Haaland</t>
+  </si>
+  <si>
+    <t>Lamine Yamal</t>
+  </si>
+  <si>
+    <t>Kylian Mbappé</t>
+  </si>
+  <si>
+    <t>Bruno Fernandes</t>
+  </si>
+  <si>
+    <t>Shohei Ohtani</t>
+  </si>
+  <si>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>Junior Caminero</t>
+  </si>
+  <si>
+    <t>Pete Crow-Armstrong</t>
+  </si>
+  <si>
+    <t>Andrea Kimi Antonelli</t>
+  </si>
+  <si>
+    <t>Denny Hamlin</t>
+  </si>
+  <si>
+    <t>NASCAR</t>
+  </si>
+  <si>
+    <t>Nikola Jokic</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>Trey McBride</t>
+  </si>
+  <si>
+    <t>Christian McCaffrey</t>
+  </si>
+  <si>
+    <t>Justin Jefferson</t>
+  </si>
+  <si>
+    <t>Brock Bowers</t>
+  </si>
+  <si>
+    <t>Auston Matthews</t>
+  </si>
+  <si>
+    <t>Logan Thompson</t>
+  </si>
+  <si>
+    <t>Cameron Young</t>
+  </si>
+  <si>
+    <t>Xander Schauffele</t>
+  </si>
+  <si>
+    <t>Collin Morikawa</t>
+  </si>
+  <si>
+    <t>Jannik Sinner</t>
+  </si>
+  <si>
+    <t>Coco Gauff</t>
+  </si>
+  <si>
+    <t>Mirra Andreeva</t>
+  </si>
+  <si>
+    <t>Paris Saint-Germain</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Internazionale</t>
+  </si>
+  <si>
+    <t>Serie A</t>
+  </si>
+  <si>
+    <t>AS Roma</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Oklahoma City Thunder</t>
+  </si>
+  <si>
+    <t>New York Knicks</t>
+  </si>
+  <si>
+    <t>North Carolina Tar Heels</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>NCAA Softball</t>
+  </si>
+  <si>
+    <t>James Madison Dukes</t>
+  </si>
+  <si>
+    <t>Florida Gators</t>
+  </si>
+  <si>
+    <t>Saint Mary's Gaels</t>
+  </si>
+  <si>
+    <t>UConn Huskies</t>
+  </si>
+  <si>
+    <t>Maryland Terrapins</t>
+  </si>
+  <si>
+    <t>Baltimore Ravens</t>
+  </si>
+  <si>
+    <t>San Francisco 49ers</t>
+  </si>
+  <si>
+    <t>Florida Panthers</t>
+  </si>
+  <si>
+    <t>Vegas Golden Knights</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>Harry Kane</t>
+  </si>
+  <si>
+    <t>Granit Xhaka</t>
+  </si>
+  <si>
+    <t>Wilson Isidor</t>
+  </si>
+  <si>
+    <t>Nordi Mukiele</t>
+  </si>
+  <si>
+    <t>Christian Pulisic</t>
+  </si>
+  <si>
+    <t>Vinícius Júnior</t>
+  </si>
+  <si>
+    <t>Aaron Judge</t>
+  </si>
+  <si>
+    <t>Gunnar Henderson</t>
+  </si>
+  <si>
+    <t>Bobby Witt Jr.</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Josh Allen</t>
+  </si>
+  <si>
+    <t>Derrick Henry</t>
+  </si>
+  <si>
+    <t>Jaxon Smith-Njigba</t>
+  </si>
+  <si>
+    <t>Patrick Mahomes</t>
+  </si>
+  <si>
+    <t>Arthur Fils</t>
+  </si>
+  <si>
+    <t>Jessica Pegula</t>
+  </si>
+  <si>
+    <t>Stefanos Tsitsipas</t>
+  </si>
+  <si>
+    <t>AS Monaco</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Ipswich Town</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Athletics</t>
+  </si>
+  <si>
+    <t>Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Golden State Warriors</t>
+  </si>
+  <si>
+    <t>Boston Celtics</t>
+  </si>
+  <si>
+    <t>Texas Longhorns</t>
+  </si>
+  <si>
+    <t>Arizona Wildcats</t>
+  </si>
+  <si>
+    <t>Michigan Wolverines</t>
+  </si>
+  <si>
+    <t>Buffalo Bills</t>
+  </si>
+  <si>
+    <t>Philadelphia Eagles</t>
+  </si>
+  <si>
+    <t>Washington Capitals</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>Folarin Balogun</t>
+  </si>
+  <si>
+    <t>Michael Olise</t>
+  </si>
+  <si>
+    <t>Luis Díaz</t>
+  </si>
+  <si>
+    <t>Evander</t>
+  </si>
+  <si>
+    <t>Igor Thiago</t>
+  </si>
+  <si>
+    <t>Julián Álvarez</t>
+  </si>
+  <si>
+    <t>Kevin McGonigle</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Dillon Dingler</t>
+  </si>
+  <si>
+    <t>Grant Taylor</t>
+  </si>
+  <si>
+    <t>Kyle Larson</t>
+  </si>
+  <si>
+    <t>Victor Wembanyama</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>AJ Dybantsa</t>
+  </si>
+  <si>
+    <t>Lamar Jackson</t>
+  </si>
+  <si>
+    <t>Jeremiyah Love</t>
+  </si>
+  <si>
+    <t>Drake Maye</t>
+  </si>
+  <si>
+    <t>Omarion Hampton</t>
+  </si>
+  <si>
+    <t>Macklin Celebrini</t>
+  </si>
+  <si>
+    <t>Sidney Crosby</t>
+  </si>
+  <si>
+    <t>Jake Guentzel</t>
+  </si>
+  <si>
+    <t>Evgeni Malkin</t>
+  </si>
+  <si>
+    <t>Rory McIlroy</t>
+  </si>
+  <si>
+    <t>John Daly II</t>
+  </si>
+  <si>
+    <t>Carlos Alcaraz</t>
+  </si>
+  <si>
+    <t>Aryna Sabalenka</t>
+  </si>
+  <si>
+    <t>Ben Shelton</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>VfB Stuttgart</t>
+  </si>
+  <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
+    <t>Washington Wizards</t>
+  </si>
+  <si>
+    <t>West Virginia Mountaineers</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Notre Dame Fighting Irish</t>
+  </si>
+  <si>
+    <t>Penn State Nittany Lions</t>
+  </si>
+  <si>
+    <t>Michigan State Spartans</t>
+  </si>
+  <si>
+    <t>St. John's Red Storm</t>
+  </si>
+  <si>
+    <t>Fairfield Stags</t>
+  </si>
+  <si>
+    <t>Pittsburgh Penguins</t>
+  </si>
+  <si>
+    <t>San Jose Sharks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -772,6 +792,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1053,11 +1082,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F206"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1093,11 +1122,11 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1113,11 +1142,11 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1133,11 +1162,11 @@
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1153,11 +1182,11 @@
       <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1173,11 +1202,11 @@
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>10</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1188,16 +1217,16 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1213,11 +1242,11 @@
       <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>72</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1233,11 +1262,11 @@
       <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>68</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1253,11 +1282,11 @@
       <c r="E10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>40</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1273,11 +1302,11 @@
       <c r="E11" t="s">
         <v>26</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>52</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1293,11 +1322,11 @@
       <c r="E12" t="s">
         <v>26</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>38</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1313,11 +1342,11 @@
       <c r="E13" t="s">
         <v>26</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>30</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1333,11 +1362,11 @@
       <c r="E14" t="s">
         <v>26</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>17</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1353,11 +1382,11 @@
       <c r="E15" t="s">
         <v>31</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>20</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1373,11 +1402,11 @@
       <c r="E16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>18</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1393,11 +1422,11 @@
       <c r="E17" t="s">
         <v>13</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>200</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1413,11 +1442,11 @@
       <c r="E18" t="s">
         <v>13</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>18</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1433,11 +1462,11 @@
       <c r="E19" t="s">
         <v>38</v>
       </c>
-      <c r="F19" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="F19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1453,11 +1482,11 @@
       <c r="E20" t="s">
         <v>38</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1473,11 +1502,11 @@
       <c r="E21" t="s">
         <v>16</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>200</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1493,11 +1522,11 @@
       <c r="E22" t="s">
         <v>43</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>10</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1513,11 +1542,11 @@
       <c r="E23" t="s">
         <v>45</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>200</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1533,11 +1562,11 @@
       <c r="E24" t="s">
         <v>45</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>22</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1553,11 +1582,11 @@
       <c r="E25" t="s">
         <v>48</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>200</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1573,11 +1602,11 @@
       <c r="E26" t="s">
         <v>22</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>200</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1593,11 +1622,11 @@
       <c r="E27" t="s">
         <v>22</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>24</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1613,11 +1642,11 @@
       <c r="E28" t="s">
         <v>26</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>25</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1633,11 +1662,11 @@
       <c r="E29" t="s">
         <v>10</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>50</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -1653,11 +1682,11 @@
       <c r="E30" t="s">
         <v>10</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>30</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1673,11 +1702,11 @@
       <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>15</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>52</v>
       </c>
@@ -1693,11 +1722,11 @@
       <c r="E32" t="s">
         <v>10</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -1713,11 +1742,11 @@
       <c r="E33" t="s">
         <v>13</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>100</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>52</v>
       </c>
@@ -1733,11 +1762,11 @@
       <c r="E34" t="s">
         <v>13</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>50</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -1753,11 +1782,11 @@
       <c r="E35" t="s">
         <v>13</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>25</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>52</v>
       </c>
@@ -1773,11 +1802,11 @@
       <c r="E36" t="s">
         <v>13</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>25</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>52</v>
       </c>
@@ -1793,11 +1822,11 @@
       <c r="E37" t="s">
         <v>16</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>200</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -1813,11 +1842,11 @@
       <c r="E38" t="s">
         <v>16</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>100</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -1833,11 +1862,11 @@
       <c r="E39" t="s">
         <v>67</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>150</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -1853,11 +1882,11 @@
       <c r="E40" t="s">
         <v>67</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>100</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -1873,11 +1902,11 @@
       <c r="E41" t="s">
         <v>67</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>50</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -1893,11 +1922,11 @@
       <c r="E42" t="s">
         <v>22</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>20</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -1913,11 +1942,11 @@
       <c r="E43" t="s">
         <v>22</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>10</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -1933,11 +1962,11 @@
       <c r="E44" t="s">
         <v>26</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -1953,11 +1982,11 @@
       <c r="E45" t="s">
         <v>74</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>100</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>52</v>
       </c>
@@ -1973,11 +2002,11 @@
       <c r="E46" t="s">
         <v>74</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>10</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1993,11 +2022,11 @@
       <c r="E47" t="s">
         <v>31</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>15</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -2013,11 +2042,11 @@
       <c r="E48" t="s">
         <v>10</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>75</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -2033,11 +2062,11 @@
       <c r="E49" t="s">
         <v>10</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>45</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -2053,11 +2082,11 @@
       <c r="E50" t="s">
         <v>10</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>25</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -2073,11 +2102,11 @@
       <c r="E51" t="s">
         <v>10</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>15</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2093,11 +2122,11 @@
       <c r="E52" t="s">
         <v>13</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>50</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -2113,11 +2142,11 @@
       <c r="E53" t="s">
         <v>13</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -2133,11 +2162,11 @@
       <c r="E54" t="s">
         <v>13</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>20</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>52</v>
       </c>
@@ -2153,11 +2182,11 @@
       <c r="E55" t="s">
         <v>13</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>10</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>52</v>
       </c>
@@ -2173,11 +2202,11 @@
       <c r="E56" t="s">
         <v>16</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>70</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -2193,11 +2222,11 @@
       <c r="E57" t="s">
         <v>16</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>30</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>52</v>
       </c>
@@ -2213,11 +2242,11 @@
       <c r="E58" t="s">
         <v>67</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>60</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -2233,11 +2262,11 @@
       <c r="E59" t="s">
         <v>67</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>10</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>52</v>
       </c>
@@ -2253,11 +2282,11 @@
       <c r="E60" t="s">
         <v>45</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>90</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>52</v>
       </c>
@@ -2273,11 +2302,11 @@
       <c r="E61" t="s">
         <v>45</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>52</v>
       </c>
@@ -2293,11 +2322,11 @@
       <c r="E62" t="s">
         <v>48</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>25</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>52</v>
       </c>
@@ -2313,11 +2342,11 @@
       <c r="E63" t="s">
         <v>92</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>15</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>52</v>
       </c>
@@ -2333,11 +2362,11 @@
       <c r="E64" t="s">
         <v>22</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>125</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>52</v>
       </c>
@@ -2353,11 +2382,11 @@
       <c r="E65" t="s">
         <v>22</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>75</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>52</v>
       </c>
@@ -2373,11 +2402,11 @@
       <c r="E66" t="s">
         <v>26</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>50</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -2393,11 +2422,11 @@
       <c r="E67" t="s">
         <v>26</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>50</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>97</v>
       </c>
@@ -2413,11 +2442,11 @@
       <c r="E68" t="s">
         <v>10</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>30</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2433,11 +2462,11 @@
       <c r="E69" t="s">
         <v>10</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>20</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>97</v>
       </c>
@@ -2453,11 +2482,11 @@
       <c r="E70" t="s">
         <v>10</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>12</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>97</v>
       </c>
@@ -2473,11 +2502,11 @@
       <c r="E71" t="s">
         <v>10</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>1</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>97</v>
       </c>
@@ -2493,11 +2522,11 @@
       <c r="E72" t="s">
         <v>10</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>1</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>97</v>
       </c>
@@ -2513,11 +2542,11 @@
       <c r="E73" t="s">
         <v>13</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>90</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>97</v>
       </c>
@@ -2533,11 +2562,11 @@
       <c r="E74" t="s">
         <v>13</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>25</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>97</v>
       </c>
@@ -2553,11 +2582,11 @@
       <c r="E75" t="s">
         <v>13</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>17</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>97</v>
       </c>
@@ -2573,11 +2602,11 @@
       <c r="E76" t="s">
         <v>13</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>8</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>97</v>
       </c>
@@ -2593,11 +2622,11 @@
       <c r="E77" t="s">
         <v>16</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>200</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -2613,11 +2642,11 @@
       <c r="E78" t="s">
         <v>16</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>10</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>97</v>
       </c>
@@ -2633,11 +2662,11 @@
       <c r="E79" t="s">
         <v>16</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>20</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>97</v>
       </c>
@@ -2653,11 +2682,11 @@
       <c r="E80" t="s">
         <v>16</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>15</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>97</v>
       </c>
@@ -2668,16 +2697,16 @@
         <v>111</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>97</v>
       </c>
@@ -2693,11 +2722,11 @@
       <c r="E82" t="s">
         <v>19</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -2713,11 +2742,11 @@
       <c r="E83" t="s">
         <v>67</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>90</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>97</v>
       </c>
@@ -2733,11 +2762,11 @@
       <c r="E84" t="s">
         <v>67</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>25</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -2753,11 +2782,11 @@
       <c r="E85" t="s">
         <v>67</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>10</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2773,11 +2802,11 @@
       <c r="E86" t="s">
         <v>67</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>4</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -2793,11 +2822,11 @@
       <c r="E87" t="s">
         <v>22</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>80</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -2813,11 +2842,11 @@
       <c r="E88" t="s">
         <v>22</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>15</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -2833,11 +2862,11 @@
       <c r="E89" t="s">
         <v>22</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>11</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -2853,11 +2882,11 @@
       <c r="E90" t="s">
         <v>22</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>11</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>97</v>
       </c>
@@ -2873,11 +2902,11 @@
       <c r="E91" t="s">
         <v>26</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>2</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>97</v>
       </c>
@@ -2893,11 +2922,11 @@
       <c r="E92" t="s">
         <v>26</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>1</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -2913,11 +2942,11 @@
       <c r="E93" t="s">
         <v>74</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>30</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2933,11 +2962,11 @@
       <c r="E94" t="s">
         <v>74</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>15</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -2953,11 +2982,11 @@
       <c r="E95" t="s">
         <v>74</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>1</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -2973,11 +3002,11 @@
       <c r="E96" t="s">
         <v>31</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>90</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -2993,11 +3022,11 @@
       <c r="E97" t="s">
         <v>31</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>141</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -3013,11 +3042,11 @@
       <c r="E98" t="s">
         <v>31</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>12</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -3033,11 +3062,11 @@
       <c r="E99" t="s">
         <v>10</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>20</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>97</v>
       </c>
@@ -3053,11 +3082,11 @@
       <c r="E100" t="s">
         <v>10</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>24</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>97</v>
       </c>
@@ -3073,11 +3102,11 @@
       <c r="E101" t="s">
         <v>13</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>20</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3093,11 +3122,11 @@
       <c r="E102" t="s">
         <v>13</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>150</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>97</v>
       </c>
@@ -3113,11 +3142,11 @@
       <c r="E103" t="s">
         <v>13</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>9</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>97</v>
       </c>
@@ -3133,11 +3162,11 @@
       <c r="E104" t="s">
         <v>13</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>8</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>97</v>
       </c>
@@ -3153,11 +3182,11 @@
       <c r="E105" t="s">
         <v>38</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>37</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>97</v>
       </c>
@@ -3173,11 +3202,11 @@
       <c r="E106" t="s">
         <v>38</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>97</v>
       </c>
@@ -3193,11 +3222,11 @@
       <c r="E107" t="s">
         <v>16</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>175</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>97</v>
       </c>
@@ -3213,11 +3242,11 @@
       <c r="E108" t="s">
         <v>16</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>97</v>
       </c>
@@ -3233,11 +3262,11 @@
       <c r="E109" t="s">
         <v>67</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>60</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>97</v>
       </c>
@@ -3253,11 +3282,11 @@
       <c r="E110" t="s">
         <v>67</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>97</v>
       </c>
@@ -3273,11 +3302,11 @@
       <c r="E111" t="s">
         <v>43</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>1</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>97</v>
       </c>
@@ -3293,11 +3322,11 @@
       <c r="E112" t="s">
         <v>144</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>11</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -3313,11 +3342,11 @@
       <c r="E113" t="s">
         <v>45</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>2</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>97</v>
       </c>
@@ -3333,11 +3362,11 @@
       <c r="E114" t="s">
         <v>48</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>97</v>
       </c>
@@ -3353,11 +3382,11 @@
       <c r="E115" t="s">
         <v>48</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>2</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>97</v>
       </c>
@@ -3373,11 +3402,11 @@
       <c r="E116" t="s">
         <v>92</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>30</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>97</v>
       </c>
@@ -3393,11 +3422,11 @@
       <c r="E117" t="s">
         <v>92</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>11</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>97</v>
       </c>
@@ -3413,11 +3442,11 @@
       <c r="E118" t="s">
         <v>22</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>2</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>97</v>
       </c>
@@ -3433,11 +3462,11 @@
       <c r="E119" t="s">
         <v>22</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>11</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>97</v>
       </c>
@@ -3453,11 +3482,11 @@
       <c r="E120" t="s">
         <v>26</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>40</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>97</v>
       </c>
@@ -3473,11 +3502,11 @@
       <c r="E121" t="s">
         <v>26</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>5</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>154</v>
       </c>
@@ -3493,11 +3522,11 @@
       <c r="E122" t="s">
         <v>10</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>100</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>154</v>
       </c>
@@ -3513,11 +3542,11 @@
       <c r="E123" t="s">
         <v>13</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>70</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>154</v>
       </c>
@@ -3533,11 +3562,11 @@
       <c r="E124" t="s">
         <v>13</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>50</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>154</v>
       </c>
@@ -3553,11 +3582,11 @@
       <c r="E125" t="s">
         <v>13</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>2</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -3573,11 +3602,11 @@
       <c r="E126" t="s">
         <v>13</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>1</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -3593,11 +3622,11 @@
       <c r="E127" t="s">
         <v>13</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>50</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>154</v>
       </c>
@@ -3613,11 +3642,11 @@
       <c r="E128" t="s">
         <v>16</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128">
         <v>80</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>154</v>
       </c>
@@ -3633,11 +3662,11 @@
       <c r="E129" t="s">
         <v>16</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129">
         <v>80</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>154</v>
       </c>
@@ -3653,11 +3682,11 @@
       <c r="E130" t="s">
         <v>16</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130">
         <v>40</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>154</v>
       </c>
@@ -3673,11 +3702,11 @@
       <c r="E131" t="s">
         <v>67</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131">
         <v>35</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>154</v>
       </c>
@@ -3693,11 +3722,11 @@
       <c r="E132" t="s">
         <v>67</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132">
         <v>30</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>154</v>
       </c>
@@ -3713,11 +3742,11 @@
       <c r="E133" t="s">
         <v>67</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133">
         <v>40</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>154</v>
       </c>
@@ -3733,11 +3762,11 @@
       <c r="E134" t="s">
         <v>22</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134">
         <v>80</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>154</v>
       </c>
@@ -3753,11 +3782,11 @@
       <c r="E135" t="s">
         <v>22</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135">
         <v>70</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -3773,11 +3802,11 @@
       <c r="E136" t="s">
         <v>22</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136">
         <v>30</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -3793,11 +3822,11 @@
       <c r="E137" t="s">
         <v>22</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137">
         <v>25</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>154</v>
       </c>
@@ -3813,11 +3842,11 @@
       <c r="E138" t="s">
         <v>31</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138">
         <v>75</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>154</v>
       </c>
@@ -3833,11 +3862,11 @@
       <c r="E139" t="s">
         <v>31</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139">
         <v>25</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -3853,11 +3882,11 @@
       <c r="E140" t="s">
         <v>31</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140">
         <v>15</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>154</v>
       </c>
@@ -3873,11 +3902,11 @@
       <c r="E141" t="s">
         <v>10</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141">
         <v>20</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>154</v>
       </c>
@@ -3893,11 +3922,11 @@
       <c r="E142" t="s">
         <v>10</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142">
         <v>20</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>154</v>
       </c>
@@ -3913,11 +3942,11 @@
       <c r="E143" t="s">
         <v>13</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143">
         <v>300</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>154</v>
       </c>
@@ -3933,11 +3962,11 @@
       <c r="E144" t="s">
         <v>13</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144">
         <v>100</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>154</v>
       </c>
@@ -3953,11 +3982,11 @@
       <c r="E145" t="s">
         <v>13</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145">
         <v>75</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>154</v>
       </c>
@@ -3973,11 +4002,11 @@
       <c r="E146" t="s">
         <v>13</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146">
         <v>55</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -3993,11 +4022,11 @@
       <c r="E147" t="s">
         <v>16</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147">
         <v>30</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>154</v>
       </c>
@@ -4013,11 +4042,11 @@
       <c r="E148" t="s">
         <v>16</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148">
         <v>25</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>154</v>
       </c>
@@ -4033,11 +4062,11 @@
       <c r="E149" t="s">
         <v>67</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149">
         <v>25</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>154</v>
       </c>
@@ -4053,11 +4082,11 @@
       <c r="E150" t="s">
         <v>67</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150">
         <v>50</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>154</v>
       </c>
@@ -4073,11 +4102,11 @@
       <c r="E151" t="s">
         <v>45</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151">
         <v>10</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -4093,11 +4122,11 @@
       <c r="E152" t="s">
         <v>48</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152">
         <v>10</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>154</v>
       </c>
@@ -4113,11 +4142,11 @@
       <c r="E153" t="s">
         <v>48</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153">
         <v>10</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>154</v>
       </c>
@@ -4133,11 +4162,11 @@
       <c r="E154" t="s">
         <v>22</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154">
         <v>60</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>154</v>
       </c>
@@ -4153,11 +4182,11 @@
       <c r="E155" t="s">
         <v>22</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155">
         <v>40</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>154</v>
       </c>
@@ -4173,11 +4202,11 @@
       <c r="E156" t="s">
         <v>26</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156">
         <v>40</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>190</v>
       </c>
@@ -4193,11 +4222,11 @@
       <c r="E157" t="s">
         <v>10</v>
       </c>
-      <c r="F157" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="158">
+      <c r="F157">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>190</v>
       </c>
@@ -4213,11 +4242,11 @@
       <c r="E158" t="s">
         <v>10</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F158">
         <v>27</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>190</v>
       </c>
@@ -4233,11 +4262,11 @@
       <c r="E159" t="s">
         <v>10</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159">
         <v>13</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>190</v>
       </c>
@@ -4253,11 +4282,11 @@
       <c r="E160" t="s">
         <v>10</v>
       </c>
-      <c r="F160" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="161">
+      <c r="F160">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>190</v>
       </c>
@@ -4273,11 +4302,11 @@
       <c r="E161" t="s">
         <v>13</v>
       </c>
-      <c r="F161" t="n">
+      <c r="F161">
         <v>42</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4293,11 +4322,11 @@
       <c r="E162" t="s">
         <v>13</v>
       </c>
-      <c r="F162" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="163">
+      <c r="F162">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>190</v>
       </c>
@@ -4313,11 +4342,11 @@
       <c r="E163" t="s">
         <v>16</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F163">
         <v>16</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>190</v>
       </c>
@@ -4333,11 +4362,11 @@
       <c r="E164" t="s">
         <v>16</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F164">
         <v>3</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>190</v>
       </c>
@@ -4353,11 +4382,11 @@
       <c r="E165" t="s">
         <v>16</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F165">
         <v>2</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>190</v>
       </c>
@@ -4373,11 +4402,11 @@
       <c r="E166" t="s">
         <v>16</v>
       </c>
-      <c r="F166" t="n">
+      <c r="F166">
         <v>2</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>190</v>
       </c>
@@ -4388,16 +4417,16 @@
         <v>201</v>
       </c>
       <c r="D167" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="E167" t="s">
         <v>19</v>
       </c>
-      <c r="F167" t="n">
+      <c r="F167">
         <v>18</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>190</v>
       </c>
@@ -4413,11 +4442,11 @@
       <c r="E168" t="s">
         <v>67</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F168">
         <v>99</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>190</v>
       </c>
@@ -4433,11 +4462,11 @@
       <c r="E169" t="s">
         <v>67</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F169">
         <v>11</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>190</v>
       </c>
@@ -4453,11 +4482,11 @@
       <c r="E170" t="s">
         <v>67</v>
       </c>
-      <c r="F170" t="n">
+      <c r="F170">
         <v>4</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>190</v>
       </c>
@@ -4473,11 +4502,11 @@
       <c r="E171" t="s">
         <v>67</v>
       </c>
-      <c r="F171" t="n">
+      <c r="F171">
         <v>2</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>190</v>
       </c>
@@ -4493,11 +4522,11 @@
       <c r="E172" t="s">
         <v>22</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F172">
         <v>69</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>190</v>
       </c>
@@ -4513,11 +4542,11 @@
       <c r="E173" t="s">
         <v>22</v>
       </c>
-      <c r="F173" t="n">
+      <c r="F173">
         <v>8</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>190</v>
       </c>
@@ -4533,11 +4562,11 @@
       <c r="E174" t="s">
         <v>22</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F174">
         <v>68</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>190</v>
       </c>
@@ -4553,11 +4582,11 @@
       <c r="E175" t="s">
         <v>22</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F175">
         <v>11</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>190</v>
       </c>
@@ -4573,11 +4602,11 @@
       <c r="E176" t="s">
         <v>26</v>
       </c>
-      <c r="F176" t="n">
+      <c r="F176">
         <v>55</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>190</v>
       </c>
@@ -4593,11 +4622,11 @@
       <c r="E177" t="s">
         <v>26</v>
       </c>
-      <c r="F177" t="n">
+      <c r="F177">
         <v>11</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>190</v>
       </c>
@@ -4613,11 +4642,11 @@
       <c r="E178" t="s">
         <v>26</v>
       </c>
-      <c r="F178" t="n">
+      <c r="F178">
         <v>4</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>190</v>
       </c>
@@ -4633,11 +4662,11 @@
       <c r="E179" t="s">
         <v>26</v>
       </c>
-      <c r="F179" t="n">
+      <c r="F179">
         <v>1</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>190</v>
       </c>
@@ -4653,11 +4682,11 @@
       <c r="E180" t="s">
         <v>74</v>
       </c>
-      <c r="F180" t="n">
+      <c r="F180">
         <v>87</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>190</v>
       </c>
@@ -4673,11 +4702,11 @@
       <c r="E181" t="s">
         <v>74</v>
       </c>
-      <c r="F181" t="n">
+      <c r="F181">
         <v>2</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>190</v>
       </c>
@@ -4693,11 +4722,11 @@
       <c r="E182" t="s">
         <v>31</v>
       </c>
-      <c r="F182" t="n">
+      <c r="F182">
         <v>139</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -4713,11 +4742,11 @@
       <c r="E183" t="s">
         <v>31</v>
       </c>
-      <c r="F183" t="n">
+      <c r="F183">
         <v>58</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>190</v>
       </c>
@@ -4733,11 +4762,11 @@
       <c r="E184" t="s">
         <v>31</v>
       </c>
-      <c r="F184" t="n">
+      <c r="F184">
         <v>44</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>190</v>
       </c>
@@ -4753,11 +4782,11 @@
       <c r="E185" t="s">
         <v>10</v>
       </c>
-      <c r="F185" t="n">
+      <c r="F185">
         <v>57</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>190</v>
       </c>
@@ -4773,11 +4802,11 @@
       <c r="E186" t="s">
         <v>10</v>
       </c>
-      <c r="F186" t="n">
+      <c r="F186">
         <v>49</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>190</v>
       </c>
@@ -4793,11 +4822,11 @@
       <c r="E187" t="s">
         <v>10</v>
       </c>
-      <c r="F187" t="n">
+      <c r="F187">
         <v>27</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>190</v>
       </c>
@@ -4813,11 +4842,11 @@
       <c r="E188" t="s">
         <v>10</v>
       </c>
-      <c r="F188" t="n">
+      <c r="F188">
         <v>16</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -4833,11 +4862,11 @@
       <c r="E189" t="s">
         <v>13</v>
       </c>
-      <c r="F189" t="n">
+      <c r="F189">
         <v>51</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>190</v>
       </c>
@@ -4853,11 +4882,11 @@
       <c r="E190" t="s">
         <v>13</v>
       </c>
-      <c r="F190" t="n">
+      <c r="F190">
         <v>92</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>190</v>
       </c>
@@ -4873,11 +4902,11 @@
       <c r="E191" t="s">
         <v>38</v>
       </c>
-      <c r="F191" t="n">
+      <c r="F191">
         <v>98</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>190</v>
       </c>
@@ -4893,11 +4922,11 @@
       <c r="E192" t="s">
         <v>38</v>
       </c>
-      <c r="F192" t="n">
+      <c r="F192">
         <v>3</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>190</v>
       </c>
@@ -4913,11 +4942,11 @@
       <c r="E193" t="s">
         <v>16</v>
       </c>
-      <c r="F193" t="n">
+      <c r="F193">
         <v>8</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>190</v>
       </c>
@@ -4933,11 +4962,11 @@
       <c r="E194" t="s">
         <v>16</v>
       </c>
-      <c r="F194" t="n">
+      <c r="F194">
         <v>3</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>190</v>
       </c>
@@ -4953,11 +4982,11 @@
       <c r="E195" t="s">
         <v>67</v>
       </c>
-      <c r="F195" t="n">
+      <c r="F195">
         <v>13</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>190</v>
       </c>
@@ -4973,11 +5002,11 @@
       <c r="E196" t="s">
         <v>67</v>
       </c>
-      <c r="F196" t="n">
+      <c r="F196">
         <v>4</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>190</v>
       </c>
@@ -4993,11 +5022,11 @@
       <c r="E197" t="s">
         <v>43</v>
       </c>
-      <c r="F197" t="n">
+      <c r="F197">
         <v>23</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>190</v>
       </c>
@@ -5013,11 +5042,11 @@
       <c r="E198" t="s">
         <v>144</v>
       </c>
-      <c r="F198" t="n">
+      <c r="F198">
         <v>5</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>190</v>
       </c>
@@ -5033,11 +5062,11 @@
       <c r="E199" t="s">
         <v>45</v>
       </c>
-      <c r="F199" t="n">
+      <c r="F199">
         <v>47</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>190</v>
       </c>
@@ -5053,11 +5082,11 @@
       <c r="E200" t="s">
         <v>45</v>
       </c>
-      <c r="F200" t="n">
+      <c r="F200">
         <v>6</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>190</v>
       </c>
@@ -5073,11 +5102,11 @@
       <c r="E201" t="s">
         <v>48</v>
       </c>
-      <c r="F201" t="n">
+      <c r="F201">
         <v>18</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>190</v>
       </c>
@@ -5093,11 +5122,11 @@
       <c r="E202" t="s">
         <v>48</v>
       </c>
-      <c r="F202" t="n">
+      <c r="F202">
         <v>17</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>190</v>
       </c>
@@ -5113,11 +5142,11 @@
       <c r="E203" t="s">
         <v>92</v>
       </c>
-      <c r="F203" t="n">
+      <c r="F203">
         <v>4</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>190</v>
       </c>
@@ -5133,11 +5162,11 @@
       <c r="E204" t="s">
         <v>92</v>
       </c>
-      <c r="F204" t="n">
+      <c r="F204">
         <v>1</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>190</v>
       </c>
@@ -5153,11 +5182,11 @@
       <c r="E205" t="s">
         <v>26</v>
       </c>
-      <c r="F205" t="n">
+      <c r="F205">
         <v>6</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>190</v>
       </c>
@@ -5173,12 +5202,12 @@
       <c r="E206" t="s">
         <v>26</v>
       </c>
-      <c r="F206" t="n">
+      <c r="F206">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755148A4-CA0B-47F4-BFF5-2688322257A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3D7CF1-7742-4331-97B8-49EFD15B2238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="241">
   <si>
     <t>Manager</t>
   </si>
@@ -750,6 +750,12 @@
   </si>
   <si>
     <t>San Jose Sharks</t>
+  </si>
+  <si>
+    <t>ATP</t>
+  </si>
+  <si>
+    <t>WTA</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1383,7 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -1397,7 +1403,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -2017,7 +2023,7 @@
         <v>76</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
@@ -2997,7 +3003,7 @@
         <v>127</v>
       </c>
       <c r="D96" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="E96" t="s">
         <v>31</v>
@@ -3017,7 +3023,7 @@
         <v>128</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="E97" t="s">
         <v>31</v>
@@ -3037,7 +3043,7 @@
         <v>129</v>
       </c>
       <c r="D98" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="E98" t="s">
         <v>31</v>
@@ -3837,7 +3843,7 @@
         <v>171</v>
       </c>
       <c r="D138" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="E138" t="s">
         <v>31</v>
@@ -3857,7 +3863,7 @@
         <v>172</v>
       </c>
       <c r="D139" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="E139" t="s">
         <v>31</v>
@@ -3877,7 +3883,7 @@
         <v>173</v>
       </c>
       <c r="D140" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="E140" t="s">
         <v>31</v>
@@ -4717,7 +4723,7 @@
         <v>216</v>
       </c>
       <c r="D182" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="E182" t="s">
         <v>31</v>
@@ -4737,7 +4743,7 @@
         <v>217</v>
       </c>
       <c r="D183" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="E183" t="s">
         <v>31</v>
@@ -4757,7 +4763,7 @@
         <v>218</v>
       </c>
       <c r="D184" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="E184" t="s">
         <v>31</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3D7CF1-7742-4331-97B8-49EFD15B2238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36A4EB-306D-4438-B779-2EEBEF9F087D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="313">
   <si>
     <t>Manager</t>
   </si>
@@ -68,6 +68,21 @@
     <t>Club Soccer Other</t>
   </si>
   <si>
+    <t>Khvicha Kvaratskhelia</t>
+  </si>
+  <si>
+    <t>Ligue 1</t>
+  </si>
+  <si>
+    <t>Désiré Doué</t>
+  </si>
+  <si>
+    <t>Denis Bouanga</t>
+  </si>
+  <si>
+    <t>MLS</t>
+  </si>
+  <si>
     <t>Florian Wirtz</t>
   </si>
   <si>
@@ -80,12 +95,27 @@
     <t>Bryan Mbeumo</t>
   </si>
   <si>
+    <t>Alexander Isak</t>
+  </si>
+  <si>
+    <t>Dominik Szoboszlai</t>
+  </si>
+  <si>
     <t>Ronald Acuna Jr.</t>
   </si>
   <si>
     <t>MLB</t>
   </si>
   <si>
+    <t>Juan Soto</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Jose Ramirez</t>
+  </si>
+  <si>
     <t>Max Verstappen</t>
   </si>
   <si>
@@ -98,6 +128,21 @@
     <t>Oscar Piastri</t>
   </si>
   <si>
+    <t>Shai Gilgeous-Alexander</t>
+  </si>
+  <si>
+    <t>NBA</t>
+  </si>
+  <si>
+    <t>Jayson Tatum</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Cooper Flagg</t>
+  </si>
+  <si>
     <t>Ja'Marr Chase</t>
   </si>
   <si>
@@ -125,24 +170,60 @@
     <t>Leon Draisaitl</t>
   </si>
   <si>
+    <t>Ludvig Aberg</t>
+  </si>
+  <si>
+    <t>PGA</t>
+  </si>
+  <si>
+    <t>Jon Rahm</t>
+  </si>
+  <si>
+    <t>Justin Thomas</t>
+  </si>
+  <si>
     <t>Novak Djokovic</t>
   </si>
   <si>
+    <t>ATP</t>
+  </si>
+  <si>
     <t>Tennis</t>
   </si>
   <si>
     <t>Iga Swiatek</t>
   </si>
   <si>
+    <t>WTA</t>
+  </si>
+  <si>
+    <t>Elena Rybakina</t>
+  </si>
+  <si>
     <t>Team</t>
   </si>
   <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Seattle Sounders FC</t>
+  </si>
+  <si>
     <t>Manchester United</t>
   </si>
   <si>
     <t>Liverpool</t>
   </si>
   <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Napoli</t>
+  </si>
+  <si>
+    <t>Serie A</t>
+  </si>
+  <si>
     <t>Spain</t>
   </si>
   <si>
@@ -161,6 +242,15 @@
     <t>Milwaukee Brewers</t>
   </si>
   <si>
+    <t>Atlanta Braves</t>
+  </si>
+  <si>
+    <t>San Antonio Spurs</t>
+  </si>
+  <si>
+    <t>Houston Rockets</t>
+  </si>
+  <si>
     <t>LSU Tigers</t>
   </si>
   <si>
@@ -191,21 +281,18 @@
     <t>Colorado Avalanche</t>
   </si>
   <si>
+    <t>Edmonton Oilers</t>
+  </si>
+  <si>
     <t>LS</t>
   </si>
   <si>
     <t>Florian Thauvin</t>
   </si>
   <si>
-    <t>Ligue 1</t>
-  </si>
-  <si>
     <t>Nicolás Fernández</t>
   </si>
   <si>
-    <t>MLS</t>
-  </si>
-  <si>
     <t>Esteban Lepaul</t>
   </si>
   <si>
@@ -233,39 +320,57 @@
     <t>Yordan Alvarez</t>
   </si>
   <si>
+    <t>Kyle Schwarber</t>
+  </si>
+  <si>
+    <t>Miguel Vargas</t>
+  </si>
+  <si>
     <t>Jalen Brunson</t>
   </si>
   <si>
-    <t>NBA</t>
-  </si>
-  <si>
     <t>Luka Doncic</t>
   </si>
   <si>
-    <t>Shai Gilgeous-Alexander</t>
-  </si>
-  <si>
     <t>Jahmyr Gibbs</t>
   </si>
   <si>
     <t>Justin Herbert</t>
   </si>
   <si>
+    <t>Amon-Ra St. Brown</t>
+  </si>
+  <si>
+    <t>Jonathan Taylor</t>
+  </si>
+  <si>
     <t>Nikita Kucherov</t>
   </si>
   <si>
+    <t>David Pastrnak</t>
+  </si>
+  <si>
+    <t>Cole Caufield</t>
+  </si>
+  <si>
+    <t>Matt Boldy</t>
+  </si>
+  <si>
     <t>Scottie Scheffler</t>
   </si>
   <si>
-    <t>PGA</t>
-  </si>
-  <si>
     <t>Viktor Hovland</t>
   </si>
   <si>
     <t>Flavio Cobolli</t>
   </si>
   <si>
+    <t>Linda Noskova</t>
+  </si>
+  <si>
+    <t>Taylor Fritz</t>
+  </si>
+  <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
@@ -290,6 +395,12 @@
     <t>Everton</t>
   </si>
   <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
     <t>Kansas City Royals</t>
   </si>
   <si>
@@ -302,6 +413,15 @@
     <t>Memphis Grizzlies</t>
   </si>
   <si>
+    <t>Auburn Tigers</t>
+  </si>
+  <si>
+    <t>Texas Tech Lady Raiders</t>
+  </si>
+  <si>
+    <t>NCAA Softball</t>
+  </si>
+  <si>
     <t>Ohio State Buckeyes</t>
   </si>
   <si>
@@ -311,9 +431,15 @@
     <t>Nebraska Cornhuskers</t>
   </si>
   <si>
+    <t>Duke Blue Devils</t>
+  </si>
+  <si>
     <t>NCAAW</t>
   </si>
   <si>
+    <t>NC State Wolfpack</t>
+  </si>
+  <si>
     <t>Los Angeles Rams</t>
   </si>
   <si>
@@ -356,6 +482,9 @@
     <t>Bruno Fernandes</t>
   </si>
   <si>
+    <t>João Pedro</t>
+  </si>
+  <si>
     <t>Shohei Ohtani</t>
   </si>
   <si>
@@ -407,6 +536,12 @@
     <t>Logan Thompson</t>
   </si>
   <si>
+    <t>Kirill Kaprizov</t>
+  </si>
+  <si>
+    <t>Quinn Hughes</t>
+  </si>
+  <si>
     <t>Cameron Young</t>
   </si>
   <si>
@@ -431,15 +566,15 @@
     <t>Bayern Munich</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
     <t>Arsenal</t>
   </si>
   <si>
     <t>Internazionale</t>
   </si>
   <si>
-    <t>Serie A</t>
-  </si>
-  <si>
     <t>AS Roma</t>
   </si>
   <si>
@@ -467,12 +602,12 @@
     <t>Texas</t>
   </si>
   <si>
-    <t>NCAA Softball</t>
-  </si>
-  <si>
     <t>James Madison Dukes</t>
   </si>
   <si>
+    <t>Georgia Bulldogs</t>
+  </si>
+  <si>
     <t>Florida Gators</t>
   </si>
   <si>
@@ -488,274 +623,355 @@
     <t>Baltimore Ravens</t>
   </si>
   <si>
+    <t>Denver Broncos</t>
+  </si>
+  <si>
+    <t>Florida Panthers</t>
+  </si>
+  <si>
+    <t>Vegas Golden Knights</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>Harry Kane</t>
+  </si>
+  <si>
+    <t>Cavan Sullivan</t>
+  </si>
+  <si>
+    <t>Son Heung-Min</t>
+  </si>
+  <si>
+    <t>Casemiro</t>
+  </si>
+  <si>
+    <t>Thomas Müller</t>
+  </si>
+  <si>
+    <t>Granit Xhaka</t>
+  </si>
+  <si>
+    <t>Wilson Isidor</t>
+  </si>
+  <si>
+    <t>Nordi Mukiele</t>
+  </si>
+  <si>
+    <t>Christian Pulisic</t>
+  </si>
+  <si>
+    <t>Vinícius Júnior</t>
+  </si>
+  <si>
+    <t>Aaron Judge</t>
+  </si>
+  <si>
+    <t>Gunnar Henderson</t>
+  </si>
+  <si>
+    <t>Bobby Witt Jr.</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Lando Norris</t>
+  </si>
+  <si>
+    <t>Carlos Sainz</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Josh Allen</t>
+  </si>
+  <si>
+    <t>Derrick Henry</t>
+  </si>
+  <si>
+    <t>Jaxon Smith-Njigba</t>
+  </si>
+  <si>
+    <t>Patrick Mahomes</t>
+  </si>
+  <si>
+    <t>Alex Ovechkin</t>
+  </si>
+  <si>
+    <t>Andrei Vasilevskiy</t>
+  </si>
+  <si>
+    <t>Aleksander Barkov</t>
+  </si>
+  <si>
+    <t>Connor Hellebuyck</t>
+  </si>
+  <si>
+    <t>Matt Fitzpatrick</t>
+  </si>
+  <si>
+    <t>Russell Henley</t>
+  </si>
+  <si>
+    <t>Arthur Fils</t>
+  </si>
+  <si>
+    <t>Jessica Pegula</t>
+  </si>
+  <si>
+    <t>Stefanos Tsitsipas</t>
+  </si>
+  <si>
+    <t>AS Monaco</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>LAFC</t>
+  </si>
+  <si>
+    <t>Inter Miami CF</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Ipswich Town</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Athletics</t>
+  </si>
+  <si>
+    <t>Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Golden State Warriors</t>
+  </si>
+  <si>
+    <t>Boston Celtics</t>
+  </si>
+  <si>
+    <t>Oklahoma Sooners</t>
+  </si>
+  <si>
+    <t>Texas Longhorns</t>
+  </si>
+  <si>
+    <t>Arizona Wildcats</t>
+  </si>
+  <si>
+    <t>Michigan Wolverines</t>
+  </si>
+  <si>
+    <t>UCLA Bruins</t>
+  </si>
+  <si>
+    <t>South Carolina Gamecocks</t>
+  </si>
+  <si>
+    <t>Buffalo Bills</t>
+  </si>
+  <si>
+    <t>Philadelphia Eagles</t>
+  </si>
+  <si>
+    <t>Washington Capitals</t>
+  </si>
+  <si>
+    <t>Tampa Bay Lightning</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>Folarin Balogun</t>
+  </si>
+  <si>
+    <t>Michael Olise</t>
+  </si>
+  <si>
+    <t>Luis Díaz</t>
+  </si>
+  <si>
+    <t>Evander</t>
+  </si>
+  <si>
+    <t>Robert Lewandowski</t>
+  </si>
+  <si>
+    <t>Igor Thiago</t>
+  </si>
+  <si>
+    <t>Julián Álvarez</t>
+  </si>
+  <si>
+    <t>Mariano Díaz</t>
+  </si>
+  <si>
+    <t>Kevin McGonigle</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Dillon Dingler</t>
+  </si>
+  <si>
+    <t>Grant Taylor</t>
+  </si>
+  <si>
+    <t>Kyle Larson</t>
+  </si>
+  <si>
+    <t>Lewis Hamilton</t>
+  </si>
+  <si>
+    <t>Victor Wembanyama</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>AJ Dybantsa</t>
+  </si>
+  <si>
+    <t>Lamar Jackson</t>
+  </si>
+  <si>
+    <t>Jeremiyah Love</t>
+  </si>
+  <si>
+    <t>Drake Maye</t>
+  </si>
+  <si>
+    <t>Omarion Hampton</t>
+  </si>
+  <si>
+    <t>Macklin Celebrini</t>
+  </si>
+  <si>
+    <t>Sidney Crosby</t>
+  </si>
+  <si>
+    <t>Jake Guentzel</t>
+  </si>
+  <si>
+    <t>Evgeni Malkin</t>
+  </si>
+  <si>
+    <t>Rory McIlroy</t>
+  </si>
+  <si>
+    <t>John Daly II</t>
+  </si>
+  <si>
+    <t>Wyndham Clark</t>
+  </si>
+  <si>
+    <t>Carlos Alcaraz</t>
+  </si>
+  <si>
+    <t>Aryna Sabalenka</t>
+  </si>
+  <si>
+    <t>Ben Shelton</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>VfB Stuttgart</t>
+  </si>
+  <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
+    <t>Washington Wizards</t>
+  </si>
+  <si>
+    <t>West Virginia Mountaineers</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Notre Dame Fighting Irish</t>
+  </si>
+  <si>
+    <t>Penn State Nittany Lions</t>
+  </si>
+  <si>
+    <t>Michigan State Spartans</t>
+  </si>
+  <si>
+    <t>St. John's Red Storm</t>
+  </si>
+  <si>
+    <t>Fairfield Stags</t>
+  </si>
+  <si>
+    <t>Cincinnati Bengals</t>
+  </si>
+  <si>
     <t>San Francisco 49ers</t>
   </si>
   <si>
-    <t>Florida Panthers</t>
-  </si>
-  <si>
-    <t>Vegas Golden Knights</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>Harry Kane</t>
-  </si>
-  <si>
-    <t>Granit Xhaka</t>
-  </si>
-  <si>
-    <t>Wilson Isidor</t>
-  </si>
-  <si>
-    <t>Nordi Mukiele</t>
-  </si>
-  <si>
-    <t>Christian Pulisic</t>
-  </si>
-  <si>
-    <t>Vinícius Júnior</t>
-  </si>
-  <si>
-    <t>Aaron Judge</t>
-  </si>
-  <si>
-    <t>Gunnar Henderson</t>
-  </si>
-  <si>
-    <t>Bobby Witt Jr.</t>
-  </si>
-  <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Stephen Curry</t>
-  </si>
-  <si>
-    <t>Giannis Antetokounmpo</t>
-  </si>
-  <si>
-    <t>Josh Allen</t>
-  </si>
-  <si>
-    <t>Derrick Henry</t>
-  </si>
-  <si>
-    <t>Jaxon Smith-Njigba</t>
-  </si>
-  <si>
-    <t>Patrick Mahomes</t>
-  </si>
-  <si>
-    <t>Arthur Fils</t>
-  </si>
-  <si>
-    <t>Jessica Pegula</t>
-  </si>
-  <si>
-    <t>Stefanos Tsitsipas</t>
-  </si>
-  <si>
-    <t>AS Monaco</t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Ipswich Town</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Athletics</t>
-  </si>
-  <si>
-    <t>Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Golden State Warriors</t>
-  </si>
-  <si>
-    <t>Boston Celtics</t>
-  </si>
-  <si>
-    <t>Texas Longhorns</t>
-  </si>
-  <si>
-    <t>Arizona Wildcats</t>
-  </si>
-  <si>
-    <t>Michigan Wolverines</t>
-  </si>
-  <si>
-    <t>Buffalo Bills</t>
-  </si>
-  <si>
-    <t>Philadelphia Eagles</t>
-  </si>
-  <si>
-    <t>Washington Capitals</t>
-  </si>
-  <si>
-    <t>TG</t>
-  </si>
-  <si>
-    <t>Folarin Balogun</t>
-  </si>
-  <si>
-    <t>Michael Olise</t>
-  </si>
-  <si>
-    <t>Luis Díaz</t>
-  </si>
-  <si>
-    <t>Evander</t>
-  </si>
-  <si>
-    <t>Igor Thiago</t>
-  </si>
-  <si>
-    <t>Julián Álvarez</t>
-  </si>
-  <si>
-    <t>Kevin McGonigle</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Dillon Dingler</t>
-  </si>
-  <si>
-    <t>Grant Taylor</t>
-  </si>
-  <si>
-    <t>Kyle Larson</t>
-  </si>
-  <si>
-    <t>Victor Wembanyama</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Kawhi Leonard</t>
-  </si>
-  <si>
-    <t>AJ Dybantsa</t>
-  </si>
-  <si>
-    <t>Lamar Jackson</t>
-  </si>
-  <si>
-    <t>Jeremiyah Love</t>
-  </si>
-  <si>
-    <t>Drake Maye</t>
-  </si>
-  <si>
-    <t>Omarion Hampton</t>
-  </si>
-  <si>
-    <t>Macklin Celebrini</t>
-  </si>
-  <si>
-    <t>Sidney Crosby</t>
-  </si>
-  <si>
-    <t>Jake Guentzel</t>
-  </si>
-  <si>
-    <t>Evgeni Malkin</t>
-  </si>
-  <si>
-    <t>Rory McIlroy</t>
-  </si>
-  <si>
-    <t>John Daly II</t>
-  </si>
-  <si>
-    <t>Carlos Alcaraz</t>
-  </si>
-  <si>
-    <t>Aryna Sabalenka</t>
-  </si>
-  <si>
-    <t>Ben Shelton</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>VfB Stuttgart</t>
-  </si>
-  <si>
-    <t>Bayer Leverkusen</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Denver Nuggets</t>
-  </si>
-  <si>
-    <t>Washington Wizards</t>
-  </si>
-  <si>
-    <t>West Virginia Mountaineers</t>
-  </si>
-  <si>
-    <t>Oklahoma</t>
-  </si>
-  <si>
-    <t>Notre Dame Fighting Irish</t>
-  </si>
-  <si>
-    <t>Penn State Nittany Lions</t>
-  </si>
-  <si>
-    <t>Michigan State Spartans</t>
-  </si>
-  <si>
-    <t>St. John's Red Storm</t>
-  </si>
-  <si>
-    <t>Fairfield Stags</t>
-  </si>
-  <si>
     <t>Pittsburgh Penguins</t>
   </si>
   <si>
     <t>San Jose Sharks</t>
   </si>
   <si>
-    <t>ATP</t>
-  </si>
-  <si>
-    <t>WTA</t>
+    <t>Washington Spirit</t>
+  </si>
+  <si>
+    <t>NWSL</t>
+  </si>
+  <si>
+    <t>Ashley Sanchez</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1146,10 +1362,10 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1160,16 +1376,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1180,16 +1396,16 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1200,16 +1416,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
       <c r="F6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1220,16 +1436,16 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
       <c r="F7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1240,16 +1456,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1260,16 +1476,16 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1280,16 +1496,16 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1300,16 +1516,16 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1320,16 +1536,16 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>38</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1340,16 +1556,16 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1360,16 +1576,16 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
         <v>29</v>
       </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
       <c r="F14">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1383,13 +1599,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1400,16 +1616,16 @@
         <v>7</v>
       </c>
       <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" t="s">
-        <v>240</v>
-      </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1417,19 +1633,19 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>200</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1437,19 +1653,19 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>18</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1457,19 +1673,19 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1477,19 +1693,19 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1497,19 +1713,19 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F21">
-        <v>200</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1517,19 +1733,19 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1537,19 +1753,19 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F23">
-        <v>200</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1557,19 +1773,19 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F24">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1577,19 +1793,19 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F25">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1597,19 +1813,19 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F26">
-        <v>200</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -1617,19 +1833,19 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1637,936 +1853,936 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F29">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F30">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
         <v>52</v>
       </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>25</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F37">
-        <v>200</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F38">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D39" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F39">
-        <v>150</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D40" t="s">
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F40">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F41">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F42">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F43">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F44">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" t="s">
         <v>73</v>
       </c>
-      <c r="D45" t="s">
-        <v>74</v>
-      </c>
       <c r="E45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F45">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" t="s">
         <v>75</v>
       </c>
-      <c r="D46" t="s">
-        <v>74</v>
-      </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
         <v>76</v>
       </c>
       <c r="D47" t="s">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F47">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
         <v>77</v>
       </c>
       <c r="D48" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F48">
-        <v>75</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F49">
-        <v>45</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F50">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F51">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E52" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F52">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F53">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F54">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F55">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F56">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F57">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="E58" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F58">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D59" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E59" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F59">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D60" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E60" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F60">
-        <v>90</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D61" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D62" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F62">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D63" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="F63">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64">
-        <v>125</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F65">
-        <v>75</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E66" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F66">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B67" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E67" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F67">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E68" t="s">
+        <v>37</v>
+      </c>
+      <c r="F68">
         <v>10</v>
-      </c>
-      <c r="F68">
-        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B69" t="s">
         <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D69" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F69">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B70" t="s">
         <v>7</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D70" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F70">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B72" t="s">
         <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D72" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E72" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B73" t="s">
         <v>7</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D73" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F73">
-        <v>90</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F74">
         <v>25</v>
@@ -2574,439 +2790,439 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B75" t="s">
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F75">
-        <v>17</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D76" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F76">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B77" t="s">
         <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E77" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F77">
-        <v>200</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B78" t="s">
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E78" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F78">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
         <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E79" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F79">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F80">
-        <v>15</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F81">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D83" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="F83">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D84" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E84" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F84">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D85" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E85" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F85">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C86" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D86" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="E86" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F86">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D87" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E87" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F87">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B88" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D88" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E88" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="F88">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B89" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D89" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="F89">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B90" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F90">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B91" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D91" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E91" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F91">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C92" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E92" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B93" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D93" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E93" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="F93">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B94" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F94">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B95" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C95" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D95" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E95" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B96" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D96" t="s">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="E96" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F96">
         <v>90</v>
@@ -3014,499 +3230,499 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D97" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="E97" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F97">
-        <v>141</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B98" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D98" t="s">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="E98" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="F98">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B99" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D99" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E99" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F99">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B100" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="E100" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="F100">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D101" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="E101" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="F101">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C102" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D102" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="E102" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F102">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D103" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="E103" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F103">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D104" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="E104" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F104">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D105" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F105">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="D106" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F106">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B107" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>175</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B108" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F108">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D109" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="F109">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B110" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D110" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="F110">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B111" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B112" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D112" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="E112" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="F112">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B113" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E113" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F113">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B114" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E114" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F114">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E115" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F115">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B116" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D116" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E116" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="F116">
-        <v>30</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D117" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E117" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="F117">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C118" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D118" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E118" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F118">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D119" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E119" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F119">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B120" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D120" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E120" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F120">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D121" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E121" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F121">
         <v>5</v>
@@ -3514,1702 +3730,3142 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D122" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E122" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F122">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B123" t="s">
         <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E123" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F123">
-        <v>70</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D124" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E124" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F124">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D125" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E125" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B126" t="s">
         <v>7</v>
       </c>
       <c r="C126" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D126" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="E126" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B127" t="s">
         <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="E127" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F127">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E128" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F128">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B129" t="s">
         <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E129" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F129">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B130" t="s">
         <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E130" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F130">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D131" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E131" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F131">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B132" t="s">
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D132" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E132" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F132">
-        <v>30</v>
+        <v>170</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B133" t="s">
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D133" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E133" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F133">
-        <v>40</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D134" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E134" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F134">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B135" t="s">
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D135" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E135" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F135">
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B136" t="s">
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D136" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E136" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F136">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D137" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E137" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F137">
-        <v>25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
       </c>
       <c r="C138" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D138" t="s">
-        <v>239</v>
+        <v>53</v>
       </c>
       <c r="E138" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F138">
-        <v>75</v>
+        <v>141</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D139" t="s">
-        <v>240</v>
+        <v>53</v>
       </c>
       <c r="E139" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F139">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C140" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D140" t="s">
-        <v>239</v>
+        <v>12</v>
       </c>
       <c r="E140" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F140">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D141" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
       </c>
       <c r="F141">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B142" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D142" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
       </c>
       <c r="F142">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D143" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E143" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F143">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D144" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E144" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F144">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B145" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C145" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D145" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E145" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F145">
-        <v>75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B146" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D146" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E146" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F146">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B147" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C147" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E147" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F147">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B148" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C148" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="D148" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E148" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F148">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B149" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C149" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D149" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E149" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F149">
-        <v>25</v>
+        <v>175</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B150" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C150" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D150" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E150" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F150">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B151" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C151" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D151" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E151" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F151">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B152" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C152" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D152" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E152" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F152">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B153" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C153" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D153" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E153" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F153">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B154" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C154" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D154" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="E154" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="F154">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B155" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D155" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="E155" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="F155">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B156" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C156" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D156" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="E156" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="F156">
-        <v>40</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B157" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C157" t="s">
         <v>191</v>
       </c>
       <c r="D157" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E157" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F157">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B158" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C158" t="s">
         <v>192</v>
       </c>
       <c r="D158" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="E158" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F158">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B159" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C159" t="s">
         <v>193</v>
       </c>
       <c r="D159" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="E159" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="F159">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B160" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C160" t="s">
         <v>194</v>
       </c>
       <c r="D160" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E160" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="F160">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B161" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C161" t="s">
         <v>195</v>
       </c>
       <c r="D161" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E161" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F161">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B162" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C162" t="s">
         <v>196</v>
       </c>
       <c r="D162" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="E162" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F162">
-        <v>33</v>
+        <v>141</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B163" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C163" t="s">
         <v>197</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E163" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F163">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B164" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C164" t="s">
         <v>198</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E164" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F164">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B165" t="s">
         <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B166" t="s">
         <v>7</v>
       </c>
       <c r="C166" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E166" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F166">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D167" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F167">
-        <v>18</v>
+        <v>75</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B168" t="s">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D168" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E168" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="F168">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B169" t="s">
         <v>7</v>
       </c>
       <c r="C169" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D169" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E169" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="F169">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D170" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="E170" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F170">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B171" t="s">
         <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D171" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="E171" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F171">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B172" t="s">
         <v>7</v>
       </c>
       <c r="C172" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D172" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E172" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F172">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D173" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E173" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F173">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B174" t="s">
         <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D174" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="E174" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F174">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B175" t="s">
         <v>7</v>
       </c>
       <c r="C175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D175" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E175" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F175">
-        <v>11</v>
+        <v>80</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
       </c>
       <c r="C176" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D176" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E176" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F176">
-        <v>55</v>
+        <v>80</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B177" t="s">
         <v>7</v>
       </c>
       <c r="C177" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D177" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E177" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F177">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B178" t="s">
         <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D178" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E178" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F178">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D179" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E179" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D180" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="E180" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="F180">
-        <v>87</v>
+        <v>25</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D181" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E181" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="F181">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D182" t="s">
-        <v>239</v>
+        <v>32</v>
       </c>
       <c r="E182" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F182">
-        <v>139</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B183" t="s">
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D183" t="s">
-        <v>240</v>
+        <v>32</v>
       </c>
       <c r="E183" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F183">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B184" t="s">
         <v>7</v>
       </c>
       <c r="C184" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D184" t="s">
-        <v>239</v>
+        <v>37</v>
       </c>
       <c r="E184" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F184">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B185" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C185" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D185" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E185" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F185">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B186" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D186" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E186" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F186">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B187" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C187" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D187" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E187" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F187">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B188" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D188" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F188">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B189" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C189" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D189" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E189" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F189">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B190" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D190" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E190" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F190">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B191" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C191" t="s">
-        <v>39</v>
+        <v>226</v>
       </c>
       <c r="D191" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E191" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F191">
-        <v>98</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B192" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C192" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D192" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E192" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F192">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B193" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C193" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D193" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E193" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F193">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E194" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F194">
-        <v>3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B195" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D195" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E195" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F195">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B196" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D196" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E196" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F196">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B197" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C197" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D197" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="E197" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F197">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B198" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C198" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D198" t="s">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="E198" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="F198">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D199" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E199" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F199">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D200" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E200" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F200">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C201" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D201" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E201" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F201">
-        <v>18</v>
+        <v>300</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B202" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D202" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="E202" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F202">
-        <v>17</v>
+        <v>100</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B203" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D203" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="E203" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="F203">
-        <v>4</v>
+        <v>75</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B204" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D204" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="E204" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="F204">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B205" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C205" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="D205" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E205" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="F205">
-        <v>6</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B206" t="s">
+        <v>55</v>
+      </c>
+      <c r="C206" t="s">
+        <v>240</v>
+      </c>
+      <c r="D206" t="s">
+        <v>67</v>
+      </c>
+      <c r="E206" t="s">
+        <v>65</v>
+      </c>
+      <c r="F206">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>199</v>
+      </c>
+      <c r="B207" t="s">
+        <v>55</v>
+      </c>
+      <c r="C207" t="s">
+        <v>241</v>
+      </c>
+      <c r="D207" t="s">
+        <v>23</v>
+      </c>
+      <c r="E207" t="s">
+        <v>23</v>
+      </c>
+      <c r="F207">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>199</v>
+      </c>
+      <c r="B208" t="s">
+        <v>55</v>
+      </c>
+      <c r="C208" t="s">
+        <v>242</v>
+      </c>
+      <c r="D208" t="s">
+        <v>23</v>
+      </c>
+      <c r="E208" t="s">
+        <v>23</v>
+      </c>
+      <c r="F208">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>199</v>
+      </c>
+      <c r="B209" t="s">
+        <v>55</v>
+      </c>
+      <c r="C209" t="s">
+        <v>243</v>
+      </c>
+      <c r="D209" t="s">
+        <v>32</v>
+      </c>
+      <c r="E209" t="s">
+        <v>32</v>
+      </c>
+      <c r="F209">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>199</v>
+      </c>
+      <c r="B210" t="s">
+        <v>55</v>
+      </c>
+      <c r="C210" t="s">
+        <v>244</v>
+      </c>
+      <c r="D210" t="s">
+        <v>32</v>
+      </c>
+      <c r="E210" t="s">
+        <v>32</v>
+      </c>
+      <c r="F210">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>199</v>
+      </c>
+      <c r="B211" t="s">
+        <v>55</v>
+      </c>
+      <c r="C211" t="s">
+        <v>245</v>
+      </c>
+      <c r="D211" t="s">
+        <v>73</v>
+      </c>
+      <c r="E211" t="s">
+        <v>73</v>
+      </c>
+      <c r="F211">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>199</v>
+      </c>
+      <c r="B212" t="s">
+        <v>55</v>
+      </c>
+      <c r="C212" t="s">
+        <v>246</v>
+      </c>
+      <c r="D212" t="s">
+        <v>75</v>
+      </c>
+      <c r="E212" t="s">
+        <v>75</v>
+      </c>
+      <c r="F212">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>199</v>
+      </c>
+      <c r="B213" t="s">
+        <v>55</v>
+      </c>
+      <c r="C213" t="s">
+        <v>247</v>
+      </c>
+      <c r="D213" t="s">
+        <v>78</v>
+      </c>
+      <c r="E213" t="s">
+        <v>78</v>
+      </c>
+      <c r="F213">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>199</v>
+      </c>
+      <c r="B214" t="s">
+        <v>55</v>
+      </c>
+      <c r="C214" t="s">
+        <v>248</v>
+      </c>
+      <c r="D214" t="s">
+        <v>78</v>
+      </c>
+      <c r="E214" t="s">
+        <v>78</v>
+      </c>
+      <c r="F214">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>199</v>
+      </c>
+      <c r="B215" t="s">
+        <v>55</v>
+      </c>
+      <c r="C215" t="s">
+        <v>249</v>
+      </c>
+      <c r="D215" t="s">
+        <v>133</v>
+      </c>
+      <c r="E215" t="s">
+        <v>133</v>
+      </c>
+      <c r="F215">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>199</v>
+      </c>
+      <c r="B216" t="s">
+        <v>55</v>
+      </c>
+      <c r="C216" t="s">
+        <v>250</v>
+      </c>
+      <c r="D216" t="s">
+        <v>133</v>
+      </c>
+      <c r="E216" t="s">
+        <v>133</v>
+      </c>
+      <c r="F216">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>199</v>
+      </c>
+      <c r="B217" t="s">
+        <v>55</v>
+      </c>
+      <c r="C217" t="s">
+        <v>251</v>
+      </c>
+      <c r="D217" t="s">
+        <v>37</v>
+      </c>
+      <c r="E217" t="s">
+        <v>37</v>
+      </c>
+      <c r="F217">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>199</v>
+      </c>
+      <c r="B218" t="s">
+        <v>55</v>
+      </c>
+      <c r="C218" t="s">
+        <v>252</v>
+      </c>
+      <c r="D218" t="s">
+        <v>37</v>
+      </c>
+      <c r="E218" t="s">
+        <v>37</v>
+      </c>
+      <c r="F218">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>199</v>
+      </c>
+      <c r="B219" t="s">
+        <v>55</v>
+      </c>
+      <c r="C219" t="s">
+        <v>253</v>
+      </c>
+      <c r="D219" t="s">
+        <v>41</v>
+      </c>
+      <c r="E219" t="s">
+        <v>41</v>
+      </c>
+      <c r="F219">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>199</v>
+      </c>
+      <c r="B220" t="s">
+        <v>55</v>
+      </c>
+      <c r="C220" t="s">
+        <v>254</v>
+      </c>
+      <c r="D220" t="s">
+        <v>41</v>
+      </c>
+      <c r="E220" t="s">
+        <v>41</v>
+      </c>
+      <c r="F220">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>255</v>
+      </c>
+      <c r="B221" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" t="s">
+        <v>256</v>
+      </c>
+      <c r="D221" t="s">
+        <v>12</v>
+      </c>
+      <c r="E221" t="s">
+        <v>10</v>
+      </c>
+      <c r="F221">
         <v>33</v>
       </c>
-      <c r="C206" t="s">
-        <v>238</v>
-      </c>
-      <c r="D206" t="s">
-        <v>26</v>
-      </c>
-      <c r="E206" t="s">
-        <v>26</v>
-      </c>
-      <c r="F206">
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>255</v>
+      </c>
+      <c r="B222" t="s">
+        <v>7</v>
+      </c>
+      <c r="C222" t="s">
+        <v>257</v>
+      </c>
+      <c r="D222" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" t="s">
+        <v>10</v>
+      </c>
+      <c r="F222">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>255</v>
+      </c>
+      <c r="B223" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" t="s">
+        <v>258</v>
+      </c>
+      <c r="D223" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" t="s">
+        <v>10</v>
+      </c>
+      <c r="F223">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>255</v>
+      </c>
+      <c r="B224" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" t="s">
+        <v>259</v>
+      </c>
+      <c r="D224" t="s">
+        <v>15</v>
+      </c>
+      <c r="E224" t="s">
+        <v>10</v>
+      </c>
+      <c r="F224">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>255</v>
+      </c>
+      <c r="B225" t="s">
+        <v>7</v>
+      </c>
+      <c r="C225" t="s">
+        <v>260</v>
+      </c>
+      <c r="D225" t="s">
+        <v>15</v>
+      </c>
+      <c r="E225" t="s">
+        <v>10</v>
+      </c>
+      <c r="F225">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>255</v>
+      </c>
+      <c r="B226" t="s">
+        <v>7</v>
+      </c>
+      <c r="C226" t="s">
+        <v>261</v>
+      </c>
+      <c r="D226" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226" t="s">
+        <v>18</v>
+      </c>
+      <c r="F226">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>255</v>
+      </c>
+      <c r="B227" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" t="s">
+        <v>262</v>
+      </c>
+      <c r="D227" t="s">
+        <v>89</v>
+      </c>
+      <c r="E227" t="s">
+        <v>18</v>
+      </c>
+      <c r="F227">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>255</v>
+      </c>
+      <c r="B228" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" t="s">
+        <v>263</v>
+      </c>
+      <c r="D228" t="s">
+        <v>89</v>
+      </c>
+      <c r="E228" t="s">
+        <v>18</v>
+      </c>
+      <c r="F228">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>255</v>
+      </c>
+      <c r="B229" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" t="s">
+        <v>264</v>
+      </c>
+      <c r="D229" t="s">
+        <v>23</v>
+      </c>
+      <c r="E229" t="s">
+        <v>23</v>
+      </c>
+      <c r="F229">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>255</v>
+      </c>
+      <c r="B230" t="s">
+        <v>7</v>
+      </c>
+      <c r="C230" t="s">
+        <v>265</v>
+      </c>
+      <c r="D230" t="s">
+        <v>23</v>
+      </c>
+      <c r="E230" t="s">
+        <v>23</v>
+      </c>
+      <c r="F230">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>255</v>
+      </c>
+      <c r="B231" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" t="s">
+        <v>266</v>
+      </c>
+      <c r="D231" t="s">
+        <v>23</v>
+      </c>
+      <c r="E231" t="s">
+        <v>23</v>
+      </c>
+      <c r="F231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>255</v>
+      </c>
+      <c r="B232" t="s">
+        <v>7</v>
+      </c>
+      <c r="C232" t="s">
+        <v>267</v>
+      </c>
+      <c r="D232" t="s">
+        <v>23</v>
+      </c>
+      <c r="E232" t="s">
+        <v>23</v>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>255</v>
+      </c>
+      <c r="B233" t="s">
+        <v>7</v>
+      </c>
+      <c r="C233" t="s">
+        <v>268</v>
+      </c>
+      <c r="D233" t="s">
+        <v>156</v>
+      </c>
+      <c r="E233" t="s">
+        <v>29</v>
+      </c>
+      <c r="F233">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>255</v>
+      </c>
+      <c r="B234" t="s">
+        <v>7</v>
+      </c>
+      <c r="C234" t="s">
+        <v>269</v>
+      </c>
+      <c r="D234" t="s">
+        <v>29</v>
+      </c>
+      <c r="E234" t="s">
+        <v>29</v>
+      </c>
+      <c r="F234">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>255</v>
+      </c>
+      <c r="B235" t="s">
+        <v>7</v>
+      </c>
+      <c r="C235" t="s">
+        <v>270</v>
+      </c>
+      <c r="D235" t="s">
+        <v>32</v>
+      </c>
+      <c r="E235" t="s">
+        <v>32</v>
+      </c>
+      <c r="F235">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>255</v>
+      </c>
+      <c r="B236" t="s">
+        <v>7</v>
+      </c>
+      <c r="C236" t="s">
+        <v>271</v>
+      </c>
+      <c r="D236" t="s">
+        <v>32</v>
+      </c>
+      <c r="E236" t="s">
+        <v>32</v>
+      </c>
+      <c r="F236">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>255</v>
+      </c>
+      <c r="B237" t="s">
+        <v>7</v>
+      </c>
+      <c r="C237" t="s">
+        <v>272</v>
+      </c>
+      <c r="D237" t="s">
+        <v>32</v>
+      </c>
+      <c r="E237" t="s">
+        <v>32</v>
+      </c>
+      <c r="F237">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>255</v>
+      </c>
+      <c r="B238" t="s">
+        <v>7</v>
+      </c>
+      <c r="C238" t="s">
+        <v>273</v>
+      </c>
+      <c r="D238" t="s">
+        <v>32</v>
+      </c>
+      <c r="E238" t="s">
+        <v>32</v>
+      </c>
+      <c r="F238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>255</v>
+      </c>
+      <c r="B239" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" t="s">
+        <v>274</v>
+      </c>
+      <c r="D239" t="s">
+        <v>37</v>
+      </c>
+      <c r="E239" t="s">
+        <v>37</v>
+      </c>
+      <c r="F239">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>255</v>
+      </c>
+      <c r="B240" t="s">
+        <v>7</v>
+      </c>
+      <c r="C240" t="s">
+        <v>275</v>
+      </c>
+      <c r="D240" t="s">
+        <v>37</v>
+      </c>
+      <c r="E240" t="s">
+        <v>37</v>
+      </c>
+      <c r="F240">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>255</v>
+      </c>
+      <c r="B241" t="s">
+        <v>7</v>
+      </c>
+      <c r="C241" t="s">
+        <v>276</v>
+      </c>
+      <c r="D241" t="s">
+        <v>37</v>
+      </c>
+      <c r="E241" t="s">
+        <v>37</v>
+      </c>
+      <c r="F241">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>255</v>
+      </c>
+      <c r="B242" t="s">
+        <v>7</v>
+      </c>
+      <c r="C242" t="s">
+        <v>277</v>
+      </c>
+      <c r="D242" t="s">
+        <v>37</v>
+      </c>
+      <c r="E242" t="s">
+        <v>37</v>
+      </c>
+      <c r="F242">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>255</v>
+      </c>
+      <c r="B243" t="s">
+        <v>7</v>
+      </c>
+      <c r="C243" t="s">
+        <v>278</v>
+      </c>
+      <c r="D243" t="s">
+        <v>41</v>
+      </c>
+      <c r="E243" t="s">
+        <v>41</v>
+      </c>
+      <c r="F243">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>255</v>
+      </c>
+      <c r="B244" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" t="s">
+        <v>279</v>
+      </c>
+      <c r="D244" t="s">
+        <v>41</v>
+      </c>
+      <c r="E244" t="s">
+        <v>41</v>
+      </c>
+      <c r="F244">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>255</v>
+      </c>
+      <c r="B245" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" t="s">
+        <v>280</v>
+      </c>
+      <c r="D245" t="s">
+        <v>41</v>
+      </c>
+      <c r="E245" t="s">
+        <v>41</v>
+      </c>
+      <c r="F245">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>255</v>
+      </c>
+      <c r="B246" t="s">
+        <v>7</v>
+      </c>
+      <c r="C246" t="s">
+        <v>281</v>
+      </c>
+      <c r="D246" t="s">
+        <v>41</v>
+      </c>
+      <c r="E246" t="s">
+        <v>41</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>255</v>
+      </c>
+      <c r="B247" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" t="s">
+        <v>282</v>
+      </c>
+      <c r="D247" t="s">
+        <v>46</v>
+      </c>
+      <c r="E247" t="s">
+        <v>46</v>
+      </c>
+      <c r="F247">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>255</v>
+      </c>
+      <c r="B248" t="s">
+        <v>7</v>
+      </c>
+      <c r="C248" t="s">
+        <v>283</v>
+      </c>
+      <c r="D248" t="s">
+        <v>46</v>
+      </c>
+      <c r="E248" t="s">
+        <v>46</v>
+      </c>
+      <c r="F248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>255</v>
+      </c>
+      <c r="B249" t="s">
+        <v>7</v>
+      </c>
+      <c r="C249" t="s">
+        <v>284</v>
+      </c>
+      <c r="D249" t="s">
+        <v>46</v>
+      </c>
+      <c r="E249" t="s">
+        <v>46</v>
+      </c>
+      <c r="F249">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>255</v>
+      </c>
+      <c r="B250" t="s">
+        <v>7</v>
+      </c>
+      <c r="C250" t="s">
+        <v>285</v>
+      </c>
+      <c r="D250" t="s">
+        <v>50</v>
+      </c>
+      <c r="E250" t="s">
+        <v>51</v>
+      </c>
+      <c r="F250">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>255</v>
+      </c>
+      <c r="B251" t="s">
+        <v>7</v>
+      </c>
+      <c r="C251" t="s">
+        <v>286</v>
+      </c>
+      <c r="D251" t="s">
+        <v>53</v>
+      </c>
+      <c r="E251" t="s">
+        <v>51</v>
+      </c>
+      <c r="F251">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" t="s">
+        <v>7</v>
+      </c>
+      <c r="C252" t="s">
+        <v>287</v>
+      </c>
+      <c r="D252" t="s">
+        <v>50</v>
+      </c>
+      <c r="E252" t="s">
+        <v>51</v>
+      </c>
+      <c r="F252">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>255</v>
+      </c>
+      <c r="B253" t="s">
+        <v>55</v>
+      </c>
+      <c r="C253" t="s">
+        <v>288</v>
+      </c>
+      <c r="D253" t="s">
+        <v>15</v>
+      </c>
+      <c r="E253" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>255</v>
+      </c>
+      <c r="B254" t="s">
+        <v>55</v>
+      </c>
+      <c r="C254" t="s">
+        <v>289</v>
+      </c>
+      <c r="D254" t="s">
+        <v>15</v>
+      </c>
+      <c r="E254" t="s">
+        <v>10</v>
+      </c>
+      <c r="F254">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>255</v>
+      </c>
+      <c r="B255" t="s">
+        <v>55</v>
+      </c>
+      <c r="C255" t="s">
+        <v>290</v>
+      </c>
+      <c r="D255" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255" t="s">
+        <v>10</v>
+      </c>
+      <c r="F255">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>55</v>
+      </c>
+      <c r="C256" t="s">
+        <v>291</v>
+      </c>
+      <c r="D256" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256" t="s">
+        <v>10</v>
+      </c>
+      <c r="F256">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>255</v>
+      </c>
+      <c r="B257" t="s">
+        <v>55</v>
+      </c>
+      <c r="C257" t="s">
+        <v>292</v>
+      </c>
+      <c r="D257" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257" t="s">
+        <v>18</v>
+      </c>
+      <c r="F257">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>255</v>
+      </c>
+      <c r="B258" t="s">
+        <v>55</v>
+      </c>
+      <c r="C258" t="s">
+        <v>293</v>
+      </c>
+      <c r="D258" t="s">
+        <v>89</v>
+      </c>
+      <c r="E258" t="s">
+        <v>18</v>
+      </c>
+      <c r="F258">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>255</v>
+      </c>
+      <c r="B259" t="s">
+        <v>55</v>
+      </c>
+      <c r="C259" t="s">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>64</v>
+      </c>
+      <c r="E259" t="s">
+        <v>65</v>
+      </c>
+      <c r="F259">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>255</v>
+      </c>
+      <c r="B260" t="s">
+        <v>55</v>
+      </c>
+      <c r="C260" t="s">
+        <v>294</v>
+      </c>
+      <c r="D260" t="s">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>65</v>
+      </c>
+      <c r="F260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>255</v>
+      </c>
+      <c r="B261" t="s">
+        <v>55</v>
+      </c>
+      <c r="C261" t="s">
+        <v>295</v>
+      </c>
+      <c r="D261" t="s">
+        <v>23</v>
+      </c>
+      <c r="E261" t="s">
+        <v>23</v>
+      </c>
+      <c r="F261">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>255</v>
+      </c>
+      <c r="B262" t="s">
+        <v>55</v>
+      </c>
+      <c r="C262" t="s">
+        <v>296</v>
+      </c>
+      <c r="D262" t="s">
+        <v>23</v>
+      </c>
+      <c r="E262" t="s">
+        <v>23</v>
+      </c>
+      <c r="F262">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>255</v>
+      </c>
+      <c r="B263" t="s">
+        <v>55</v>
+      </c>
+      <c r="C263" t="s">
+        <v>297</v>
+      </c>
+      <c r="D263" t="s">
+        <v>32</v>
+      </c>
+      <c r="E263" t="s">
+        <v>32</v>
+      </c>
+      <c r="F263">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>255</v>
+      </c>
+      <c r="B264" t="s">
+        <v>55</v>
+      </c>
+      <c r="C264" t="s">
+        <v>298</v>
+      </c>
+      <c r="D264" t="s">
+        <v>32</v>
+      </c>
+      <c r="E264" t="s">
+        <v>32</v>
+      </c>
+      <c r="F264">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>255</v>
+      </c>
+      <c r="B265" t="s">
+        <v>55</v>
+      </c>
+      <c r="C265" t="s">
+        <v>299</v>
+      </c>
+      <c r="D265" t="s">
+        <v>73</v>
+      </c>
+      <c r="E265" t="s">
+        <v>73</v>
+      </c>
+      <c r="F265">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>255</v>
+      </c>
+      <c r="B266" t="s">
+        <v>55</v>
+      </c>
+      <c r="C266" t="s">
+        <v>300</v>
+      </c>
+      <c r="D266" t="s">
+        <v>128</v>
+      </c>
+      <c r="E266" t="s">
+        <v>128</v>
+      </c>
+      <c r="F266">
         <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>255</v>
+      </c>
+      <c r="B267" t="s">
+        <v>55</v>
+      </c>
+      <c r="C267" t="s">
+        <v>301</v>
+      </c>
+      <c r="D267" t="s">
+        <v>75</v>
+      </c>
+      <c r="E267" t="s">
+        <v>75</v>
+      </c>
+      <c r="F267">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>255</v>
+      </c>
+      <c r="B268" t="s">
+        <v>55</v>
+      </c>
+      <c r="C268" t="s">
+        <v>302</v>
+      </c>
+      <c r="D268" t="s">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>75</v>
+      </c>
+      <c r="F268">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>255</v>
+      </c>
+      <c r="B269" t="s">
+        <v>55</v>
+      </c>
+      <c r="C269" t="s">
+        <v>303</v>
+      </c>
+      <c r="D269" t="s">
+        <v>78</v>
+      </c>
+      <c r="E269" t="s">
+        <v>78</v>
+      </c>
+      <c r="F269">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>255</v>
+      </c>
+      <c r="B270" t="s">
+        <v>55</v>
+      </c>
+      <c r="C270" t="s">
+        <v>304</v>
+      </c>
+      <c r="D270" t="s">
+        <v>78</v>
+      </c>
+      <c r="E270" t="s">
+        <v>78</v>
+      </c>
+      <c r="F270">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>255</v>
+      </c>
+      <c r="B271" t="s">
+        <v>55</v>
+      </c>
+      <c r="C271" t="s">
+        <v>301</v>
+      </c>
+      <c r="D271" t="s">
+        <v>133</v>
+      </c>
+      <c r="E271" t="s">
+        <v>133</v>
+      </c>
+      <c r="F271">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>255</v>
+      </c>
+      <c r="B272" t="s">
+        <v>55</v>
+      </c>
+      <c r="C272" t="s">
+        <v>305</v>
+      </c>
+      <c r="D272" t="s">
+        <v>133</v>
+      </c>
+      <c r="E272" t="s">
+        <v>133</v>
+      </c>
+      <c r="F272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>255</v>
+      </c>
+      <c r="B273" t="s">
+        <v>55</v>
+      </c>
+      <c r="C273" t="s">
+        <v>306</v>
+      </c>
+      <c r="D273" t="s">
+        <v>37</v>
+      </c>
+      <c r="E273" t="s">
+        <v>37</v>
+      </c>
+      <c r="F273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>255</v>
+      </c>
+      <c r="B274" t="s">
+        <v>55</v>
+      </c>
+      <c r="C274" t="s">
+        <v>307</v>
+      </c>
+      <c r="D274" t="s">
+        <v>37</v>
+      </c>
+      <c r="E274" t="s">
+        <v>37</v>
+      </c>
+      <c r="F274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>255</v>
+      </c>
+      <c r="B275" t="s">
+        <v>55</v>
+      </c>
+      <c r="C275" t="s">
+        <v>308</v>
+      </c>
+      <c r="D275" t="s">
+        <v>41</v>
+      </c>
+      <c r="E275" t="s">
+        <v>41</v>
+      </c>
+      <c r="F275">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>255</v>
+      </c>
+      <c r="B276" t="s">
+        <v>55</v>
+      </c>
+      <c r="C276" t="s">
+        <v>309</v>
+      </c>
+      <c r="D276" t="s">
+        <v>41</v>
+      </c>
+      <c r="E276" t="s">
+        <v>41</v>
+      </c>
+      <c r="F276">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>255</v>
+      </c>
+      <c r="B277" t="s">
+        <v>55</v>
+      </c>
+      <c r="C277" t="s">
+        <v>310</v>
+      </c>
+      <c r="D277" t="s">
+        <v>311</v>
+      </c>
+      <c r="E277" t="s">
+        <v>10</v>
+      </c>
+      <c r="F277">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>255</v>
+      </c>
+      <c r="B278" t="s">
+        <v>7</v>
+      </c>
+      <c r="C278" t="s">
+        <v>312</v>
+      </c>
+      <c r="D278" t="s">
+        <v>311</v>
+      </c>
+      <c r="E278" t="s">
+        <v>10</v>
+      </c>
+      <c r="F278">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36A4EB-306D-4438-B779-2EEBEF9F087D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F73CD7FE-0378-7A43-835C-99DB99685A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="313">
   <si>
     <t>Manager</t>
   </si>
@@ -963,9 +963,6 @@
   </si>
   <si>
     <t>San Jose Sharks</t>
-  </si>
-  <si>
-    <t>Washington Spirit</t>
   </si>
   <si>
     <t>NWSL</t>
@@ -1305,10 +1302,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F278"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F277"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1328,7 +1325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1348,7 +1345,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1368,7 +1365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1388,7 +1385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1408,7 +1405,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1428,7 +1425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1448,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1468,7 +1465,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1488,7 +1485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1508,7 +1505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1528,7 +1525,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1548,7 +1545,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1568,7 +1565,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1588,7 +1585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1608,7 +1605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1628,7 +1625,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1648,7 +1645,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1668,7 +1665,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1688,7 +1685,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1708,7 +1705,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1728,7 +1725,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1748,7 +1745,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1768,7 +1765,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1788,7 +1785,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1808,7 +1805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1828,7 +1825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1848,7 +1845,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1868,7 +1865,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1888,7 +1885,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1908,7 +1905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1928,7 +1925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1948,7 +1945,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1968,7 +1965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1988,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2008,7 +2005,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2028,7 +2025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -2048,7 +2045,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2068,7 +2065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2088,7 +2085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2108,7 +2105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2128,7 +2125,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2148,7 +2145,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2168,7 +2165,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2188,7 +2185,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2208,7 +2205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2228,7 +2225,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2248,7 +2245,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2268,7 +2265,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2288,7 +2285,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2308,7 +2305,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2328,7 +2325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2348,7 +2345,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>83</v>
       </c>
@@ -2368,7 +2365,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -2388,7 +2385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2408,7 +2405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -2428,7 +2425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -2448,7 +2445,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -2468,7 +2465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -2488,7 +2485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -2508,7 +2505,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -2528,7 +2525,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -2548,7 +2545,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -2568,7 +2565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -2588,7 +2585,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -2608,7 +2605,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -2628,7 +2625,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -2648,7 +2645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -2668,7 +2665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -2688,7 +2685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2708,7 +2705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2728,7 +2725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2748,7 +2745,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2768,7 +2765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2788,7 +2785,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2808,7 +2805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2828,7 +2825,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2848,7 +2845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2868,7 +2865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2888,7 +2885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2908,7 +2905,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2928,7 +2925,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2948,7 +2945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2968,7 +2965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2988,7 +2985,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -3008,7 +3005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -3028,7 +3025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3048,7 +3045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -3068,7 +3065,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -3088,7 +3085,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3108,7 +3105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3128,7 +3125,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3148,7 +3145,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3168,7 +3165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3188,7 +3185,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3208,7 +3205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3228,7 +3225,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3248,7 +3245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3268,7 +3265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3288,7 +3285,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3308,7 +3305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3328,7 +3325,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3348,7 +3345,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3368,7 +3365,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3388,7 +3385,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3408,7 +3405,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>139</v>
       </c>
@@ -3428,7 +3425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>139</v>
       </c>
@@ -3448,7 +3445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>139</v>
       </c>
@@ -3468,7 +3465,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>139</v>
       </c>
@@ -3488,7 +3485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>139</v>
       </c>
@@ -3508,7 +3505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3528,7 +3525,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -3548,7 +3545,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -3568,7 +3565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>139</v>
       </c>
@@ -3588,7 +3585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>139</v>
       </c>
@@ -3608,7 +3605,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>139</v>
       </c>
@@ -3628,7 +3625,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>139</v>
       </c>
@@ -3648,7 +3645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>139</v>
       </c>
@@ -3668,7 +3665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -3688,7 +3685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>139</v>
       </c>
@@ -3708,7 +3705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>139</v>
       </c>
@@ -3728,7 +3725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>139</v>
       </c>
@@ -3748,7 +3745,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>139</v>
       </c>
@@ -3768,7 +3765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>139</v>
       </c>
@@ -3788,7 +3785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -3808,7 +3805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>139</v>
       </c>
@@ -3828,7 +3825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>139</v>
       </c>
@@ -3848,7 +3845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -3868,7 +3865,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -3888,7 +3885,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>139</v>
       </c>
@@ -3908,7 +3905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -3928,7 +3925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -3948,7 +3945,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>139</v>
       </c>
@@ -3968,7 +3965,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -3988,7 +3985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -4008,7 +4005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -4028,7 +4025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -4048,7 +4045,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>139</v>
       </c>
@@ -4068,7 +4065,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -4088,7 +4085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -4108,7 +4105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -4128,7 +4125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>139</v>
       </c>
@@ -4148,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>139</v>
       </c>
@@ -4168,7 +4165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>139</v>
       </c>
@@ -4188,7 +4185,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -4208,7 +4205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>139</v>
       </c>
@@ -4228,7 +4225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>139</v>
       </c>
@@ -4248,7 +4245,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>139</v>
       </c>
@@ -4268,7 +4265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>139</v>
       </c>
@@ -4288,7 +4285,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>139</v>
       </c>
@@ -4308,7 +4305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>139</v>
       </c>
@@ -4328,7 +4325,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>139</v>
       </c>
@@ -4348,7 +4345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>139</v>
       </c>
@@ -4368,7 +4365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>139</v>
       </c>
@@ -4388,7 +4385,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>139</v>
       </c>
@@ -4408,7 +4405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>139</v>
       </c>
@@ -4428,7 +4425,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>139</v>
       </c>
@@ -4448,7 +4445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>139</v>
       </c>
@@ -4468,7 +4465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>139</v>
       </c>
@@ -4488,7 +4485,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>139</v>
       </c>
@@ -4508,7 +4505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>139</v>
       </c>
@@ -4528,7 +4525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -4548,7 +4545,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>139</v>
       </c>
@@ -4568,7 +4565,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>139</v>
       </c>
@@ -4588,7 +4585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>199</v>
       </c>
@@ -4608,7 +4605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4628,7 +4625,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>199</v>
       </c>
@@ -4648,7 +4645,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>199</v>
       </c>
@@ -4668,7 +4665,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>199</v>
       </c>
@@ -4688,7 +4685,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>199</v>
       </c>
@@ -4708,7 +4705,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>199</v>
       </c>
@@ -4728,7 +4725,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -4748,7 +4745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>199</v>
       </c>
@@ -4768,7 +4765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>199</v>
       </c>
@@ -4788,7 +4785,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>199</v>
       </c>
@@ -4808,7 +4805,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>199</v>
       </c>
@@ -4828,7 +4825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>199</v>
       </c>
@@ -4848,7 +4845,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>199</v>
       </c>
@@ -4868,7 +4865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>199</v>
       </c>
@@ -4888,7 +4885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>199</v>
       </c>
@@ -4908,7 +4905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>199</v>
       </c>
@@ -4928,7 +4925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>199</v>
       </c>
@@ -4948,7 +4945,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>199</v>
       </c>
@@ -4968,7 +4965,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>199</v>
       </c>
@@ -4988,7 +4985,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>199</v>
       </c>
@@ -5008,7 +5005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>199</v>
       </c>
@@ -5028,7 +5025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>199</v>
       </c>
@@ -5048,7 +5045,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>199</v>
       </c>
@@ -5068,7 +5065,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -5088,7 +5085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>199</v>
       </c>
@@ -5108,7 +5105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>199</v>
       </c>
@@ -5128,7 +5125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -5148,7 +5145,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>199</v>
       </c>
@@ -5168,7 +5165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -5188,7 +5185,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -5208,7 +5205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -5228,7 +5225,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -5248,7 +5245,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>199</v>
       </c>
@@ -5268,7 +5265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>199</v>
       </c>
@@ -5288,7 +5285,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -5308,7 +5305,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5328,7 +5325,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>199</v>
       </c>
@@ -5348,7 +5345,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>199</v>
       </c>
@@ -5368,7 +5365,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>199</v>
       </c>
@@ -5388,7 +5385,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>199</v>
       </c>
@@ -5408,7 +5405,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>199</v>
       </c>
@@ -5428,7 +5425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>199</v>
       </c>
@@ -5448,7 +5445,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>199</v>
       </c>
@@ -5468,7 +5465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>199</v>
       </c>
@@ -5488,7 +5485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>199</v>
       </c>
@@ -5508,7 +5505,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>199</v>
       </c>
@@ -5528,7 +5525,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>199</v>
       </c>
@@ -5548,7 +5545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>199</v>
       </c>
@@ -5568,7 +5565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -5588,7 +5585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>199</v>
       </c>
@@ -5608,7 +5605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>199</v>
       </c>
@@ -5628,7 +5625,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>199</v>
       </c>
@@ -5648,7 +5645,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>199</v>
       </c>
@@ -5668,7 +5665,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>199</v>
       </c>
@@ -5688,7 +5685,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>199</v>
       </c>
@@ -5708,7 +5705,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>255</v>
       </c>
@@ -5728,7 +5725,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>255</v>
       </c>
@@ -5748,7 +5745,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>255</v>
       </c>
@@ -5768,7 +5765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>255</v>
       </c>
@@ -5788,7 +5785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>255</v>
       </c>
@@ -5808,7 +5805,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>255</v>
       </c>
@@ -5828,7 +5825,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>255</v>
       </c>
@@ -5848,7 +5845,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>255</v>
       </c>
@@ -5868,7 +5865,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>255</v>
       </c>
@@ -5888,7 +5885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>255</v>
       </c>
@@ -5908,7 +5905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>255</v>
       </c>
@@ -5928,7 +5925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>255</v>
       </c>
@@ -5948,7 +5945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>255</v>
       </c>
@@ -5968,7 +5965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>255</v>
       </c>
@@ -5988,7 +5985,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>255</v>
       </c>
@@ -6008,7 +6005,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -6028,7 +6025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>255</v>
       </c>
@@ -6048,7 +6045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>255</v>
       </c>
@@ -6068,7 +6065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>255</v>
       </c>
@@ -6088,7 +6085,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>255</v>
       </c>
@@ -6108,7 +6105,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>255</v>
       </c>
@@ -6128,7 +6125,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>255</v>
       </c>
@@ -6148,7 +6145,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>255</v>
       </c>
@@ -6168,7 +6165,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>255</v>
       </c>
@@ -6188,7 +6185,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>255</v>
       </c>
@@ -6208,7 +6205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>255</v>
       </c>
@@ -6228,7 +6225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>255</v>
       </c>
@@ -6248,7 +6245,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>255</v>
       </c>
@@ -6268,7 +6265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>255</v>
       </c>
@@ -6288,7 +6285,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>255</v>
       </c>
@@ -6308,7 +6305,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -6328,7 +6325,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>255</v>
       </c>
@@ -6348,7 +6345,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -6368,7 +6365,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>255</v>
       </c>
@@ -6388,7 +6385,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>255</v>
       </c>
@@ -6408,7 +6405,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>255</v>
       </c>
@@ -6428,7 +6425,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -6448,7 +6445,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>255</v>
       </c>
@@ -6468,7 +6465,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>255</v>
       </c>
@@ -6488,7 +6485,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>255</v>
       </c>
@@ -6508,7 +6505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>255</v>
       </c>
@@ -6528,7 +6525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>255</v>
       </c>
@@ -6548,7 +6545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>255</v>
       </c>
@@ -6568,7 +6565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>255</v>
       </c>
@@ -6588,7 +6585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>255</v>
       </c>
@@ -6608,7 +6605,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>255</v>
       </c>
@@ -6628,7 +6625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>255</v>
       </c>
@@ -6648,7 +6645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>255</v>
       </c>
@@ -6668,7 +6665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>255</v>
       </c>
@@ -6688,7 +6685,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>255</v>
       </c>
@@ -6708,7 +6705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>255</v>
       </c>
@@ -6728,7 +6725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>255</v>
       </c>
@@ -6748,7 +6745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>255</v>
       </c>
@@ -6768,7 +6765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>255</v>
       </c>
@@ -6788,7 +6785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>255</v>
       </c>
@@ -6808,7 +6805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>255</v>
       </c>
@@ -6828,43 +6825,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>255</v>
       </c>
       <c r="B277" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C277" t="s">
+        <v>311</v>
+      </c>
+      <c r="D277" t="s">
         <v>310</v>
-      </c>
-      <c r="D277" t="s">
-        <v>311</v>
       </c>
       <c r="E277" t="s">
         <v>10</v>
       </c>
       <c r="F277">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A278" t="s">
-        <v>255</v>
-      </c>
-      <c r="B278" t="s">
-        <v>7</v>
-      </c>
-      <c r="C278" t="s">
-        <v>312</v>
-      </c>
-      <c r="D278" t="s">
-        <v>311</v>
-      </c>
-      <c r="E278" t="s">
-        <v>10</v>
-      </c>
-      <c r="F278">
         <v>125</v>
       </c>
     </row>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F73CD7FE-0378-7A43-835C-99DB99685A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B508820-DBB0-1247-9684-ACFDB70B1F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="313">
   <si>
     <t>Manager</t>
   </si>
@@ -969,6 +969,9 @@
   </si>
   <si>
     <t>Ashley Sanchez</t>
+  </si>
+  <si>
+    <t>Lens</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -6845,6 +6848,26 @@
         <v>125</v>
       </c>
     </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>139</v>
+      </c>
+      <c r="B278" t="s">
+        <v>55</v>
+      </c>
+      <c r="C278" t="s">
+        <v>312</v>
+      </c>
+      <c r="D278" t="s">
+        <v>12</v>
+      </c>
+      <c r="E278" t="s">
+        <v>10</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B508820-DBB0-1247-9684-ACFDB70B1F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A9CDC1D-6201-8C4E-8D28-CD186F4B7D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="313">
   <si>
     <t>Manager</t>
   </si>
@@ -963,12 +963,6 @@
   </si>
   <si>
     <t>San Jose Sharks</t>
-  </si>
-  <si>
-    <t>NWSL</t>
-  </si>
-  <si>
-    <t>Ashley Sanchez</t>
   </si>
   <si>
     <t>Lens</t>
@@ -1305,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -6830,41 +6824,21 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>255</v>
+        <v>139</v>
       </c>
       <c r="B277" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C277" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D277" t="s">
-        <v>310</v>
+        <v>12</v>
       </c>
       <c r="E277" t="s">
         <v>10</v>
       </c>
       <c r="F277">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
-        <v>139</v>
-      </c>
-      <c r="B278" t="s">
-        <v>55</v>
-      </c>
-      <c r="C278" t="s">
-        <v>312</v>
-      </c>
-      <c r="D278" t="s">
-        <v>12</v>
-      </c>
-      <c r="E278" t="s">
-        <v>10</v>
-      </c>
-      <c r="F278">
         <v>0</v>
       </c>
     </row>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A9CDC1D-6201-8C4E-8D28-CD186F4B7D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817F8B7E-3A67-4D61-98EE-14BDE52F779F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="311">
   <si>
     <t>Manager</t>
   </si>
@@ -1300,9 +1300,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F277"/>
-  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2022,9 +2022,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>255</v>
       </c>
       <c r="B37" t="s">
         <v>55</v>
@@ -2042,7 +2042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>83</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>139</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>139</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>139</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>139</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>139</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>139</v>
       </c>
@@ -3582,9 +3582,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
@@ -3602,7 +3602,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>139</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>139</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>139</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>139</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>139</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>139</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>139</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>139</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>139</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>139</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>139</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>139</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>139</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>139</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>139</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>139</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>139</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>139</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>139</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>139</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>139</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>139</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>139</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>139</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>139</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>139</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>139</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>139</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>139</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>139</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>139</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>139</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>139</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>139</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>199</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>199</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>199</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>199</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>199</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>199</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>199</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>199</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>199</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>199</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>199</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>199</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>199</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>199</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>199</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>199</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>199</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>199</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>199</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>199</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>199</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>199</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>199</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>199</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>199</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>199</v>
       </c>
@@ -5262,7 +5262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>199</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5322,7 +5322,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>199</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>199</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>199</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>199</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>199</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>199</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>199</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>199</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>199</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>199</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>199</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>199</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -5582,7 +5582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>199</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>199</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>199</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>199</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>199</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>199</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>255</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>255</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>255</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>255</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>255</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>255</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>255</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>255</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>255</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>255</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>255</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>255</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>255</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>255</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>255</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>255</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>255</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>255</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>255</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>255</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>255</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>255</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>255</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>255</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>255</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>255</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>255</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>255</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>255</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>255</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>255</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>255</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>255</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>255</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>255</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>255</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>255</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>255</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>255</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>255</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>255</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>255</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>255</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>255</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>255</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>255</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>255</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>255</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>255</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>255</v>
       </c>
@@ -6782,7 +6782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>255</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>255</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>139</v>
       </c>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817F8B7E-3A67-4D61-98EE-14BDE52F779F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A60FFFE-A0BA-4AC0-A514-61125E43F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="317">
   <si>
     <t>Manager</t>
   </si>
@@ -966,6 +966,24 @@
   </si>
   <si>
     <t>Lens</t>
+  </si>
+  <si>
+    <t>Miami Hurricanes</t>
+  </si>
+  <si>
+    <t>Scotty Barnes</t>
+  </si>
+  <si>
+    <t>Tommy Fleetwood</t>
+  </si>
+  <si>
+    <t>Joe Burrow</t>
+  </si>
+  <si>
+    <t>USC Trojans</t>
+  </si>
+  <si>
+    <t>Lille</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F285"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -6842,6 +6860,166 @@
         <v>0</v>
       </c>
     </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>199</v>
+      </c>
+      <c r="B278" t="s">
+        <v>55</v>
+      </c>
+      <c r="C278" t="s">
+        <v>311</v>
+      </c>
+      <c r="D278" t="s">
+        <v>75</v>
+      </c>
+      <c r="E278" t="s">
+        <v>75</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>199</v>
+      </c>
+      <c r="B279" t="s">
+        <v>7</v>
+      </c>
+      <c r="C279" t="s">
+        <v>312</v>
+      </c>
+      <c r="D279" t="s">
+        <v>32</v>
+      </c>
+      <c r="E279" t="s">
+        <v>32</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>199</v>
+      </c>
+      <c r="B280" t="s">
+        <v>7</v>
+      </c>
+      <c r="C280" t="s">
+        <v>313</v>
+      </c>
+      <c r="D280" t="s">
+        <v>46</v>
+      </c>
+      <c r="E280" t="s">
+        <v>46</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>6</v>
+      </c>
+      <c r="B281" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281" t="s">
+        <v>314</v>
+      </c>
+      <c r="D281" t="s">
+        <v>37</v>
+      </c>
+      <c r="E281" t="s">
+        <v>37</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>6</v>
+      </c>
+      <c r="B282" t="s">
+        <v>55</v>
+      </c>
+      <c r="C282" t="s">
+        <v>193</v>
+      </c>
+      <c r="D282" t="s">
+        <v>78</v>
+      </c>
+      <c r="E282" t="s">
+        <v>78</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>6</v>
+      </c>
+      <c r="B283" t="s">
+        <v>55</v>
+      </c>
+      <c r="C283" t="s">
+        <v>315</v>
+      </c>
+      <c r="D283" t="s">
+        <v>78</v>
+      </c>
+      <c r="E283" t="s">
+        <v>133</v>
+      </c>
+      <c r="F283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" t="s">
+        <v>55</v>
+      </c>
+      <c r="C284" t="s">
+        <v>248</v>
+      </c>
+      <c r="D284" t="s">
+        <v>78</v>
+      </c>
+      <c r="E284" t="s">
+        <v>133</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>6</v>
+      </c>
+      <c r="B285" t="s">
+        <v>55</v>
+      </c>
+      <c r="C285" t="s">
+        <v>316</v>
+      </c>
+      <c r="D285" t="s">
+        <v>12</v>
+      </c>
+      <c r="E285" t="s">
+        <v>10</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A60FFFE-A0BA-4AC0-A514-61125E43F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D636EAD-F4E2-4F14-A3D7-DABD33A0626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="328">
   <si>
     <t>Manager</t>
   </si>
@@ -425,9 +425,6 @@
     <t>Ohio State Buckeyes</t>
   </si>
   <si>
-    <t>Arkansas Razorbacks</t>
-  </si>
-  <si>
     <t>Nebraska Cornhuskers</t>
   </si>
   <si>
@@ -984,6 +981,42 @@
   </si>
   <si>
     <t>Lille</t>
+  </si>
+  <si>
+    <t>Si Woo Kim</t>
+  </si>
+  <si>
+    <t>Bam Adebayo</t>
+  </si>
+  <si>
+    <t>Mikal Bridges</t>
+  </si>
+  <si>
+    <t>Arda Güler</t>
+  </si>
+  <si>
+    <t>Club Soccer Top</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>Zavier Gozo</t>
+  </si>
+  <si>
+    <t>EPL</t>
+  </si>
+  <si>
+    <t>Joshua Kimmich</t>
+  </si>
+  <si>
+    <t>Ryan Blaney</t>
+  </si>
+  <si>
+    <t>Chase Elliott</t>
+  </si>
+  <si>
+    <t>Anders Dreyer</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F285"/>
+  <dimension ref="A1:F295"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -2042,7 +2075,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B37" t="s">
         <v>55</v>
@@ -3248,7 +3281,7 @@
         <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>130</v>
+        <v>244</v>
       </c>
       <c r="D97" t="s">
         <v>75</v>
@@ -3268,7 +3301,7 @@
         <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D98" t="s">
         <v>78</v>
@@ -3288,7 +3321,7 @@
         <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D99" t="s">
         <v>78</v>
@@ -3311,10 +3344,10 @@
         <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F100">
         <v>15</v>
@@ -3328,13 +3361,13 @@
         <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F101">
         <v>100</v>
@@ -3348,7 +3381,7 @@
         <v>55</v>
       </c>
       <c r="C102" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D102" t="s">
         <v>37</v>
@@ -3368,7 +3401,7 @@
         <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D103" t="s">
         <v>37</v>
@@ -3388,7 +3421,7 @@
         <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D104" t="s">
         <v>41</v>
@@ -3408,7 +3441,7 @@
         <v>55</v>
       </c>
       <c r="C105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
@@ -3422,13 +3455,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
+        <v>138</v>
+      </c>
+      <c r="B106" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" t="s">
         <v>139</v>
-      </c>
-      <c r="B106" t="s">
-        <v>7</v>
-      </c>
-      <c r="C106" t="s">
-        <v>140</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
@@ -3442,13 +3475,13 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D107" t="s">
         <v>12</v>
@@ -3462,13 +3495,13 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D108" t="s">
         <v>12</v>
@@ -3482,13 +3515,13 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B109" t="s">
         <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
@@ -3502,13 +3535,13 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
@@ -3522,13 +3555,13 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
         <v>17</v>
@@ -3542,13 +3575,13 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B112" t="s">
         <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D112" t="s">
         <v>89</v>
@@ -3562,13 +3595,13 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>89</v>
@@ -3582,13 +3615,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B114" t="s">
         <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D114" t="s">
         <v>17</v>
@@ -3602,13 +3635,13 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D115" t="s">
         <v>17</v>
@@ -3622,13 +3655,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -3642,13 +3675,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B117" t="s">
         <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D117" t="s">
         <v>23</v>
@@ -3662,13 +3695,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B118" t="s">
         <v>7</v>
       </c>
       <c r="C118" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D118" t="s">
         <v>23</v>
@@ -3682,13 +3715,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D119" t="s">
         <v>23</v>
@@ -3702,13 +3735,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B120" t="s">
         <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D120" t="s">
         <v>28</v>
@@ -3722,16 +3755,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
+        <v>154</v>
+      </c>
+      <c r="D121" t="s">
         <v>155</v>
-      </c>
-      <c r="D121" t="s">
-        <v>156</v>
       </c>
       <c r="E121" t="s">
         <v>29</v>
@@ -3742,13 +3775,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -3762,13 +3795,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B123" t="s">
         <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -3782,13 +3815,13 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -3802,13 +3835,13 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -3822,13 +3855,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B126" t="s">
         <v>7</v>
       </c>
       <c r="C126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D126" t="s">
         <v>37</v>
@@ -3842,13 +3875,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B127" t="s">
         <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D127" t="s">
         <v>37</v>
@@ -3862,13 +3895,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D128" t="s">
         <v>37</v>
@@ -3882,13 +3915,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B129" t="s">
         <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
         <v>37</v>
@@ -3902,13 +3935,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B130" t="s">
         <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D130" t="s">
         <v>41</v>
@@ -3922,13 +3955,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D131" t="s">
         <v>41</v>
@@ -3942,13 +3975,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B132" t="s">
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D132" t="s">
         <v>41</v>
@@ -3962,13 +3995,13 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B133" t="s">
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D133" t="s">
         <v>41</v>
@@ -3982,13 +4015,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D134" t="s">
         <v>46</v>
@@ -4002,13 +4035,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B135" t="s">
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D135" t="s">
         <v>46</v>
@@ -4022,13 +4055,13 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B136" t="s">
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D136" t="s">
         <v>46</v>
@@ -4042,13 +4075,13 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D137" t="s">
         <v>50</v>
@@ -4062,13 +4095,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D138" t="s">
         <v>53</v>
@@ -4082,13 +4115,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D139" t="s">
         <v>53</v>
@@ -4102,13 +4135,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B140" t="s">
         <v>55</v>
       </c>
       <c r="C140" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D140" t="s">
         <v>12</v>
@@ -4122,13 +4155,13 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" t="s">
         <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D141" t="s">
         <v>9</v>
@@ -4142,13 +4175,13 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B142" t="s">
         <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D142" t="s">
         <v>15</v>
@@ -4162,13 +4195,13 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B143" t="s">
         <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D143" t="s">
         <v>17</v>
@@ -4182,13 +4215,13 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B144" t="s">
         <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D144" t="s">
         <v>62</v>
@@ -4202,13 +4235,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B145" t="s">
         <v>55</v>
       </c>
       <c r="C145" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D145" t="s">
         <v>62</v>
@@ -4222,13 +4255,13 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B146" t="s">
         <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D146" t="s">
         <v>62</v>
@@ -4242,13 +4275,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B147" t="s">
         <v>55</v>
       </c>
       <c r="C147" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D147" t="s">
         <v>67</v>
@@ -4262,7 +4295,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B148" t="s">
         <v>55</v>
@@ -4282,13 +4315,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B149" t="s">
         <v>55</v>
       </c>
       <c r="C149" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D149" t="s">
         <v>23</v>
@@ -4302,13 +4335,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B150" t="s">
         <v>55</v>
       </c>
       <c r="C150" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D150" t="s">
         <v>23</v>
@@ -4322,13 +4355,13 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B151" t="s">
         <v>55</v>
       </c>
       <c r="C151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D151" t="s">
         <v>32</v>
@@ -4342,13 +4375,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B152" t="s">
         <v>55</v>
       </c>
       <c r="C152" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D152" t="s">
         <v>32</v>
@@ -4362,13 +4395,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B153" t="s">
         <v>55</v>
       </c>
       <c r="C153" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D153" t="s">
         <v>73</v>
@@ -4382,13 +4415,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B154" t="s">
         <v>55</v>
       </c>
       <c r="C154" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D154" t="s">
         <v>128</v>
@@ -4402,13 +4435,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B155" t="s">
         <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D155" t="s">
         <v>75</v>
@@ -4422,13 +4455,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B156" t="s">
         <v>55</v>
       </c>
       <c r="C156" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4442,13 +4475,13 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B157" t="s">
         <v>55</v>
       </c>
       <c r="C157" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D157" t="s">
         <v>78</v>
@@ -4462,13 +4495,13 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B158" t="s">
         <v>55</v>
       </c>
       <c r="C158" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D158" t="s">
         <v>78</v>
@@ -4482,19 +4515,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B159" t="s">
         <v>55</v>
       </c>
       <c r="C159" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D159" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E159" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F159">
         <v>30</v>
@@ -4502,19 +4535,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B160" t="s">
         <v>55</v>
       </c>
       <c r="C160" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D160" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E160" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F160">
         <v>11</v>
@@ -4522,13 +4555,13 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B161" t="s">
         <v>55</v>
       </c>
       <c r="C161" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D161" t="s">
         <v>37</v>
@@ -4542,13 +4575,13 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B162" t="s">
         <v>55</v>
       </c>
       <c r="C162" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D162" t="s">
         <v>37</v>
@@ -4562,13 +4595,13 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B163" t="s">
         <v>55</v>
       </c>
       <c r="C163" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D163" t="s">
         <v>41</v>
@@ -4582,13 +4615,13 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B164" t="s">
         <v>55</v>
       </c>
       <c r="C164" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D164" t="s">
         <v>41</v>
@@ -4602,13 +4635,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
+        <v>198</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
         <v>199</v>
-      </c>
-      <c r="B165" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" t="s">
-        <v>200</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -4622,13 +4655,13 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B166" t="s">
         <v>7</v>
       </c>
       <c r="C166" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D166" t="s">
         <v>15</v>
@@ -4642,13 +4675,13 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D167" t="s">
         <v>15</v>
@@ -4662,13 +4695,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B168" t="s">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D168" t="s">
         <v>15</v>
@@ -4682,13 +4715,13 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B169" t="s">
         <v>7</v>
       </c>
       <c r="C169" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D169" t="s">
         <v>15</v>
@@ -4702,13 +4735,13 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D170" t="s">
         <v>17</v>
@@ -4722,13 +4755,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B171" t="s">
         <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D171" t="s">
         <v>17</v>
@@ -4742,13 +4775,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B172" t="s">
         <v>7</v>
       </c>
       <c r="C172" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D172" t="s">
         <v>17</v>
@@ -4762,13 +4795,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D173" t="s">
         <v>62</v>
@@ -4782,13 +4815,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B174" t="s">
         <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D174" t="s">
         <v>89</v>
@@ -4802,13 +4835,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B175" t="s">
         <v>7</v>
       </c>
       <c r="C175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D175" t="s">
         <v>23</v>
@@ -4822,13 +4855,13 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
       </c>
       <c r="C176" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D176" t="s">
         <v>23</v>
@@ -4842,13 +4875,13 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B177" t="s">
         <v>7</v>
       </c>
       <c r="C177" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D177" t="s">
         <v>23</v>
@@ -4862,13 +4895,13 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B178" t="s">
         <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D178" t="s">
         <v>23</v>
@@ -4882,13 +4915,13 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -4902,13 +4935,13 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -4922,13 +4955,13 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D181" t="s">
         <v>32</v>
@@ -4942,13 +4975,13 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D182" t="s">
         <v>32</v>
@@ -4962,13 +4995,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B183" t="s">
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D183" t="s">
         <v>32</v>
@@ -4982,13 +5015,13 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B184" t="s">
         <v>7</v>
       </c>
       <c r="C184" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D184" t="s">
         <v>37</v>
@@ -5002,13 +5035,13 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B185" t="s">
         <v>7</v>
       </c>
       <c r="C185" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D185" t="s">
         <v>37</v>
@@ -5022,13 +5055,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B186" t="s">
         <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D186" t="s">
         <v>37</v>
@@ -5042,13 +5075,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B187" t="s">
         <v>7</v>
       </c>
       <c r="C187" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D187" t="s">
         <v>37</v>
@@ -5062,13 +5095,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B188" t="s">
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D188" t="s">
         <v>41</v>
@@ -5082,13 +5115,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B189" t="s">
         <v>7</v>
       </c>
       <c r="C189" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D189" t="s">
         <v>41</v>
@@ -5102,13 +5135,13 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B190" t="s">
         <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D190" t="s">
         <v>41</v>
@@ -5122,13 +5155,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B191" t="s">
         <v>7</v>
       </c>
       <c r="C191" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D191" t="s">
         <v>41</v>
@@ -5142,13 +5175,13 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B192" t="s">
         <v>7</v>
       </c>
       <c r="C192" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D192" t="s">
         <v>46</v>
@@ -5162,13 +5195,13 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B193" t="s">
         <v>7</v>
       </c>
       <c r="C193" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D193" t="s">
         <v>46</v>
@@ -5182,13 +5215,13 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B194" t="s">
         <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D194" t="s">
         <v>50</v>
@@ -5202,13 +5235,13 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B195" t="s">
         <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D195" t="s">
         <v>53</v>
@@ -5222,13 +5255,13 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B196" t="s">
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D196" t="s">
         <v>50</v>
@@ -5242,13 +5275,13 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B197" t="s">
         <v>55</v>
       </c>
       <c r="C197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D197" t="s">
         <v>12</v>
@@ -5262,13 +5295,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B198" t="s">
         <v>55</v>
       </c>
       <c r="C198" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D198" t="s">
         <v>12</v>
@@ -5282,13 +5315,13 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B199" t="s">
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -5302,13 +5335,13 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B200" t="s">
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -5322,13 +5355,13 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B201" t="s">
         <v>55</v>
       </c>
       <c r="C201" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D201" t="s">
         <v>17</v>
@@ -5342,13 +5375,13 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B202" t="s">
         <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D202" t="s">
         <v>89</v>
@@ -5362,13 +5395,13 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B203" t="s">
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D203" t="s">
         <v>17</v>
@@ -5382,13 +5415,13 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B204" t="s">
         <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D204" t="s">
         <v>17</v>
@@ -5402,7 +5435,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B205" t="s">
         <v>55</v>
@@ -5422,13 +5455,13 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B206" t="s">
         <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D206" t="s">
         <v>67</v>
@@ -5442,13 +5475,13 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B207" t="s">
         <v>55</v>
       </c>
       <c r="C207" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
@@ -5462,13 +5495,13 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B208" t="s">
         <v>55</v>
       </c>
       <c r="C208" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -5482,13 +5515,13 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B209" t="s">
         <v>55</v>
       </c>
       <c r="C209" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -5502,13 +5535,13 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B210" t="s">
         <v>55</v>
       </c>
       <c r="C210" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -5522,13 +5555,13 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B211" t="s">
         <v>55</v>
       </c>
       <c r="C211" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D211" t="s">
         <v>73</v>
@@ -5542,13 +5575,13 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B212" t="s">
         <v>55</v>
       </c>
       <c r="C212" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D212" t="s">
         <v>75</v>
@@ -5562,13 +5595,13 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B213" t="s">
         <v>55</v>
       </c>
       <c r="C213" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D213" t="s">
         <v>78</v>
@@ -5582,13 +5615,13 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B214" t="s">
         <v>55</v>
       </c>
       <c r="C214" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D214" t="s">
         <v>78</v>
@@ -5602,19 +5635,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B215" t="s">
         <v>55</v>
       </c>
       <c r="C215" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D215" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E215" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F215">
         <v>100</v>
@@ -5622,19 +5655,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B216" t="s">
         <v>55</v>
       </c>
       <c r="C216" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D216" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E216" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F216">
         <v>75</v>
@@ -5642,13 +5675,13 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B217" t="s">
         <v>55</v>
       </c>
       <c r="C217" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D217" t="s">
         <v>37</v>
@@ -5662,13 +5695,13 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B218" t="s">
         <v>55</v>
       </c>
       <c r="C218" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D218" t="s">
         <v>37</v>
@@ -5682,13 +5715,13 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B219" t="s">
         <v>55</v>
       </c>
       <c r="C219" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D219" t="s">
         <v>41</v>
@@ -5702,13 +5735,13 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B220" t="s">
         <v>55</v>
       </c>
       <c r="C220" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D220" t="s">
         <v>41</v>
@@ -5722,13 +5755,13 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
+        <v>254</v>
+      </c>
+      <c r="B221" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" t="s">
         <v>255</v>
-      </c>
-      <c r="B221" t="s">
-        <v>7</v>
-      </c>
-      <c r="C221" t="s">
-        <v>256</v>
       </c>
       <c r="D221" t="s">
         <v>12</v>
@@ -5742,13 +5775,13 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B222" t="s">
         <v>7</v>
       </c>
       <c r="C222" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
@@ -5762,13 +5795,13 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B223" t="s">
         <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D223" t="s">
         <v>9</v>
@@ -5782,13 +5815,13 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B224" t="s">
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -5802,13 +5835,13 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B225" t="s">
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D225" t="s">
         <v>15</v>
@@ -5822,13 +5855,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B226" t="s">
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D226" t="s">
         <v>17</v>
@@ -5842,13 +5875,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B227" t="s">
         <v>7</v>
       </c>
       <c r="C227" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>89</v>
@@ -5862,13 +5895,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
       </c>
       <c r="C228" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D228" t="s">
         <v>89</v>
@@ -5882,13 +5915,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D229" t="s">
         <v>23</v>
@@ -5902,13 +5935,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
       </c>
       <c r="C230" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D230" t="s">
         <v>23</v>
@@ -5922,13 +5955,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B231" t="s">
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D231" t="s">
         <v>23</v>
@@ -5942,13 +5975,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B232" t="s">
         <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D232" t="s">
         <v>23</v>
@@ -5962,16 +5995,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B233" t="s">
         <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D233" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E233" t="s">
         <v>29</v>
@@ -5982,13 +6015,13 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B234" t="s">
         <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D234" t="s">
         <v>29</v>
@@ -6002,13 +6035,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B235" t="s">
         <v>7</v>
       </c>
       <c r="C235" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -6022,13 +6055,13 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B236" t="s">
         <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -6042,13 +6075,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B237" t="s">
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -6062,13 +6095,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B238" t="s">
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -6082,13 +6115,13 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B239" t="s">
         <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D239" t="s">
         <v>37</v>
@@ -6102,13 +6135,13 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B240" t="s">
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D240" t="s">
         <v>37</v>
@@ -6122,13 +6155,13 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B241" t="s">
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D241" t="s">
         <v>37</v>
@@ -6142,13 +6175,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B242" t="s">
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D242" t="s">
         <v>37</v>
@@ -6162,13 +6195,13 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B243" t="s">
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D243" t="s">
         <v>41</v>
@@ -6182,13 +6215,13 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B244" t="s">
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D244" t="s">
         <v>41</v>
@@ -6202,13 +6235,13 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B245" t="s">
         <v>7</v>
       </c>
       <c r="C245" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D245" t="s">
         <v>41</v>
@@ -6222,13 +6255,13 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B246" t="s">
         <v>7</v>
       </c>
       <c r="C246" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D246" t="s">
         <v>41</v>
@@ -6242,13 +6275,13 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B247" t="s">
         <v>7</v>
       </c>
       <c r="C247" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D247" t="s">
         <v>46</v>
@@ -6262,13 +6295,13 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B248" t="s">
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D248" t="s">
         <v>46</v>
@@ -6282,13 +6315,13 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B249" t="s">
         <v>7</v>
       </c>
       <c r="C249" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D249" t="s">
         <v>46</v>
@@ -6302,13 +6335,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B250" t="s">
         <v>7</v>
       </c>
       <c r="C250" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D250" t="s">
         <v>50</v>
@@ -6322,13 +6355,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B251" t="s">
         <v>7</v>
       </c>
       <c r="C251" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D251" t="s">
         <v>53</v>
@@ -6342,13 +6375,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B252" t="s">
         <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D252" t="s">
         <v>50</v>
@@ -6362,13 +6395,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B253" t="s">
         <v>55</v>
       </c>
       <c r="C253" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D253" t="s">
         <v>15</v>
@@ -6382,13 +6415,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B254" t="s">
         <v>55</v>
       </c>
       <c r="C254" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D254" t="s">
         <v>15</v>
@@ -6402,13 +6435,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B255" t="s">
         <v>55</v>
       </c>
       <c r="C255" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D255" t="s">
         <v>9</v>
@@ -6422,13 +6455,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B256" t="s">
         <v>55</v>
       </c>
       <c r="C256" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D256" t="s">
         <v>9</v>
@@ -6442,13 +6475,13 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B257" t="s">
         <v>55</v>
       </c>
       <c r="C257" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D257" t="s">
         <v>17</v>
@@ -6462,13 +6495,13 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B258" t="s">
         <v>55</v>
       </c>
       <c r="C258" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D258" t="s">
         <v>89</v>
@@ -6482,7 +6515,7 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B259" t="s">
         <v>55</v>
@@ -6502,13 +6535,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B260" t="s">
         <v>55</v>
       </c>
       <c r="C260" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D260" t="s">
         <v>67</v>
@@ -6522,13 +6555,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B261" t="s">
         <v>55</v>
       </c>
       <c r="C261" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D261" t="s">
         <v>23</v>
@@ -6542,13 +6575,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B262" t="s">
         <v>55</v>
       </c>
       <c r="C262" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D262" t="s">
         <v>23</v>
@@ -6562,13 +6595,13 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B263" t="s">
         <v>55</v>
       </c>
       <c r="C263" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D263" t="s">
         <v>32</v>
@@ -6582,13 +6615,13 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B264" t="s">
         <v>55</v>
       </c>
       <c r="C264" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D264" t="s">
         <v>32</v>
@@ -6602,13 +6635,13 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B265" t="s">
         <v>55</v>
       </c>
       <c r="C265" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D265" t="s">
         <v>73</v>
@@ -6622,13 +6655,13 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B266" t="s">
         <v>55</v>
       </c>
       <c r="C266" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D266" t="s">
         <v>128</v>
@@ -6642,13 +6675,13 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B267" t="s">
         <v>55</v>
       </c>
       <c r="C267" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D267" t="s">
         <v>75</v>
@@ -6662,13 +6695,13 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B268" t="s">
         <v>55</v>
       </c>
       <c r="C268" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D268" t="s">
         <v>75</v>
@@ -6682,13 +6715,13 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B269" t="s">
         <v>55</v>
       </c>
       <c r="C269" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D269" t="s">
         <v>78</v>
@@ -6702,13 +6735,13 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B270" t="s">
         <v>55</v>
       </c>
       <c r="C270" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D270" t="s">
         <v>78</v>
@@ -6722,19 +6755,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B271" t="s">
         <v>55</v>
       </c>
       <c r="C271" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D271" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E271" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F271">
         <v>4</v>
@@ -6742,19 +6775,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B272" t="s">
         <v>55</v>
       </c>
       <c r="C272" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D272" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E272" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -6762,13 +6795,13 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B273" t="s">
         <v>55</v>
       </c>
       <c r="C273" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D273" t="s">
         <v>37</v>
@@ -6782,13 +6815,13 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B274" t="s">
         <v>55</v>
       </c>
       <c r="C274" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D274" t="s">
         <v>37</v>
@@ -6802,13 +6835,13 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B275" t="s">
         <v>55</v>
       </c>
       <c r="C275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D275" t="s">
         <v>41</v>
@@ -6822,13 +6855,13 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B276" t="s">
         <v>55</v>
       </c>
       <c r="C276" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D276" t="s">
         <v>41</v>
@@ -6842,13 +6875,13 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B277" t="s">
         <v>55</v>
       </c>
       <c r="C277" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D277" t="s">
         <v>12</v>
@@ -6862,13 +6895,13 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B278" t="s">
         <v>55</v>
       </c>
       <c r="C278" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D278" t="s">
         <v>75</v>
@@ -6882,13 +6915,13 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B279" t="s">
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -6902,13 +6935,13 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B280" t="s">
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D280" t="s">
         <v>46</v>
@@ -6928,7 +6961,7 @@
         <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D281" t="s">
         <v>37</v>
@@ -6948,7 +6981,7 @@
         <v>55</v>
       </c>
       <c r="C282" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D282" t="s">
         <v>78</v>
@@ -6968,13 +7001,13 @@
         <v>55</v>
       </c>
       <c r="C283" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D283" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="E283" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F283">
         <v>0</v>
@@ -6988,13 +7021,13 @@
         <v>55</v>
       </c>
       <c r="C284" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D284" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="E284" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -7008,7 +7041,7 @@
         <v>55</v>
       </c>
       <c r="C285" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D285" t="s">
         <v>12</v>
@@ -7017,6 +7050,206 @@
         <v>10</v>
       </c>
       <c r="F285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>83</v>
+      </c>
+      <c r="B286" t="s">
+        <v>7</v>
+      </c>
+      <c r="C286" t="s">
+        <v>316</v>
+      </c>
+      <c r="D286" t="s">
+        <v>46</v>
+      </c>
+      <c r="E286" t="s">
+        <v>46</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>83</v>
+      </c>
+      <c r="B287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287" t="s">
+        <v>317</v>
+      </c>
+      <c r="D287" t="s">
+        <v>32</v>
+      </c>
+      <c r="E287" t="s">
+        <v>32</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>83</v>
+      </c>
+      <c r="B288" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288" t="s">
+        <v>318</v>
+      </c>
+      <c r="D288" t="s">
+        <v>32</v>
+      </c>
+      <c r="E288" t="s">
+        <v>32</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>83</v>
+      </c>
+      <c r="B289" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" t="s">
+        <v>319</v>
+      </c>
+      <c r="D289" t="s">
+        <v>89</v>
+      </c>
+      <c r="E289" t="s">
+        <v>320</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>254</v>
+      </c>
+      <c r="B290" t="s">
+        <v>55</v>
+      </c>
+      <c r="C290" t="s">
+        <v>321</v>
+      </c>
+      <c r="D290" t="s">
+        <v>89</v>
+      </c>
+      <c r="E290" t="s">
+        <v>320</v>
+      </c>
+      <c r="F290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>254</v>
+      </c>
+      <c r="B291" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" t="s">
+        <v>322</v>
+      </c>
+      <c r="D291" t="s">
+        <v>323</v>
+      </c>
+      <c r="E291" t="s">
+        <v>320</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>83</v>
+      </c>
+      <c r="B292" t="s">
+        <v>7</v>
+      </c>
+      <c r="C292" t="s">
+        <v>324</v>
+      </c>
+      <c r="D292" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292" t="s">
+        <v>10</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>83</v>
+      </c>
+      <c r="B293" t="s">
+        <v>7</v>
+      </c>
+      <c r="C293" t="s">
+        <v>325</v>
+      </c>
+      <c r="D293" t="s">
+        <v>155</v>
+      </c>
+      <c r="E293" t="s">
+        <v>155</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>83</v>
+      </c>
+      <c r="B294" t="s">
+        <v>7</v>
+      </c>
+      <c r="C294" t="s">
+        <v>326</v>
+      </c>
+      <c r="D294" t="s">
+        <v>155</v>
+      </c>
+      <c r="E294" t="s">
+        <v>155</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>6</v>
+      </c>
+      <c r="B295" t="s">
+        <v>7</v>
+      </c>
+      <c r="C295" t="s">
+        <v>327</v>
+      </c>
+      <c r="D295" t="s">
+        <v>9</v>
+      </c>
+      <c r="E295" t="s">
+        <v>10</v>
+      </c>
+      <c r="F295">
         <v>0</v>
       </c>
     </row>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D636EAD-F4E2-4F14-A3D7-DABD33A0626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A6855F9-7C2C-4715-B887-EA92F5CB0EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="334">
   <si>
     <t>Manager</t>
   </si>
@@ -425,6 +426,9 @@
     <t>Ohio State Buckeyes</t>
   </si>
   <si>
+    <t>Arkansas Razorbacks</t>
+  </si>
+  <si>
     <t>Nebraska Cornhuskers</t>
   </si>
   <si>
@@ -932,9 +936,6 @@
     <t>West Virginia Mountaineers</t>
   </si>
   <si>
-    <t>Oklahoma</t>
-  </si>
-  <si>
     <t>Notre Dame Fighting Irish</t>
   </si>
   <si>
@@ -1007,6 +1008,21 @@
     <t>EPL</t>
   </si>
   <si>
+    <t>Como</t>
+  </si>
+  <si>
+    <t>Lautaro Martinez</t>
+  </si>
+  <si>
+    <t>Donyell Malen</t>
+  </si>
+  <si>
+    <t>Freiberg</t>
+  </si>
+  <si>
+    <t>Alabama Crimson Tide</t>
+  </si>
+  <si>
     <t>Joshua Kimmich</t>
   </si>
   <si>
@@ -1017,6 +1033,9 @@
   </si>
   <si>
     <t>Anders Dreyer</t>
+  </si>
+  <si>
+    <t>Tennessee Volunteers</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F295"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -2075,7 +2094,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B37" t="s">
         <v>55</v>
@@ -3281,7 +3300,7 @@
         <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>244</v>
+        <v>130</v>
       </c>
       <c r="D97" t="s">
         <v>75</v>
@@ -3301,7 +3320,7 @@
         <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D98" t="s">
         <v>78</v>
@@ -3321,7 +3340,7 @@
         <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D99" t="s">
         <v>78</v>
@@ -3344,10 +3363,10 @@
         <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E100" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F100">
         <v>15</v>
@@ -3361,13 +3380,13 @@
         <v>55</v>
       </c>
       <c r="C101" t="s">
+        <v>134</v>
+      </c>
+      <c r="D101" t="s">
         <v>133</v>
       </c>
-      <c r="D101" t="s">
-        <v>132</v>
-      </c>
       <c r="E101" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F101">
         <v>100</v>
@@ -3381,7 +3400,7 @@
         <v>55</v>
       </c>
       <c r="C102" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D102" t="s">
         <v>37</v>
@@ -3401,7 +3420,7 @@
         <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D103" t="s">
         <v>37</v>
@@ -3421,7 +3440,7 @@
         <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D104" t="s">
         <v>41</v>
@@ -3441,7 +3460,7 @@
         <v>55</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
@@ -3455,13 +3474,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B106" t="s">
         <v>7</v>
       </c>
       <c r="C106" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
@@ -3475,13 +3494,13 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D107" t="s">
         <v>12</v>
@@ -3495,13 +3514,13 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D108" t="s">
         <v>12</v>
@@ -3515,13 +3534,13 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B109" t="s">
         <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
@@ -3535,13 +3554,13 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
@@ -3555,13 +3574,13 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
         <v>17</v>
@@ -3575,13 +3594,13 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B112" t="s">
         <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D112" t="s">
         <v>89</v>
@@ -3595,13 +3614,13 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D113" t="s">
         <v>89</v>
@@ -3615,13 +3634,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B114" t="s">
         <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
         <v>17</v>
@@ -3635,13 +3654,13 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
         <v>17</v>
@@ -3655,13 +3674,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -3675,13 +3694,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B117" t="s">
         <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D117" t="s">
         <v>23</v>
@@ -3695,13 +3714,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B118" t="s">
         <v>7</v>
       </c>
       <c r="C118" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D118" t="s">
         <v>23</v>
@@ -3715,13 +3734,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D119" t="s">
         <v>23</v>
@@ -3735,13 +3754,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B120" t="s">
         <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D120" t="s">
         <v>28</v>
@@ -3755,16 +3774,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D121" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E121" t="s">
         <v>29</v>
@@ -3775,13 +3794,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -3795,13 +3814,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B123" t="s">
         <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -3815,13 +3834,13 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -3835,13 +3854,13 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -3855,13 +3874,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B126" t="s">
         <v>7</v>
       </c>
       <c r="C126" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D126" t="s">
         <v>37</v>
@@ -3875,13 +3894,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B127" t="s">
         <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D127" t="s">
         <v>37</v>
@@ -3895,13 +3914,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
         <v>37</v>
@@ -3915,13 +3934,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B129" t="s">
         <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D129" t="s">
         <v>37</v>
@@ -3935,13 +3954,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B130" t="s">
         <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D130" t="s">
         <v>41</v>
@@ -3955,13 +3974,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D131" t="s">
         <v>41</v>
@@ -3975,13 +3994,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B132" t="s">
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D132" t="s">
         <v>41</v>
@@ -3995,13 +4014,13 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B133" t="s">
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D133" t="s">
         <v>41</v>
@@ -4015,13 +4034,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D134" t="s">
         <v>46</v>
@@ -4035,13 +4054,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B135" t="s">
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D135" t="s">
         <v>46</v>
@@ -4055,13 +4074,13 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B136" t="s">
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D136" t="s">
         <v>46</v>
@@ -4075,13 +4094,13 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D137" t="s">
         <v>50</v>
@@ -4095,13 +4114,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
       </c>
       <c r="C138" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D138" t="s">
         <v>53</v>
@@ -4115,13 +4134,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D139" t="s">
         <v>53</v>
@@ -4135,13 +4154,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B140" t="s">
         <v>55</v>
       </c>
       <c r="C140" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D140" t="s">
         <v>12</v>
@@ -4155,13 +4174,13 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B141" t="s">
         <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D141" t="s">
         <v>9</v>
@@ -4175,13 +4194,13 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B142" t="s">
         <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D142" t="s">
         <v>15</v>
@@ -4195,13 +4214,13 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B143" t="s">
         <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D143" t="s">
         <v>17</v>
@@ -4215,13 +4234,13 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
         <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D144" t="s">
         <v>62</v>
@@ -4235,13 +4254,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B145" t="s">
         <v>55</v>
       </c>
       <c r="C145" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D145" t="s">
         <v>62</v>
@@ -4255,13 +4274,13 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B146" t="s">
         <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D146" t="s">
         <v>62</v>
@@ -4275,13 +4294,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B147" t="s">
         <v>55</v>
       </c>
       <c r="C147" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D147" t="s">
         <v>67</v>
@@ -4295,7 +4314,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B148" t="s">
         <v>55</v>
@@ -4315,13 +4334,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B149" t="s">
         <v>55</v>
       </c>
       <c r="C149" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D149" t="s">
         <v>23</v>
@@ -4335,13 +4354,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B150" t="s">
         <v>55</v>
       </c>
       <c r="C150" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D150" t="s">
         <v>23</v>
@@ -4355,13 +4374,13 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B151" t="s">
         <v>55</v>
       </c>
       <c r="C151" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D151" t="s">
         <v>32</v>
@@ -4375,13 +4394,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B152" t="s">
         <v>55</v>
       </c>
       <c r="C152" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D152" t="s">
         <v>32</v>
@@ -4395,13 +4414,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B153" t="s">
         <v>55</v>
       </c>
       <c r="C153" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D153" t="s">
         <v>73</v>
@@ -4415,13 +4434,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B154" t="s">
         <v>55</v>
       </c>
       <c r="C154" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D154" t="s">
         <v>128</v>
@@ -4435,13 +4454,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B155" t="s">
         <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D155" t="s">
         <v>75</v>
@@ -4455,13 +4474,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B156" t="s">
         <v>55</v>
       </c>
       <c r="C156" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4475,13 +4494,13 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B157" t="s">
         <v>55</v>
       </c>
       <c r="C157" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D157" t="s">
         <v>78</v>
@@ -4495,13 +4514,13 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B158" t="s">
         <v>55</v>
       </c>
       <c r="C158" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D158" t="s">
         <v>78</v>
@@ -4515,19 +4534,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B159" t="s">
         <v>55</v>
       </c>
       <c r="C159" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D159" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E159" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F159">
         <v>30</v>
@@ -4535,19 +4554,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B160" t="s">
         <v>55</v>
       </c>
       <c r="C160" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D160" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E160" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F160">
         <v>11</v>
@@ -4555,13 +4574,13 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B161" t="s">
         <v>55</v>
       </c>
       <c r="C161" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D161" t="s">
         <v>37</v>
@@ -4575,13 +4594,13 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B162" t="s">
         <v>55</v>
       </c>
       <c r="C162" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D162" t="s">
         <v>37</v>
@@ -4595,13 +4614,13 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B163" t="s">
         <v>55</v>
       </c>
       <c r="C163" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D163" t="s">
         <v>41</v>
@@ -4615,13 +4634,13 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B164" t="s">
         <v>55</v>
       </c>
       <c r="C164" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D164" t="s">
         <v>41</v>
@@ -4635,13 +4654,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B165" t="s">
         <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -4655,13 +4674,13 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B166" t="s">
         <v>7</v>
       </c>
       <c r="C166" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D166" t="s">
         <v>15</v>
@@ -4675,13 +4694,13 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D167" t="s">
         <v>15</v>
@@ -4695,13 +4714,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B168" t="s">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D168" t="s">
         <v>15</v>
@@ -4715,13 +4734,13 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B169" t="s">
         <v>7</v>
       </c>
       <c r="C169" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D169" t="s">
         <v>15</v>
@@ -4735,13 +4754,13 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D170" t="s">
         <v>17</v>
@@ -4755,13 +4774,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B171" t="s">
         <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D171" t="s">
         <v>17</v>
@@ -4775,13 +4794,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B172" t="s">
         <v>7</v>
       </c>
       <c r="C172" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D172" t="s">
         <v>17</v>
@@ -4795,13 +4814,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D173" t="s">
         <v>62</v>
@@ -4815,13 +4834,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B174" t="s">
         <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D174" t="s">
         <v>89</v>
@@ -4835,13 +4854,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B175" t="s">
         <v>7</v>
       </c>
       <c r="C175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D175" t="s">
         <v>23</v>
@@ -4855,13 +4874,13 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
       </c>
       <c r="C176" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D176" t="s">
         <v>23</v>
@@ -4875,13 +4894,13 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B177" t="s">
         <v>7</v>
       </c>
       <c r="C177" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D177" t="s">
         <v>23</v>
@@ -4895,13 +4914,13 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B178" t="s">
         <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D178" t="s">
         <v>23</v>
@@ -4915,13 +4934,13 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -4935,13 +4954,13 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -4955,13 +4974,13 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D181" t="s">
         <v>32</v>
@@ -4975,13 +4994,13 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D182" t="s">
         <v>32</v>
@@ -4995,13 +5014,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B183" t="s">
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D183" t="s">
         <v>32</v>
@@ -5015,13 +5034,13 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B184" t="s">
         <v>7</v>
       </c>
       <c r="C184" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D184" t="s">
         <v>37</v>
@@ -5035,13 +5054,13 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B185" t="s">
         <v>7</v>
       </c>
       <c r="C185" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D185" t="s">
         <v>37</v>
@@ -5055,13 +5074,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B186" t="s">
         <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D186" t="s">
         <v>37</v>
@@ -5075,13 +5094,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B187" t="s">
         <v>7</v>
       </c>
       <c r="C187" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D187" t="s">
         <v>37</v>
@@ -5095,13 +5114,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B188" t="s">
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D188" t="s">
         <v>41</v>
@@ -5115,13 +5134,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B189" t="s">
         <v>7</v>
       </c>
       <c r="C189" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D189" t="s">
         <v>41</v>
@@ -5135,13 +5154,13 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B190" t="s">
         <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D190" t="s">
         <v>41</v>
@@ -5155,13 +5174,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B191" t="s">
         <v>7</v>
       </c>
       <c r="C191" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D191" t="s">
         <v>41</v>
@@ -5175,13 +5194,13 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B192" t="s">
         <v>7</v>
       </c>
       <c r="C192" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D192" t="s">
         <v>46</v>
@@ -5195,13 +5214,13 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B193" t="s">
         <v>7</v>
       </c>
       <c r="C193" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D193" t="s">
         <v>46</v>
@@ -5215,13 +5234,13 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B194" t="s">
         <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D194" t="s">
         <v>50</v>
@@ -5235,13 +5254,13 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B195" t="s">
         <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D195" t="s">
         <v>53</v>
@@ -5255,13 +5274,13 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B196" t="s">
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D196" t="s">
         <v>50</v>
@@ -5275,13 +5294,13 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B197" t="s">
         <v>55</v>
       </c>
       <c r="C197" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D197" t="s">
         <v>12</v>
@@ -5295,13 +5314,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B198" t="s">
         <v>55</v>
       </c>
       <c r="C198" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D198" t="s">
         <v>12</v>
@@ -5315,13 +5334,13 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B199" t="s">
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -5335,13 +5354,13 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B200" t="s">
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -5355,13 +5374,13 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B201" t="s">
         <v>55</v>
       </c>
       <c r="C201" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D201" t="s">
         <v>17</v>
@@ -5375,13 +5394,13 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B202" t="s">
         <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D202" t="s">
         <v>89</v>
@@ -5395,13 +5414,13 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B203" t="s">
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D203" t="s">
         <v>17</v>
@@ -5415,13 +5434,13 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B204" t="s">
         <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D204" t="s">
         <v>17</v>
@@ -5435,7 +5454,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B205" t="s">
         <v>55</v>
@@ -5455,13 +5474,13 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B206" t="s">
         <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D206" t="s">
         <v>67</v>
@@ -5475,13 +5494,13 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B207" t="s">
         <v>55</v>
       </c>
       <c r="C207" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
@@ -5495,13 +5514,13 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B208" t="s">
         <v>55</v>
       </c>
       <c r="C208" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -5515,13 +5534,13 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B209" t="s">
         <v>55</v>
       </c>
       <c r="C209" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -5535,13 +5554,13 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B210" t="s">
         <v>55</v>
       </c>
       <c r="C210" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -5555,13 +5574,13 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B211" t="s">
         <v>55</v>
       </c>
       <c r="C211" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D211" t="s">
         <v>73</v>
@@ -5575,13 +5594,13 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B212" t="s">
         <v>55</v>
       </c>
       <c r="C212" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D212" t="s">
         <v>75</v>
@@ -5595,13 +5614,13 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B213" t="s">
         <v>55</v>
       </c>
       <c r="C213" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D213" t="s">
         <v>78</v>
@@ -5615,13 +5634,13 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B214" t="s">
         <v>55</v>
       </c>
       <c r="C214" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D214" t="s">
         <v>78</v>
@@ -5635,19 +5654,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B215" t="s">
         <v>55</v>
       </c>
       <c r="C215" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D215" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E215" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F215">
         <v>100</v>
@@ -5655,19 +5674,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B216" t="s">
         <v>55</v>
       </c>
       <c r="C216" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D216" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E216" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F216">
         <v>75</v>
@@ -5675,13 +5694,13 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B217" t="s">
         <v>55</v>
       </c>
       <c r="C217" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D217" t="s">
         <v>37</v>
@@ -5695,13 +5714,13 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B218" t="s">
         <v>55</v>
       </c>
       <c r="C218" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D218" t="s">
         <v>37</v>
@@ -5715,13 +5734,13 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B219" t="s">
         <v>55</v>
       </c>
       <c r="C219" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D219" t="s">
         <v>41</v>
@@ -5735,13 +5754,13 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B220" t="s">
         <v>55</v>
       </c>
       <c r="C220" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D220" t="s">
         <v>41</v>
@@ -5755,13 +5774,13 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B221" t="s">
         <v>7</v>
       </c>
       <c r="C221" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D221" t="s">
         <v>12</v>
@@ -5775,13 +5794,13 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B222" t="s">
         <v>7</v>
       </c>
       <c r="C222" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
@@ -5795,13 +5814,13 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B223" t="s">
         <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D223" t="s">
         <v>9</v>
@@ -5815,13 +5834,13 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B224" t="s">
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -5835,13 +5854,13 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B225" t="s">
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D225" t="s">
         <v>15</v>
@@ -5855,13 +5874,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B226" t="s">
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>17</v>
@@ -5875,13 +5894,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B227" t="s">
         <v>7</v>
       </c>
       <c r="C227" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D227" t="s">
         <v>89</v>
@@ -5895,13 +5914,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
       </c>
       <c r="C228" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D228" t="s">
         <v>89</v>
@@ -5915,13 +5934,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D229" t="s">
         <v>23</v>
@@ -5935,13 +5954,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
       </c>
       <c r="C230" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D230" t="s">
         <v>23</v>
@@ -5955,13 +5974,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B231" t="s">
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D231" t="s">
         <v>23</v>
@@ -5975,13 +5994,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B232" t="s">
         <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D232" t="s">
         <v>23</v>
@@ -5995,16 +6014,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B233" t="s">
         <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D233" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E233" t="s">
         <v>29</v>
@@ -6015,13 +6034,13 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B234" t="s">
         <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D234" t="s">
         <v>29</v>
@@ -6035,13 +6054,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B235" t="s">
         <v>7</v>
       </c>
       <c r="C235" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -6055,13 +6074,13 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B236" t="s">
         <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -6075,13 +6094,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B237" t="s">
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -6095,13 +6114,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B238" t="s">
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -6115,13 +6134,13 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B239" t="s">
         <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D239" t="s">
         <v>37</v>
@@ -6135,13 +6154,13 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B240" t="s">
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D240" t="s">
         <v>37</v>
@@ -6155,13 +6174,13 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B241" t="s">
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D241" t="s">
         <v>37</v>
@@ -6175,13 +6194,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B242" t="s">
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D242" t="s">
         <v>37</v>
@@ -6195,13 +6214,13 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B243" t="s">
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D243" t="s">
         <v>41</v>
@@ -6215,13 +6234,13 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B244" t="s">
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D244" t="s">
         <v>41</v>
@@ -6235,13 +6254,13 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B245" t="s">
         <v>7</v>
       </c>
       <c r="C245" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D245" t="s">
         <v>41</v>
@@ -6255,13 +6274,13 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B246" t="s">
         <v>7</v>
       </c>
       <c r="C246" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D246" t="s">
         <v>41</v>
@@ -6275,13 +6294,13 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B247" t="s">
         <v>7</v>
       </c>
       <c r="C247" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D247" t="s">
         <v>46</v>
@@ -6295,13 +6314,13 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B248" t="s">
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D248" t="s">
         <v>46</v>
@@ -6315,13 +6334,13 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B249" t="s">
         <v>7</v>
       </c>
       <c r="C249" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D249" t="s">
         <v>46</v>
@@ -6335,13 +6354,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B250" t="s">
         <v>7</v>
       </c>
       <c r="C250" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D250" t="s">
         <v>50</v>
@@ -6355,13 +6374,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B251" t="s">
         <v>7</v>
       </c>
       <c r="C251" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D251" t="s">
         <v>53</v>
@@ -6375,13 +6394,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B252" t="s">
         <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D252" t="s">
         <v>50</v>
@@ -6395,13 +6414,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B253" t="s">
         <v>55</v>
       </c>
       <c r="C253" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D253" t="s">
         <v>15</v>
@@ -6415,13 +6434,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B254" t="s">
         <v>55</v>
       </c>
       <c r="C254" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D254" t="s">
         <v>15</v>
@@ -6435,13 +6454,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B255" t="s">
         <v>55</v>
       </c>
       <c r="C255" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D255" t="s">
         <v>9</v>
@@ -6455,13 +6474,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B256" t="s">
         <v>55</v>
       </c>
       <c r="C256" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D256" t="s">
         <v>9</v>
@@ -6475,13 +6494,13 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B257" t="s">
         <v>55</v>
       </c>
       <c r="C257" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D257" t="s">
         <v>17</v>
@@ -6495,13 +6514,13 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B258" t="s">
         <v>55</v>
       </c>
       <c r="C258" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D258" t="s">
         <v>89</v>
@@ -6515,7 +6534,7 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B259" t="s">
         <v>55</v>
@@ -6535,13 +6554,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B260" t="s">
         <v>55</v>
       </c>
       <c r="C260" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D260" t="s">
         <v>67</v>
@@ -6555,13 +6574,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B261" t="s">
         <v>55</v>
       </c>
       <c r="C261" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D261" t="s">
         <v>23</v>
@@ -6575,13 +6594,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B262" t="s">
         <v>55</v>
       </c>
       <c r="C262" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D262" t="s">
         <v>23</v>
@@ -6595,13 +6614,13 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B263" t="s">
         <v>55</v>
       </c>
       <c r="C263" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D263" t="s">
         <v>32</v>
@@ -6615,13 +6634,13 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B264" t="s">
         <v>55</v>
       </c>
       <c r="C264" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D264" t="s">
         <v>32</v>
@@ -6635,13 +6654,13 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B265" t="s">
         <v>55</v>
       </c>
       <c r="C265" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D265" t="s">
         <v>73</v>
@@ -6655,13 +6674,13 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B266" t="s">
         <v>55</v>
       </c>
       <c r="C266" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="D266" t="s">
         <v>128</v>
@@ -6675,7 +6694,7 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B267" t="s">
         <v>55</v>
@@ -6695,7 +6714,7 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B268" t="s">
         <v>55</v>
@@ -6715,7 +6734,7 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B269" t="s">
         <v>55</v>
@@ -6735,7 +6754,7 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B270" t="s">
         <v>55</v>
@@ -6755,7 +6774,7 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B271" t="s">
         <v>55</v>
@@ -6764,10 +6783,10 @@
         <v>300</v>
       </c>
       <c r="D271" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E271" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F271">
         <v>4</v>
@@ -6775,7 +6794,7 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B272" t="s">
         <v>55</v>
@@ -6784,10 +6803,10 @@
         <v>304</v>
       </c>
       <c r="D272" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E272" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -6795,7 +6814,7 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B273" t="s">
         <v>55</v>
@@ -6815,7 +6834,7 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B274" t="s">
         <v>55</v>
@@ -6835,7 +6854,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B275" t="s">
         <v>55</v>
@@ -6855,7 +6874,7 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B276" t="s">
         <v>55</v>
@@ -6875,7 +6894,7 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B277" t="s">
         <v>55</v>
@@ -6895,7 +6914,7 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B278" t="s">
         <v>55</v>
@@ -6915,7 +6934,7 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B279" t="s">
         <v>7</v>
@@ -6935,7 +6954,7 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B280" t="s">
         <v>7</v>
@@ -6981,7 +7000,7 @@
         <v>55</v>
       </c>
       <c r="C282" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D282" t="s">
         <v>78</v>
@@ -7004,10 +7023,10 @@
         <v>314</v>
       </c>
       <c r="D283" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E283" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F283">
         <v>0</v>
@@ -7021,13 +7040,13 @@
         <v>55</v>
       </c>
       <c r="C284" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D284" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E284" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -7135,7 +7154,7 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B290" t="s">
         <v>55</v>
@@ -7155,7 +7174,7 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B291" t="s">
         <v>7</v>
@@ -7175,19 +7194,19 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B292" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C292" t="s">
         <v>324</v>
       </c>
       <c r="D292" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="E292" t="s">
-        <v>10</v>
+        <v>320</v>
       </c>
       <c r="F292">
         <v>0</v>
@@ -7195,7 +7214,7 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B293" t="s">
         <v>7</v>
@@ -7204,10 +7223,10 @@
         <v>325</v>
       </c>
       <c r="D293" t="s">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="E293" t="s">
-        <v>155</v>
+        <v>320</v>
       </c>
       <c r="F293">
         <v>0</v>
@@ -7215,7 +7234,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="B294" t="s">
         <v>7</v>
@@ -7224,10 +7243,10 @@
         <v>326</v>
       </c>
       <c r="D294" t="s">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="E294" t="s">
-        <v>155</v>
+        <v>320</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -7238,7 +7257,7 @@
         <v>6</v>
       </c>
       <c r="B295" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C295" t="s">
         <v>327</v>
@@ -7250,6 +7269,126 @@
         <v>10</v>
       </c>
       <c r="F295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>199</v>
+      </c>
+      <c r="B296" t="s">
+        <v>55</v>
+      </c>
+      <c r="C296" t="s">
+        <v>328</v>
+      </c>
+      <c r="D296" t="s">
+        <v>128</v>
+      </c>
+      <c r="E296" t="s">
+        <v>128</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>83</v>
+      </c>
+      <c r="B297" t="s">
+        <v>7</v>
+      </c>
+      <c r="C297" t="s">
+        <v>329</v>
+      </c>
+      <c r="D297" t="s">
+        <v>9</v>
+      </c>
+      <c r="E297" t="s">
+        <v>10</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>83</v>
+      </c>
+      <c r="B298" t="s">
+        <v>7</v>
+      </c>
+      <c r="C298" t="s">
+        <v>330</v>
+      </c>
+      <c r="D298" t="s">
+        <v>156</v>
+      </c>
+      <c r="E298" t="s">
+        <v>156</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>83</v>
+      </c>
+      <c r="B299" t="s">
+        <v>7</v>
+      </c>
+      <c r="C299" t="s">
+        <v>331</v>
+      </c>
+      <c r="D299" t="s">
+        <v>156</v>
+      </c>
+      <c r="E299" t="s">
+        <v>156</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" t="s">
+        <v>7</v>
+      </c>
+      <c r="C300" t="s">
+        <v>332</v>
+      </c>
+      <c r="D300" t="s">
+        <v>9</v>
+      </c>
+      <c r="E300" t="s">
+        <v>10</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>6</v>
+      </c>
+      <c r="B301" t="s">
+        <v>55</v>
+      </c>
+      <c r="C301" t="s">
+        <v>333</v>
+      </c>
+      <c r="D301" t="s">
+        <v>128</v>
+      </c>
+      <c r="E301" t="s">
+        <v>128</v>
+      </c>
+      <c r="F301">
         <v>0</v>
       </c>
     </row>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A6855F9-7C2C-4715-B887-EA92F5CB0EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{C109C182-F1F8-4A85-985E-E22DCC72D580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="333">
   <si>
     <t>Manager</t>
   </si>
@@ -994,9 +994,6 @@
   </si>
   <si>
     <t>Arda Güler</t>
-  </si>
-  <si>
-    <t>Club Soccer Top</t>
   </si>
   <si>
     <t>Athletic Club</t>
@@ -7146,7 +7143,7 @@
         <v>89</v>
       </c>
       <c r="E289" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="F289">
         <v>0</v>
@@ -7160,13 +7157,13 @@
         <v>55</v>
       </c>
       <c r="C290" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D290" t="s">
         <v>89</v>
       </c>
       <c r="E290" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="F290">
         <v>0</v>
@@ -7180,13 +7177,13 @@
         <v>7</v>
       </c>
       <c r="C291" t="s">
+        <v>321</v>
+      </c>
+      <c r="D291" t="s">
         <v>322</v>
       </c>
-      <c r="D291" t="s">
-        <v>323</v>
-      </c>
       <c r="E291" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="F291">
         <v>0</v>
@@ -7200,13 +7197,13 @@
         <v>55</v>
       </c>
       <c r="C292" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D292" t="s">
         <v>62</v>
       </c>
       <c r="E292" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="F292">
         <v>0</v>
@@ -7220,13 +7217,13 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D293" t="s">
         <v>62</v>
       </c>
       <c r="E293" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="F293">
         <v>0</v>
@@ -7240,13 +7237,13 @@
         <v>7</v>
       </c>
       <c r="C294" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D294" t="s">
         <v>62</v>
       </c>
       <c r="E294" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -7260,7 +7257,7 @@
         <v>55</v>
       </c>
       <c r="C295" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
@@ -7280,7 +7277,7 @@
         <v>55</v>
       </c>
       <c r="C296" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D296" t="s">
         <v>128</v>
@@ -7300,7 +7297,7 @@
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -7320,13 +7317,13 @@
         <v>7</v>
       </c>
       <c r="C298" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D298" t="s">
         <v>156</v>
       </c>
       <c r="E298" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="F298">
         <v>0</v>
@@ -7340,13 +7337,13 @@
         <v>7</v>
       </c>
       <c r="C299" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D299" t="s">
         <v>156</v>
       </c>
       <c r="E299" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="F299">
         <v>0</v>
@@ -7360,7 +7357,7 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D300" t="s">
         <v>9</v>
@@ -7380,7 +7377,7 @@
         <v>55</v>
       </c>
       <c r="C301" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D301" t="s">
         <v>128</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{C109C182-F1F8-4A85-985E-E22DCC72D580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD6C3B03-27D9-E047-98A8-710CE771726E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1000,9 +999,6 @@
   </si>
   <si>
     <t>Zavier Gozo</t>
-  </si>
-  <si>
-    <t>EPL</t>
   </si>
   <si>
     <t>Como</t>
@@ -1367,9 +1363,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F301"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +1385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1409,7 +1405,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1429,7 +1425,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1449,7 +1445,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1469,7 +1465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1489,7 +1485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1509,7 +1505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1529,7 +1525,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1549,7 +1545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1569,7 +1565,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1589,7 +1585,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1609,7 +1605,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1629,7 +1625,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1649,7 +1645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1669,7 +1665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1689,7 +1685,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1709,7 +1705,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1729,7 +1725,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1749,7 +1745,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1769,7 +1765,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1789,7 +1785,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1809,7 +1805,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1829,7 +1825,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1849,7 +1845,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1869,7 +1865,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1889,7 +1885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1909,7 +1905,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1929,7 +1925,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1949,7 +1945,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1969,7 +1965,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1989,7 +1985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2009,7 +2005,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -2029,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2049,7 +2045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2065,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2089,7 +2085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>255</v>
       </c>
@@ -2109,7 +2105,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2129,7 +2125,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2149,7 +2145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2169,7 +2165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2189,7 +2185,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2209,7 +2205,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2229,7 +2225,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2249,7 +2245,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2269,7 +2265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2289,7 +2285,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2309,7 +2305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2329,7 +2325,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2349,7 +2345,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2369,7 +2365,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2389,7 +2385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2409,7 +2405,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>83</v>
       </c>
@@ -2429,7 +2425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -2449,7 +2445,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2469,7 +2465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -2489,7 +2485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -2509,7 +2505,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -2529,7 +2525,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -2549,7 +2545,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -2569,7 +2565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -2589,7 +2585,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -2609,7 +2605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -2629,7 +2625,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -2649,7 +2645,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -2669,7 +2665,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -2689,7 +2685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -2709,7 +2705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -2729,7 +2725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -2749,7 +2745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2769,7 +2765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2789,7 +2785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2809,7 +2805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2829,7 +2825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2849,7 +2845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2869,7 +2865,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2889,7 +2885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2909,7 +2905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2929,7 +2925,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2949,7 +2945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2969,7 +2965,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2989,7 +2985,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -3009,7 +3005,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -3029,7 +3025,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -3049,7 +3045,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -3069,7 +3065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -3089,7 +3085,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3109,7 +3105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -3129,7 +3125,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -3149,7 +3145,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3169,7 +3165,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3189,7 +3185,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3209,7 +3205,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3229,7 +3225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3249,7 +3245,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3269,7 +3265,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3289,7 +3285,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3309,7 +3305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3329,7 +3325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3349,7 +3345,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3369,7 +3365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3389,7 +3385,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3409,7 +3405,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3429,7 +3425,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3449,7 +3445,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3469,7 +3465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>139</v>
       </c>
@@ -3489,7 +3485,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>139</v>
       </c>
@@ -3509,7 +3505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>139</v>
       </c>
@@ -3529,7 +3525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>139</v>
       </c>
@@ -3549,7 +3545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>139</v>
       </c>
@@ -3569,7 +3565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3589,7 +3585,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -3609,7 +3605,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -3629,7 +3625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>139</v>
       </c>
@@ -3649,7 +3645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>255</v>
       </c>
@@ -3669,7 +3665,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>139</v>
       </c>
@@ -3689,7 +3685,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>139</v>
       </c>
@@ -3709,7 +3705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>139</v>
       </c>
@@ -3729,7 +3725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -3749,7 +3745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>139</v>
       </c>
@@ -3769,7 +3765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>139</v>
       </c>
@@ -3789,7 +3785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>139</v>
       </c>
@@ -3809,7 +3805,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>139</v>
       </c>
@@ -3829,7 +3825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>139</v>
       </c>
@@ -3849,7 +3845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -3869,7 +3865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>139</v>
       </c>
@@ -3889,7 +3885,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>139</v>
       </c>
@@ -3909,7 +3905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -3929,7 +3925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -3949,7 +3945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>139</v>
       </c>
@@ -3969,7 +3965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -3989,7 +3985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -4009,7 +4005,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>139</v>
       </c>
@@ -4029,7 +4025,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -4049,7 +4045,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -4069,7 +4065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -4089,7 +4085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -4109,7 +4105,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>139</v>
       </c>
@@ -4129,7 +4125,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -4149,7 +4145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -4169,7 +4165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -4189,7 +4185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>139</v>
       </c>
@@ -4209,7 +4205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>139</v>
       </c>
@@ -4229,7 +4225,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>139</v>
       </c>
@@ -4249,7 +4245,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -4269,7 +4265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>139</v>
       </c>
@@ -4289,7 +4285,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>139</v>
       </c>
@@ -4309,7 +4305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>139</v>
       </c>
@@ -4329,7 +4325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>139</v>
       </c>
@@ -4349,7 +4345,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>139</v>
       </c>
@@ -4369,7 +4365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>139</v>
       </c>
@@ -4389,7 +4385,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>139</v>
       </c>
@@ -4409,7 +4405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>139</v>
       </c>
@@ -4429,7 +4425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>139</v>
       </c>
@@ -4449,7 +4445,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>139</v>
       </c>
@@ -4469,7 +4465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>139</v>
       </c>
@@ -4489,7 +4485,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>139</v>
       </c>
@@ -4509,7 +4505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>139</v>
       </c>
@@ -4529,7 +4525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>139</v>
       </c>
@@ -4549,7 +4545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>139</v>
       </c>
@@ -4569,7 +4565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>139</v>
       </c>
@@ -4589,7 +4585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -4609,7 +4605,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>139</v>
       </c>
@@ -4629,7 +4625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>139</v>
       </c>
@@ -4649,7 +4645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>199</v>
       </c>
@@ -4669,7 +4665,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4689,7 +4685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>199</v>
       </c>
@@ -4709,7 +4705,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>199</v>
       </c>
@@ -4729,7 +4725,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>199</v>
       </c>
@@ -4749,7 +4745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>199</v>
       </c>
@@ -4769,7 +4765,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>199</v>
       </c>
@@ -4789,7 +4785,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -4809,7 +4805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>199</v>
       </c>
@@ -4829,7 +4825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>199</v>
       </c>
@@ -4849,7 +4845,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>199</v>
       </c>
@@ -4869,7 +4865,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>199</v>
       </c>
@@ -4889,7 +4885,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>199</v>
       </c>
@@ -4909,7 +4905,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>199</v>
       </c>
@@ -4929,7 +4925,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>199</v>
       </c>
@@ -4949,7 +4945,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>199</v>
       </c>
@@ -4969,7 +4965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>199</v>
       </c>
@@ -4989,7 +4985,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>199</v>
       </c>
@@ -5009,7 +5005,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>199</v>
       </c>
@@ -5029,7 +5025,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>199</v>
       </c>
@@ -5049,7 +5045,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>199</v>
       </c>
@@ -5069,7 +5065,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>199</v>
       </c>
@@ -5089,7 +5085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>199</v>
       </c>
@@ -5109,7 +5105,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>199</v>
       </c>
@@ -5129,7 +5125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -5149,7 +5145,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>199</v>
       </c>
@@ -5169,7 +5165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>199</v>
       </c>
@@ -5189,7 +5185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -5209,7 +5205,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>199</v>
       </c>
@@ -5229,7 +5225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -5249,7 +5245,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -5269,7 +5265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -5289,7 +5285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -5309,7 +5305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>199</v>
       </c>
@@ -5329,7 +5325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>199</v>
       </c>
@@ -5349,7 +5345,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -5369,7 +5365,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5389,7 +5385,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>199</v>
       </c>
@@ -5409,7 +5405,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>199</v>
       </c>
@@ -5429,7 +5425,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>199</v>
       </c>
@@ -5449,7 +5445,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>199</v>
       </c>
@@ -5469,7 +5465,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>199</v>
       </c>
@@ -5489,7 +5485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>199</v>
       </c>
@@ -5509,7 +5505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>199</v>
       </c>
@@ -5529,7 +5525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>199</v>
       </c>
@@ -5549,7 +5545,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>199</v>
       </c>
@@ -5569,7 +5565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>199</v>
       </c>
@@ -5589,7 +5585,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>199</v>
       </c>
@@ -5609,7 +5605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>199</v>
       </c>
@@ -5629,7 +5625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -5649,7 +5645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>199</v>
       </c>
@@ -5669,7 +5665,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>199</v>
       </c>
@@ -5689,7 +5685,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>199</v>
       </c>
@@ -5709,7 +5705,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>199</v>
       </c>
@@ -5729,7 +5725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>199</v>
       </c>
@@ -5749,7 +5745,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>199</v>
       </c>
@@ -5769,7 +5765,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>255</v>
       </c>
@@ -5789,7 +5785,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>255</v>
       </c>
@@ -5809,7 +5805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>255</v>
       </c>
@@ -5829,7 +5825,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>255</v>
       </c>
@@ -5849,7 +5845,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>255</v>
       </c>
@@ -5869,7 +5865,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>255</v>
       </c>
@@ -5889,7 +5885,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>255</v>
       </c>
@@ -5909,7 +5905,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>255</v>
       </c>
@@ -5929,7 +5925,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>255</v>
       </c>
@@ -5949,7 +5945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>255</v>
       </c>
@@ -5969,7 +5965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>255</v>
       </c>
@@ -5989,7 +5985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>255</v>
       </c>
@@ -6009,7 +6005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>255</v>
       </c>
@@ -6029,7 +6025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>255</v>
       </c>
@@ -6049,7 +6045,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>255</v>
       </c>
@@ -6069,7 +6065,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -6089,7 +6085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>255</v>
       </c>
@@ -6109,7 +6105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>255</v>
       </c>
@@ -6129,7 +6125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>255</v>
       </c>
@@ -6149,7 +6145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>255</v>
       </c>
@@ -6169,7 +6165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>255</v>
       </c>
@@ -6189,7 +6185,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>255</v>
       </c>
@@ -6209,7 +6205,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>255</v>
       </c>
@@ -6229,7 +6225,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>255</v>
       </c>
@@ -6249,7 +6245,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>255</v>
       </c>
@@ -6269,7 +6265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>255</v>
       </c>
@@ -6289,7 +6285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>255</v>
       </c>
@@ -6309,7 +6305,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>255</v>
       </c>
@@ -6329,7 +6325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>255</v>
       </c>
@@ -6349,7 +6345,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>255</v>
       </c>
@@ -6369,7 +6365,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -6389,7 +6385,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>255</v>
       </c>
@@ -6409,7 +6405,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -6429,7 +6425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>255</v>
       </c>
@@ -6449,7 +6445,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>255</v>
       </c>
@@ -6469,7 +6465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>255</v>
       </c>
@@ -6489,7 +6485,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -6509,7 +6505,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>255</v>
       </c>
@@ -6529,7 +6525,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>255</v>
       </c>
@@ -6549,7 +6545,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>255</v>
       </c>
@@ -6569,7 +6565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>255</v>
       </c>
@@ -6589,7 +6585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>255</v>
       </c>
@@ -6609,7 +6605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>255</v>
       </c>
@@ -6629,7 +6625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>255</v>
       </c>
@@ -6649,7 +6645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>255</v>
       </c>
@@ -6669,7 +6665,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>255</v>
       </c>
@@ -6689,7 +6685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>255</v>
       </c>
@@ -6709,7 +6705,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>255</v>
       </c>
@@ -6729,7 +6725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>255</v>
       </c>
@@ -6749,7 +6745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>255</v>
       </c>
@@ -6769,7 +6765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>255</v>
       </c>
@@ -6789,7 +6785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>255</v>
       </c>
@@ -6809,7 +6805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>255</v>
       </c>
@@ -6829,7 +6825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>255</v>
       </c>
@@ -6849,7 +6845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>255</v>
       </c>
@@ -6869,7 +6865,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>255</v>
       </c>
@@ -6889,7 +6885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>139</v>
       </c>
@@ -6909,7 +6905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>199</v>
       </c>
@@ -6929,7 +6925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>199</v>
       </c>
@@ -6949,7 +6945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>199</v>
       </c>
@@ -6969,7 +6965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -6989,7 +6985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -7009,7 +7005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>6</v>
       </c>
@@ -7029,7 +7025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -7049,7 +7045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -7069,7 +7065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>83</v>
       </c>
@@ -7089,7 +7085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>83</v>
       </c>
@@ -7109,7 +7105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>83</v>
       </c>
@@ -7129,7 +7125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>83</v>
       </c>
@@ -7149,7 +7145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>255</v>
       </c>
@@ -7169,7 +7165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>255</v>
       </c>
@@ -7180,7 +7176,7 @@
         <v>321</v>
       </c>
       <c r="D291" t="s">
-        <v>322</v>
+        <v>17</v>
       </c>
       <c r="E291" t="s">
         <v>18</v>
@@ -7189,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -7197,7 +7193,7 @@
         <v>55</v>
       </c>
       <c r="C292" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D292" t="s">
         <v>62</v>
@@ -7209,7 +7205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -7217,7 +7213,7 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D293" t="s">
         <v>62</v>
@@ -7229,7 +7225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>139</v>
       </c>
@@ -7237,7 +7233,7 @@
         <v>7</v>
       </c>
       <c r="C294" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D294" t="s">
         <v>62</v>
@@ -7249,7 +7245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -7257,7 +7253,7 @@
         <v>55</v>
       </c>
       <c r="C295" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
@@ -7269,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>199</v>
       </c>
@@ -7277,7 +7273,7 @@
         <v>55</v>
       </c>
       <c r="C296" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D296" t="s">
         <v>128</v>
@@ -7289,7 +7285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>83</v>
       </c>
@@ -7297,7 +7293,7 @@
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -7309,7 +7305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>83</v>
       </c>
@@ -7317,7 +7313,7 @@
         <v>7</v>
       </c>
       <c r="C298" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D298" t="s">
         <v>156</v>
@@ -7329,7 +7325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>83</v>
       </c>
@@ -7337,7 +7333,7 @@
         <v>7</v>
       </c>
       <c r="C299" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D299" t="s">
         <v>156</v>
@@ -7349,7 +7345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -7357,7 +7353,7 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D300" t="s">
         <v>9</v>
@@ -7369,7 +7365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -7377,7 +7373,7 @@
         <v>55</v>
       </c>
       <c r="C301" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D301" t="s">
         <v>128</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD6C3B03-27D9-E047-98A8-710CE771726E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{8703EED0-7D8D-410D-8556-3D9CD54233D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="332">
   <si>
     <t>Manager</t>
   </si>
@@ -1010,9 +1011,6 @@
     <t>Donyell Malen</t>
   </si>
   <si>
-    <t>Freiberg</t>
-  </si>
-  <si>
     <t>Alabama Crimson Tide</t>
   </si>
   <si>
@@ -1029,6 +1027,9 @@
   </si>
   <si>
     <t>Tennessee Volunteers</t>
+  </si>
+  <si>
+    <t>Freiburg</t>
   </si>
 </sst>
 </file>
@@ -1363,9 +1364,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F301"/>
-  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1385,7 +1386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1405,7 +1406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1425,7 +1426,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1445,7 +1446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1465,7 +1466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1485,7 +1486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1505,7 +1506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1525,7 +1526,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1545,7 +1546,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1565,7 +1566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1585,7 +1586,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1605,7 +1606,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1625,7 +1626,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1645,7 +1646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1665,7 +1666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1685,7 +1686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1705,7 +1706,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1725,7 +1726,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1745,7 +1746,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1765,7 +1766,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1785,7 +1786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1805,7 +1806,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1825,7 +1826,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1845,7 +1846,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1865,7 +1866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1885,7 +1886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1905,7 +1906,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1925,7 +1926,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1945,7 +1946,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1965,7 +1966,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1985,7 +1986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2005,7 +2006,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -2025,7 +2026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2045,7 +2046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2065,7 +2066,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2085,7 +2086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>255</v>
       </c>
@@ -2105,7 +2106,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2125,7 +2126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2145,7 +2146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2165,7 +2166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2185,7 +2186,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2205,7 +2206,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2225,7 +2226,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2245,7 +2246,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2265,7 +2266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2285,7 +2286,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2305,7 +2306,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2325,7 +2326,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2345,7 +2346,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2365,7 +2366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2385,7 +2386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2405,7 +2406,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>83</v>
       </c>
@@ -2425,7 +2426,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -2445,7 +2446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2465,7 +2466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -2505,7 +2506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -2525,7 +2526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -2545,7 +2546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -2585,7 +2586,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -2625,7 +2626,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -2645,7 +2646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -2705,7 +2706,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2765,7 +2766,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2785,7 +2786,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2805,7 +2806,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2825,7 +2826,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2845,7 +2846,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2865,7 +2866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2885,7 +2886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2905,7 +2906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2925,7 +2926,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2945,7 +2946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2965,7 +2966,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2985,7 +2986,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -3005,7 +3006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -3025,7 +3026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -3045,7 +3046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -3065,7 +3066,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -3085,7 +3086,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3105,7 +3106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -3125,7 +3126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3165,7 +3166,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3185,7 +3186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3225,7 +3226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3245,7 +3246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3285,7 +3286,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3305,7 +3306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3365,7 +3366,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3385,7 +3386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3405,7 +3406,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3445,7 +3446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3465,7 +3466,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>139</v>
       </c>
@@ -3485,7 +3486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>139</v>
       </c>
@@ -3505,7 +3506,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>139</v>
       </c>
@@ -3525,7 +3526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>139</v>
       </c>
@@ -3545,7 +3546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>139</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3585,7 +3586,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -3605,7 +3606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -3625,7 +3626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>139</v>
       </c>
@@ -3645,7 +3646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>255</v>
       </c>
@@ -3665,7 +3666,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>139</v>
       </c>
@@ -3685,7 +3686,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>139</v>
       </c>
@@ -3705,7 +3706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>139</v>
       </c>
@@ -3725,7 +3726,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -3745,7 +3746,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>139</v>
       </c>
@@ -3765,7 +3766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>139</v>
       </c>
@@ -3785,7 +3786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>139</v>
       </c>
@@ -3805,7 +3806,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>139</v>
       </c>
@@ -3825,7 +3826,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>139</v>
       </c>
@@ -3845,7 +3846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -3865,7 +3866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>139</v>
       </c>
@@ -3885,7 +3886,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>139</v>
       </c>
@@ -3905,7 +3906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -3925,7 +3926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -3945,7 +3946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>139</v>
       </c>
@@ -3965,7 +3966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -3985,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -4005,7 +4006,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>139</v>
       </c>
@@ -4025,7 +4026,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -4065,7 +4066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -4085,7 +4086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -4105,7 +4106,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>139</v>
       </c>
@@ -4125,7 +4126,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -4145,7 +4146,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -4165,7 +4166,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -4185,7 +4186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>139</v>
       </c>
@@ -4205,7 +4206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>139</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>139</v>
       </c>
@@ -4245,7 +4246,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -4265,7 +4266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>139</v>
       </c>
@@ -4285,7 +4286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>139</v>
       </c>
@@ -4305,7 +4306,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>139</v>
       </c>
@@ -4325,7 +4326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>139</v>
       </c>
@@ -4345,7 +4346,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>139</v>
       </c>
@@ -4365,7 +4366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>139</v>
       </c>
@@ -4385,7 +4386,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>139</v>
       </c>
@@ -4405,7 +4406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>139</v>
       </c>
@@ -4425,7 +4426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>139</v>
       </c>
@@ -4445,7 +4446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>139</v>
       </c>
@@ -4465,7 +4466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>139</v>
       </c>
@@ -4485,7 +4486,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>139</v>
       </c>
@@ -4505,7 +4506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>139</v>
       </c>
@@ -4525,7 +4526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>139</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>139</v>
       </c>
@@ -4565,7 +4566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>139</v>
       </c>
@@ -4585,7 +4586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -4605,7 +4606,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>139</v>
       </c>
@@ -4625,7 +4626,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>139</v>
       </c>
@@ -4645,7 +4646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>199</v>
       </c>
@@ -4665,7 +4666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4685,7 +4686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>199</v>
       </c>
@@ -4705,7 +4706,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>199</v>
       </c>
@@ -4725,7 +4726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>199</v>
       </c>
@@ -4745,7 +4746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>199</v>
       </c>
@@ -4765,7 +4766,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>199</v>
       </c>
@@ -4785,7 +4786,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -4805,7 +4806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>199</v>
       </c>
@@ -4825,7 +4826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>199</v>
       </c>
@@ -4845,7 +4846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>199</v>
       </c>
@@ -4865,7 +4866,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>199</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>199</v>
       </c>
@@ -4905,7 +4906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>199</v>
       </c>
@@ -4925,7 +4926,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>199</v>
       </c>
@@ -4945,7 +4946,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>199</v>
       </c>
@@ -4965,7 +4966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>199</v>
       </c>
@@ -4985,7 +4986,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>199</v>
       </c>
@@ -5005,7 +5006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>199</v>
       </c>
@@ -5025,7 +5026,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>199</v>
       </c>
@@ -5045,7 +5046,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>199</v>
       </c>
@@ -5065,7 +5066,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>199</v>
       </c>
@@ -5085,7 +5086,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>199</v>
       </c>
@@ -5105,7 +5106,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>199</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -5145,7 +5146,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>199</v>
       </c>
@@ -5165,7 +5166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>199</v>
       </c>
@@ -5185,7 +5186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -5205,7 +5206,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>199</v>
       </c>
@@ -5225,7 +5226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -5245,7 +5246,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -5265,7 +5266,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -5285,7 +5286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -5305,7 +5306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>199</v>
       </c>
@@ -5325,7 +5326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>199</v>
       </c>
@@ -5345,7 +5346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -5365,7 +5366,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5385,7 +5386,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>199</v>
       </c>
@@ -5405,7 +5406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>199</v>
       </c>
@@ -5425,7 +5426,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>199</v>
       </c>
@@ -5445,7 +5446,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>199</v>
       </c>
@@ -5465,7 +5466,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>199</v>
       </c>
@@ -5485,7 +5486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>199</v>
       </c>
@@ -5505,7 +5506,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>199</v>
       </c>
@@ -5525,7 +5526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>199</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>199</v>
       </c>
@@ -5565,7 +5566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>199</v>
       </c>
@@ -5585,7 +5586,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>199</v>
       </c>
@@ -5605,7 +5606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>199</v>
       </c>
@@ -5625,7 +5626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -5645,7 +5646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>199</v>
       </c>
@@ -5665,7 +5666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>199</v>
       </c>
@@ -5685,7 +5686,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>199</v>
       </c>
@@ -5705,7 +5706,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>199</v>
       </c>
@@ -5725,7 +5726,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>199</v>
       </c>
@@ -5745,7 +5746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>199</v>
       </c>
@@ -5765,7 +5766,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>255</v>
       </c>
@@ -5785,7 +5786,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>255</v>
       </c>
@@ -5805,7 +5806,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>255</v>
       </c>
@@ -5825,7 +5826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>255</v>
       </c>
@@ -5845,7 +5846,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>255</v>
       </c>
@@ -5865,7 +5866,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>255</v>
       </c>
@@ -5885,7 +5886,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>255</v>
       </c>
@@ -5905,7 +5906,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>255</v>
       </c>
@@ -5925,7 +5926,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>255</v>
       </c>
@@ -5945,7 +5946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>255</v>
       </c>
@@ -5965,7 +5966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>255</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>255</v>
       </c>
@@ -6005,7 +6006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>255</v>
       </c>
@@ -6025,7 +6026,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>255</v>
       </c>
@@ -6045,7 +6046,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>255</v>
       </c>
@@ -6065,7 +6066,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -6085,7 +6086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>255</v>
       </c>
@@ -6105,7 +6106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>255</v>
       </c>
@@ -6125,7 +6126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>255</v>
       </c>
@@ -6145,7 +6146,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>255</v>
       </c>
@@ -6165,7 +6166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>255</v>
       </c>
@@ -6185,7 +6186,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>255</v>
       </c>
@@ -6205,7 +6206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>255</v>
       </c>
@@ -6225,7 +6226,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>255</v>
       </c>
@@ -6245,7 +6246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>255</v>
       </c>
@@ -6265,7 +6266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>255</v>
       </c>
@@ -6285,7 +6286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>255</v>
       </c>
@@ -6305,7 +6306,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>255</v>
       </c>
@@ -6325,7 +6326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>255</v>
       </c>
@@ -6345,7 +6346,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>255</v>
       </c>
@@ -6365,7 +6366,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -6385,7 +6386,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>255</v>
       </c>
@@ -6405,7 +6406,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>255</v>
       </c>
@@ -6445,7 +6446,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>255</v>
       </c>
@@ -6465,7 +6466,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>255</v>
       </c>
@@ -6485,7 +6486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -6505,7 +6506,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>255</v>
       </c>
@@ -6525,7 +6526,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>255</v>
       </c>
@@ -6545,7 +6546,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>255</v>
       </c>
@@ -6565,7 +6566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>255</v>
       </c>
@@ -6585,7 +6586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>255</v>
       </c>
@@ -6605,7 +6606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>255</v>
       </c>
@@ -6625,7 +6626,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>255</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>255</v>
       </c>
@@ -6665,7 +6666,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>255</v>
       </c>
@@ -6685,7 +6686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>255</v>
       </c>
@@ -6705,7 +6706,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>255</v>
       </c>
@@ -6725,7 +6726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>255</v>
       </c>
@@ -6745,7 +6746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>255</v>
       </c>
@@ -6765,7 +6766,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>255</v>
       </c>
@@ -6785,7 +6786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>255</v>
       </c>
@@ -6805,7 +6806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>255</v>
       </c>
@@ -6825,7 +6826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>255</v>
       </c>
@@ -6845,7 +6846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>255</v>
       </c>
@@ -6865,7 +6866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>255</v>
       </c>
@@ -6885,7 +6886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>139</v>
       </c>
@@ -6905,7 +6906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>199</v>
       </c>
@@ -6925,7 +6926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>199</v>
       </c>
@@ -6945,7 +6946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>199</v>
       </c>
@@ -6965,7 +6966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -6985,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -7005,7 +7006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>6</v>
       </c>
@@ -7025,7 +7026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -7045,7 +7046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -7065,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>83</v>
       </c>
@@ -7085,7 +7086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>83</v>
       </c>
@@ -7105,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>83</v>
       </c>
@@ -7125,7 +7126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>83</v>
       </c>
@@ -7145,7 +7146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>255</v>
       </c>
@@ -7165,7 +7166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>255</v>
       </c>
@@ -7185,7 +7186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -7205,7 +7206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -7225,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>139</v>
       </c>
@@ -7245,7 +7246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -7253,7 +7254,7 @@
         <v>55</v>
       </c>
       <c r="C295" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
@@ -7265,7 +7266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>199</v>
       </c>
@@ -7273,7 +7274,7 @@
         <v>55</v>
       </c>
       <c r="C296" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D296" t="s">
         <v>128</v>
@@ -7285,7 +7286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>83</v>
       </c>
@@ -7293,7 +7294,7 @@
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -7305,7 +7306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>83</v>
       </c>
@@ -7313,7 +7314,7 @@
         <v>7</v>
       </c>
       <c r="C298" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D298" t="s">
         <v>156</v>
@@ -7325,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>83</v>
       </c>
@@ -7333,7 +7334,7 @@
         <v>7</v>
       </c>
       <c r="C299" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D299" t="s">
         <v>156</v>
@@ -7345,7 +7346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -7353,7 +7354,7 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D300" t="s">
         <v>9</v>
@@ -7365,7 +7366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -7373,7 +7374,7 @@
         <v>55</v>
       </c>
       <c r="C301" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D301" t="s">
         <v>128</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{8703EED0-7D8D-410D-8556-3D9CD54233D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{10C21DB2-9E56-4425-B41B-CF145DBE088A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7357,7 +7357,7 @@
         <v>329</v>
       </c>
       <c r="D300" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E300" t="s">
         <v>10</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{10C21DB2-9E56-4425-B41B-CF145DBE088A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{8CFC64B3-3871-46F6-BFFB-54C73AB2F2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -969,9 +969,6 @@
     <t>Miami Hurricanes</t>
   </si>
   <si>
-    <t>Scotty Barnes</t>
-  </si>
-  <si>
     <t>Tommy Fleetwood</t>
   </si>
   <si>
@@ -1030,6 +1027,9 @@
   </si>
   <si>
     <t>Freiburg</t>
+  </si>
+  <si>
+    <t>Scottie Barnes</t>
   </si>
 </sst>
 </file>
@@ -6934,7 +6934,7 @@
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -6954,7 +6954,7 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D280" t="s">
         <v>46</v>
@@ -6974,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D281" t="s">
         <v>37</v>
@@ -7014,7 +7014,7 @@
         <v>55</v>
       </c>
       <c r="C283" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D283" t="s">
         <v>133</v>
@@ -7054,7 +7054,7 @@
         <v>55</v>
       </c>
       <c r="C285" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D285" t="s">
         <v>12</v>
@@ -7074,7 +7074,7 @@
         <v>7</v>
       </c>
       <c r="C286" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D286" t="s">
         <v>46</v>
@@ -7094,7 +7094,7 @@
         <v>7</v>
       </c>
       <c r="C287" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D287" t="s">
         <v>32</v>
@@ -7114,7 +7114,7 @@
         <v>7</v>
       </c>
       <c r="C288" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D288" t="s">
         <v>32</v>
@@ -7134,7 +7134,7 @@
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D289" t="s">
         <v>89</v>
@@ -7154,7 +7154,7 @@
         <v>55</v>
       </c>
       <c r="C290" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D290" t="s">
         <v>89</v>
@@ -7174,7 +7174,7 @@
         <v>7</v>
       </c>
       <c r="C291" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D291" t="s">
         <v>17</v>
@@ -7194,7 +7194,7 @@
         <v>55</v>
       </c>
       <c r="C292" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D292" t="s">
         <v>62</v>
@@ -7214,7 +7214,7 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D293" t="s">
         <v>62</v>
@@ -7234,7 +7234,7 @@
         <v>7</v>
       </c>
       <c r="C294" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D294" t="s">
         <v>62</v>
@@ -7254,7 +7254,7 @@
         <v>55</v>
       </c>
       <c r="C295" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
@@ -7274,7 +7274,7 @@
         <v>55</v>
       </c>
       <c r="C296" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D296" t="s">
         <v>128</v>
@@ -7294,7 +7294,7 @@
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -7314,7 +7314,7 @@
         <v>7</v>
       </c>
       <c r="C298" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D298" t="s">
         <v>156</v>
@@ -7334,7 +7334,7 @@
         <v>7</v>
       </c>
       <c r="C299" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D299" t="s">
         <v>156</v>
@@ -7354,7 +7354,7 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D300" t="s">
         <v>15</v>
@@ -7374,7 +7374,7 @@
         <v>55</v>
       </c>
       <c r="C301" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D301" t="s">
         <v>128</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{8CFC64B3-3871-46F6-BFFB-54C73AB2F2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{1655C6A7-1091-44BE-9641-09AC3CDD690A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,9 +417,6 @@
     <t>Auburn Tigers</t>
   </si>
   <si>
-    <t>Texas Tech Lady Raiders</t>
-  </si>
-  <si>
     <t>NCAA Softball</t>
   </si>
   <si>
@@ -1023,13 +1020,16 @@
     <t>Anders Dreyer</t>
   </si>
   <si>
-    <t>Tennessee Volunteers</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Scottie Barnes</t>
+  </si>
+  <si>
+    <t>Tennessee Lady Volunteers</t>
+  </si>
+  <si>
+    <t>Texas Tech Red Raiders</t>
   </si>
 </sst>
 </file>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B37" t="s">
         <v>55</v>
@@ -3254,13 +3254,13 @@
         <v>55</v>
       </c>
       <c r="C95" t="s">
+        <v>331</v>
+      </c>
+      <c r="D95" t="s">
         <v>127</v>
       </c>
-      <c r="D95" t="s">
-        <v>128</v>
-      </c>
       <c r="E95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F95">
         <v>50</v>
@@ -3274,7 +3274,7 @@
         <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D96" t="s">
         <v>75</v>
@@ -3294,7 +3294,7 @@
         <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
         <v>75</v>
@@ -3314,7 +3314,7 @@
         <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D98" t="s">
         <v>78</v>
@@ -3334,7 +3334,7 @@
         <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D99" t="s">
         <v>78</v>
@@ -3357,10 +3357,10 @@
         <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F100">
         <v>15</v>
@@ -3374,13 +3374,13 @@
         <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F101">
         <v>100</v>
@@ -3394,7 +3394,7 @@
         <v>55</v>
       </c>
       <c r="C102" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D102" t="s">
         <v>37</v>
@@ -3414,7 +3414,7 @@
         <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D103" t="s">
         <v>37</v>
@@ -3434,7 +3434,7 @@
         <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D104" t="s">
         <v>41</v>
@@ -3454,7 +3454,7 @@
         <v>55</v>
       </c>
       <c r="C105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
@@ -3468,13 +3468,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
+        <v>138</v>
+      </c>
+      <c r="B106" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" t="s">
         <v>139</v>
-      </c>
-      <c r="B106" t="s">
-        <v>7</v>
-      </c>
-      <c r="C106" t="s">
-        <v>140</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
@@ -3488,13 +3488,13 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D107" t="s">
         <v>12</v>
@@ -3508,13 +3508,13 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D108" t="s">
         <v>12</v>
@@ -3528,13 +3528,13 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B109" t="s">
         <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
@@ -3548,13 +3548,13 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
@@ -3568,13 +3568,13 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
         <v>17</v>
@@ -3588,13 +3588,13 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B112" t="s">
         <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D112" t="s">
         <v>89</v>
@@ -3608,13 +3608,13 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>89</v>
@@ -3628,13 +3628,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B114" t="s">
         <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D114" t="s">
         <v>17</v>
@@ -3648,13 +3648,13 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D115" t="s">
         <v>17</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -3688,13 +3688,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B117" t="s">
         <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D117" t="s">
         <v>23</v>
@@ -3708,13 +3708,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B118" t="s">
         <v>7</v>
       </c>
       <c r="C118" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D118" t="s">
         <v>23</v>
@@ -3728,13 +3728,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D119" t="s">
         <v>23</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B120" t="s">
         <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D120" t="s">
         <v>28</v>
@@ -3768,16 +3768,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
+        <v>154</v>
+      </c>
+      <c r="D121" t="s">
         <v>155</v>
-      </c>
-      <c r="D121" t="s">
-        <v>156</v>
       </c>
       <c r="E121" t="s">
         <v>29</v>
@@ -3788,13 +3788,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -3808,13 +3808,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B123" t="s">
         <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -3828,13 +3828,13 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -3848,13 +3848,13 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -3868,13 +3868,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B126" t="s">
         <v>7</v>
       </c>
       <c r="C126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D126" t="s">
         <v>37</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B127" t="s">
         <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D127" t="s">
         <v>37</v>
@@ -3908,13 +3908,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D128" t="s">
         <v>37</v>
@@ -3928,13 +3928,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B129" t="s">
         <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
         <v>37</v>
@@ -3948,13 +3948,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B130" t="s">
         <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D130" t="s">
         <v>41</v>
@@ -3968,13 +3968,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D131" t="s">
         <v>41</v>
@@ -3988,13 +3988,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B132" t="s">
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D132" t="s">
         <v>41</v>
@@ -4008,13 +4008,13 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B133" t="s">
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D133" t="s">
         <v>41</v>
@@ -4028,13 +4028,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D134" t="s">
         <v>46</v>
@@ -4048,13 +4048,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B135" t="s">
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D135" t="s">
         <v>46</v>
@@ -4068,13 +4068,13 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B136" t="s">
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D136" t="s">
         <v>46</v>
@@ -4088,13 +4088,13 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D137" t="s">
         <v>50</v>
@@ -4108,13 +4108,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D138" t="s">
         <v>53</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D139" t="s">
         <v>53</v>
@@ -4148,13 +4148,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B140" t="s">
         <v>55</v>
       </c>
       <c r="C140" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D140" t="s">
         <v>12</v>
@@ -4168,13 +4168,13 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" t="s">
         <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D141" t="s">
         <v>9</v>
@@ -4188,13 +4188,13 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B142" t="s">
         <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D142" t="s">
         <v>15</v>
@@ -4208,13 +4208,13 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B143" t="s">
         <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D143" t="s">
         <v>17</v>
@@ -4228,13 +4228,13 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B144" t="s">
         <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D144" t="s">
         <v>62</v>
@@ -4248,13 +4248,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B145" t="s">
         <v>55</v>
       </c>
       <c r="C145" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D145" t="s">
         <v>62</v>
@@ -4268,13 +4268,13 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B146" t="s">
         <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D146" t="s">
         <v>62</v>
@@ -4288,13 +4288,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B147" t="s">
         <v>55</v>
       </c>
       <c r="C147" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D147" t="s">
         <v>67</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B148" t="s">
         <v>55</v>
@@ -4328,13 +4328,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B149" t="s">
         <v>55</v>
       </c>
       <c r="C149" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D149" t="s">
         <v>23</v>
@@ -4348,13 +4348,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B150" t="s">
         <v>55</v>
       </c>
       <c r="C150" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D150" t="s">
         <v>23</v>
@@ -4368,13 +4368,13 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B151" t="s">
         <v>55</v>
       </c>
       <c r="C151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D151" t="s">
         <v>32</v>
@@ -4388,13 +4388,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B152" t="s">
         <v>55</v>
       </c>
       <c r="C152" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D152" t="s">
         <v>32</v>
@@ -4408,13 +4408,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B153" t="s">
         <v>55</v>
       </c>
       <c r="C153" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D153" t="s">
         <v>73</v>
@@ -4428,19 +4428,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B154" t="s">
         <v>55</v>
       </c>
       <c r="C154" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D154" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E154" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F154">
         <v>11</v>
@@ -4448,13 +4448,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B155" t="s">
         <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D155" t="s">
         <v>75</v>
@@ -4468,13 +4468,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B156" t="s">
         <v>55</v>
       </c>
       <c r="C156" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4488,13 +4488,13 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B157" t="s">
         <v>55</v>
       </c>
       <c r="C157" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D157" t="s">
         <v>78</v>
@@ -4508,13 +4508,13 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B158" t="s">
         <v>55</v>
       </c>
       <c r="C158" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D158" t="s">
         <v>78</v>
@@ -4528,19 +4528,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B159" t="s">
         <v>55</v>
       </c>
       <c r="C159" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D159" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E159" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F159">
         <v>30</v>
@@ -4548,19 +4548,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B160" t="s">
         <v>55</v>
       </c>
       <c r="C160" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D160" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E160" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F160">
         <v>11</v>
@@ -4568,13 +4568,13 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B161" t="s">
         <v>55</v>
       </c>
       <c r="C161" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D161" t="s">
         <v>37</v>
@@ -4588,13 +4588,13 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B162" t="s">
         <v>55</v>
       </c>
       <c r="C162" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D162" t="s">
         <v>37</v>
@@ -4608,13 +4608,13 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B163" t="s">
         <v>55</v>
       </c>
       <c r="C163" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D163" t="s">
         <v>41</v>
@@ -4628,13 +4628,13 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B164" t="s">
         <v>55</v>
       </c>
       <c r="C164" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D164" t="s">
         <v>41</v>
@@ -4648,13 +4648,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
+        <v>198</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
         <v>199</v>
-      </c>
-      <c r="B165" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" t="s">
-        <v>200</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -4668,13 +4668,13 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B166" t="s">
         <v>7</v>
       </c>
       <c r="C166" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D166" t="s">
         <v>15</v>
@@ -4688,13 +4688,13 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D167" t="s">
         <v>15</v>
@@ -4708,13 +4708,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B168" t="s">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D168" t="s">
         <v>15</v>
@@ -4728,13 +4728,13 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B169" t="s">
         <v>7</v>
       </c>
       <c r="C169" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D169" t="s">
         <v>15</v>
@@ -4748,13 +4748,13 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D170" t="s">
         <v>17</v>
@@ -4768,13 +4768,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B171" t="s">
         <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D171" t="s">
         <v>17</v>
@@ -4788,13 +4788,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B172" t="s">
         <v>7</v>
       </c>
       <c r="C172" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D172" t="s">
         <v>17</v>
@@ -4808,13 +4808,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D173" t="s">
         <v>62</v>
@@ -4828,13 +4828,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B174" t="s">
         <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D174" t="s">
         <v>89</v>
@@ -4848,13 +4848,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B175" t="s">
         <v>7</v>
       </c>
       <c r="C175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D175" t="s">
         <v>23</v>
@@ -4868,13 +4868,13 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
       </c>
       <c r="C176" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D176" t="s">
         <v>23</v>
@@ -4888,13 +4888,13 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B177" t="s">
         <v>7</v>
       </c>
       <c r="C177" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D177" t="s">
         <v>23</v>
@@ -4908,13 +4908,13 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B178" t="s">
         <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D178" t="s">
         <v>23</v>
@@ -4928,13 +4928,13 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -4948,13 +4948,13 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -4968,13 +4968,13 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D181" t="s">
         <v>32</v>
@@ -4988,13 +4988,13 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D182" t="s">
         <v>32</v>
@@ -5008,13 +5008,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B183" t="s">
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D183" t="s">
         <v>32</v>
@@ -5028,13 +5028,13 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B184" t="s">
         <v>7</v>
       </c>
       <c r="C184" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D184" t="s">
         <v>37</v>
@@ -5048,13 +5048,13 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B185" t="s">
         <v>7</v>
       </c>
       <c r="C185" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D185" t="s">
         <v>37</v>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B186" t="s">
         <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D186" t="s">
         <v>37</v>
@@ -5088,13 +5088,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B187" t="s">
         <v>7</v>
       </c>
       <c r="C187" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D187" t="s">
         <v>37</v>
@@ -5108,13 +5108,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B188" t="s">
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D188" t="s">
         <v>41</v>
@@ -5128,13 +5128,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B189" t="s">
         <v>7</v>
       </c>
       <c r="C189" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D189" t="s">
         <v>41</v>
@@ -5148,13 +5148,13 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B190" t="s">
         <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D190" t="s">
         <v>41</v>
@@ -5168,13 +5168,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B191" t="s">
         <v>7</v>
       </c>
       <c r="C191" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D191" t="s">
         <v>41</v>
@@ -5188,13 +5188,13 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B192" t="s">
         <v>7</v>
       </c>
       <c r="C192" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D192" t="s">
         <v>46</v>
@@ -5208,13 +5208,13 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B193" t="s">
         <v>7</v>
       </c>
       <c r="C193" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D193" t="s">
         <v>46</v>
@@ -5228,13 +5228,13 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B194" t="s">
         <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D194" t="s">
         <v>50</v>
@@ -5248,13 +5248,13 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B195" t="s">
         <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D195" t="s">
         <v>53</v>
@@ -5268,13 +5268,13 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B196" t="s">
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D196" t="s">
         <v>50</v>
@@ -5288,13 +5288,13 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B197" t="s">
         <v>55</v>
       </c>
       <c r="C197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D197" t="s">
         <v>12</v>
@@ -5308,13 +5308,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B198" t="s">
         <v>55</v>
       </c>
       <c r="C198" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D198" t="s">
         <v>12</v>
@@ -5328,13 +5328,13 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B199" t="s">
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -5348,13 +5348,13 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B200" t="s">
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -5368,13 +5368,13 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B201" t="s">
         <v>55</v>
       </c>
       <c r="C201" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D201" t="s">
         <v>17</v>
@@ -5388,13 +5388,13 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B202" t="s">
         <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D202" t="s">
         <v>89</v>
@@ -5408,13 +5408,13 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B203" t="s">
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D203" t="s">
         <v>17</v>
@@ -5428,13 +5428,13 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B204" t="s">
         <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D204" t="s">
         <v>17</v>
@@ -5448,7 +5448,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B205" t="s">
         <v>55</v>
@@ -5468,13 +5468,13 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B206" t="s">
         <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D206" t="s">
         <v>67</v>
@@ -5488,13 +5488,13 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B207" t="s">
         <v>55</v>
       </c>
       <c r="C207" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
@@ -5508,13 +5508,13 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B208" t="s">
         <v>55</v>
       </c>
       <c r="C208" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -5528,13 +5528,13 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B209" t="s">
         <v>55</v>
       </c>
       <c r="C209" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -5548,13 +5548,13 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B210" t="s">
         <v>55</v>
       </c>
       <c r="C210" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -5568,13 +5568,13 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B211" t="s">
         <v>55</v>
       </c>
       <c r="C211" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D211" t="s">
         <v>73</v>
@@ -5588,13 +5588,13 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B212" t="s">
         <v>55</v>
       </c>
       <c r="C212" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D212" t="s">
         <v>75</v>
@@ -5608,13 +5608,13 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B213" t="s">
         <v>55</v>
       </c>
       <c r="C213" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D213" t="s">
         <v>78</v>
@@ -5628,13 +5628,13 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B214" t="s">
         <v>55</v>
       </c>
       <c r="C214" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D214" t="s">
         <v>78</v>
@@ -5648,19 +5648,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B215" t="s">
         <v>55</v>
       </c>
       <c r="C215" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D215" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E215" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F215">
         <v>100</v>
@@ -5668,19 +5668,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B216" t="s">
         <v>55</v>
       </c>
       <c r="C216" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D216" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E216" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F216">
         <v>75</v>
@@ -5688,13 +5688,13 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B217" t="s">
         <v>55</v>
       </c>
       <c r="C217" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D217" t="s">
         <v>37</v>
@@ -5708,13 +5708,13 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B218" t="s">
         <v>55</v>
       </c>
       <c r="C218" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D218" t="s">
         <v>37</v>
@@ -5728,13 +5728,13 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B219" t="s">
         <v>55</v>
       </c>
       <c r="C219" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D219" t="s">
         <v>41</v>
@@ -5748,13 +5748,13 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B220" t="s">
         <v>55</v>
       </c>
       <c r="C220" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D220" t="s">
         <v>41</v>
@@ -5768,13 +5768,13 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
+        <v>254</v>
+      </c>
+      <c r="B221" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" t="s">
         <v>255</v>
-      </c>
-      <c r="B221" t="s">
-        <v>7</v>
-      </c>
-      <c r="C221" t="s">
-        <v>256</v>
       </c>
       <c r="D221" t="s">
         <v>12</v>
@@ -5788,13 +5788,13 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B222" t="s">
         <v>7</v>
       </c>
       <c r="C222" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
@@ -5808,13 +5808,13 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B223" t="s">
         <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D223" t="s">
         <v>9</v>
@@ -5828,13 +5828,13 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B224" t="s">
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -5848,13 +5848,13 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B225" t="s">
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D225" t="s">
         <v>15</v>
@@ -5868,13 +5868,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B226" t="s">
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D226" t="s">
         <v>17</v>
@@ -5888,13 +5888,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B227" t="s">
         <v>7</v>
       </c>
       <c r="C227" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>89</v>
@@ -5908,13 +5908,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
       </c>
       <c r="C228" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D228" t="s">
         <v>89</v>
@@ -5928,13 +5928,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D229" t="s">
         <v>23</v>
@@ -5948,13 +5948,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
       </c>
       <c r="C230" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D230" t="s">
         <v>23</v>
@@ -5968,13 +5968,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B231" t="s">
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D231" t="s">
         <v>23</v>
@@ -5988,13 +5988,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B232" t="s">
         <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D232" t="s">
         <v>23</v>
@@ -6008,16 +6008,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B233" t="s">
         <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D233" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E233" t="s">
         <v>29</v>
@@ -6028,13 +6028,13 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B234" t="s">
         <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D234" t="s">
         <v>29</v>
@@ -6048,13 +6048,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B235" t="s">
         <v>7</v>
       </c>
       <c r="C235" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -6068,13 +6068,13 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B236" t="s">
         <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -6088,13 +6088,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B237" t="s">
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -6108,13 +6108,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B238" t="s">
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -6128,13 +6128,13 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B239" t="s">
         <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D239" t="s">
         <v>37</v>
@@ -6148,13 +6148,13 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B240" t="s">
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D240" t="s">
         <v>37</v>
@@ -6168,13 +6168,13 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B241" t="s">
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D241" t="s">
         <v>37</v>
@@ -6188,13 +6188,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B242" t="s">
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D242" t="s">
         <v>37</v>
@@ -6208,13 +6208,13 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B243" t="s">
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D243" t="s">
         <v>41</v>
@@ -6228,13 +6228,13 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B244" t="s">
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D244" t="s">
         <v>41</v>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B245" t="s">
         <v>7</v>
       </c>
       <c r="C245" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D245" t="s">
         <v>41</v>
@@ -6268,13 +6268,13 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B246" t="s">
         <v>7</v>
       </c>
       <c r="C246" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D246" t="s">
         <v>41</v>
@@ -6288,13 +6288,13 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B247" t="s">
         <v>7</v>
       </c>
       <c r="C247" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D247" t="s">
         <v>46</v>
@@ -6308,13 +6308,13 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B248" t="s">
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D248" t="s">
         <v>46</v>
@@ -6328,13 +6328,13 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B249" t="s">
         <v>7</v>
       </c>
       <c r="C249" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D249" t="s">
         <v>46</v>
@@ -6348,13 +6348,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B250" t="s">
         <v>7</v>
       </c>
       <c r="C250" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D250" t="s">
         <v>50</v>
@@ -6368,13 +6368,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B251" t="s">
         <v>7</v>
       </c>
       <c r="C251" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D251" t="s">
         <v>53</v>
@@ -6388,13 +6388,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B252" t="s">
         <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D252" t="s">
         <v>50</v>
@@ -6408,13 +6408,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B253" t="s">
         <v>55</v>
       </c>
       <c r="C253" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D253" t="s">
         <v>15</v>
@@ -6428,13 +6428,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B254" t="s">
         <v>55</v>
       </c>
       <c r="C254" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D254" t="s">
         <v>15</v>
@@ -6448,13 +6448,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B255" t="s">
         <v>55</v>
       </c>
       <c r="C255" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D255" t="s">
         <v>9</v>
@@ -6468,13 +6468,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B256" t="s">
         <v>55</v>
       </c>
       <c r="C256" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D256" t="s">
         <v>9</v>
@@ -6488,13 +6488,13 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B257" t="s">
         <v>55</v>
       </c>
       <c r="C257" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D257" t="s">
         <v>17</v>
@@ -6508,13 +6508,13 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B258" t="s">
         <v>55</v>
       </c>
       <c r="C258" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D258" t="s">
         <v>89</v>
@@ -6528,7 +6528,7 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B259" t="s">
         <v>55</v>
@@ -6548,13 +6548,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B260" t="s">
         <v>55</v>
       </c>
       <c r="C260" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D260" t="s">
         <v>67</v>
@@ -6568,13 +6568,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B261" t="s">
         <v>55</v>
       </c>
       <c r="C261" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D261" t="s">
         <v>23</v>
@@ -6588,13 +6588,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B262" t="s">
         <v>55</v>
       </c>
       <c r="C262" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D262" t="s">
         <v>23</v>
@@ -6608,13 +6608,13 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B263" t="s">
         <v>55</v>
       </c>
       <c r="C263" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D263" t="s">
         <v>32</v>
@@ -6628,13 +6628,13 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B264" t="s">
         <v>55</v>
       </c>
       <c r="C264" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D264" t="s">
         <v>32</v>
@@ -6648,13 +6648,13 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B265" t="s">
         <v>55</v>
       </c>
       <c r="C265" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D265" t="s">
         <v>73</v>
@@ -6668,19 +6668,19 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B266" t="s">
         <v>55</v>
       </c>
       <c r="C266" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D266" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E266" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F266">
         <v>5</v>
@@ -6688,13 +6688,13 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B267" t="s">
         <v>55</v>
       </c>
       <c r="C267" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D267" t="s">
         <v>75</v>
@@ -6708,13 +6708,13 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B268" t="s">
         <v>55</v>
       </c>
       <c r="C268" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D268" t="s">
         <v>75</v>
@@ -6728,13 +6728,13 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B269" t="s">
         <v>55</v>
       </c>
       <c r="C269" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D269" t="s">
         <v>78</v>
@@ -6748,13 +6748,13 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B270" t="s">
         <v>55</v>
       </c>
       <c r="C270" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D270" t="s">
         <v>78</v>
@@ -6768,19 +6768,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B271" t="s">
         <v>55</v>
       </c>
       <c r="C271" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D271" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E271" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F271">
         <v>4</v>
@@ -6788,19 +6788,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B272" t="s">
         <v>55</v>
       </c>
       <c r="C272" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D272" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E272" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -6808,13 +6808,13 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B273" t="s">
         <v>55</v>
       </c>
       <c r="C273" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D273" t="s">
         <v>37</v>
@@ -6828,13 +6828,13 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B274" t="s">
         <v>55</v>
       </c>
       <c r="C274" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D274" t="s">
         <v>37</v>
@@ -6848,13 +6848,13 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B275" t="s">
         <v>55</v>
       </c>
       <c r="C275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D275" t="s">
         <v>41</v>
@@ -6868,13 +6868,13 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B276" t="s">
         <v>55</v>
       </c>
       <c r="C276" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D276" t="s">
         <v>41</v>
@@ -6888,13 +6888,13 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B277" t="s">
         <v>55</v>
       </c>
       <c r="C277" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D277" t="s">
         <v>12</v>
@@ -6908,13 +6908,13 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B278" t="s">
         <v>55</v>
       </c>
       <c r="C278" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D278" t="s">
         <v>75</v>
@@ -6928,13 +6928,13 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B279" t="s">
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -6948,13 +6948,13 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B280" t="s">
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D280" t="s">
         <v>46</v>
@@ -6974,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D281" t="s">
         <v>37</v>
@@ -6994,7 +6994,7 @@
         <v>55</v>
       </c>
       <c r="C282" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D282" t="s">
         <v>78</v>
@@ -7014,13 +7014,13 @@
         <v>55</v>
       </c>
       <c r="C283" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D283" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E283" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F283">
         <v>0</v>
@@ -7034,13 +7034,13 @@
         <v>55</v>
       </c>
       <c r="C284" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D284" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E284" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -7054,7 +7054,7 @@
         <v>55</v>
       </c>
       <c r="C285" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D285" t="s">
         <v>12</v>
@@ -7074,7 +7074,7 @@
         <v>7</v>
       </c>
       <c r="C286" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D286" t="s">
         <v>46</v>
@@ -7094,7 +7094,7 @@
         <v>7</v>
       </c>
       <c r="C287" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D287" t="s">
         <v>32</v>
@@ -7114,7 +7114,7 @@
         <v>7</v>
       </c>
       <c r="C288" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D288" t="s">
         <v>32</v>
@@ -7134,7 +7134,7 @@
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D289" t="s">
         <v>89</v>
@@ -7148,13 +7148,13 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B290" t="s">
         <v>55</v>
       </c>
       <c r="C290" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D290" t="s">
         <v>89</v>
@@ -7168,13 +7168,13 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B291" t="s">
         <v>7</v>
       </c>
       <c r="C291" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D291" t="s">
         <v>17</v>
@@ -7194,7 +7194,7 @@
         <v>55</v>
       </c>
       <c r="C292" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D292" t="s">
         <v>62</v>
@@ -7214,7 +7214,7 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D293" t="s">
         <v>62</v>
@@ -7228,13 +7228,13 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B294" t="s">
         <v>7</v>
       </c>
       <c r="C294" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D294" t="s">
         <v>62</v>
@@ -7254,7 +7254,7 @@
         <v>55</v>
       </c>
       <c r="C295" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
@@ -7268,19 +7268,19 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B296" t="s">
         <v>55</v>
       </c>
       <c r="C296" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D296" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E296" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F296">
         <v>0</v>
@@ -7294,7 +7294,7 @@
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -7314,10 +7314,10 @@
         <v>7</v>
       </c>
       <c r="C298" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D298" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E298" t="s">
         <v>29</v>
@@ -7334,10 +7334,10 @@
         <v>7</v>
       </c>
       <c r="C299" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D299" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E299" t="s">
         <v>29</v>
@@ -7354,7 +7354,7 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D300" t="s">
         <v>15</v>
@@ -7374,13 +7374,13 @@
         <v>55</v>
       </c>
       <c r="C301" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D301" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E301" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F301">
         <v>0</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{1655C6A7-1091-44BE-9641-09AC3CDD690A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{47265246-8916-4D1E-9170-712142C2DE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1020,9 +1020,6 @@
     <t>Anders Dreyer</t>
   </si>
   <si>
-    <t>Freiburg</t>
-  </si>
-  <si>
     <t>Scottie Barnes</t>
   </si>
   <si>
@@ -1030,6 +1027,9 @@
   </si>
   <si>
     <t>Texas Tech Red Raiders</t>
+  </si>
+  <si>
+    <t>SC Freiburg</t>
   </si>
 </sst>
 </file>
@@ -3254,7 +3254,7 @@
         <v>55</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D95" t="s">
         <v>127</v>
@@ -6934,7 +6934,7 @@
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -7254,7 +7254,7 @@
         <v>55</v>
       </c>
       <c r="C295" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
@@ -7374,7 +7374,7 @@
         <v>55</v>
       </c>
       <c r="C301" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D301" t="s">
         <v>127</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{47265246-8916-4D1E-9170-712142C2DE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{629A3109-DBA0-4781-8032-901187BEA1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="388">
   <si>
     <t>Manager</t>
   </si>
@@ -1030,6 +1030,174 @@
   </si>
   <si>
     <t>SC Freiburg</t>
+  </si>
+  <si>
+    <t>New York Mets</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Dallas Mavericks</t>
+  </si>
+  <si>
+    <t>Atlanta Falcons</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>New York City FC</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Houston Astros</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
+    <t>Los Angeles Chargers</t>
+  </si>
+  <si>
+    <t>Indianapolis Colts</t>
+  </si>
+  <si>
+    <t>Boston Bruins</t>
+  </si>
+  <si>
+    <t>Minnesota Wild</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Detroit Pistons</t>
+  </si>
+  <si>
+    <t>Atlanta Hawks</t>
+  </si>
+  <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
+    <t>Arizona Cardinals</t>
+  </si>
+  <si>
+    <t>Minnesota Vikings</t>
+  </si>
+  <si>
+    <t>Las Vegas Raiders</t>
+  </si>
+  <si>
+    <t>Toronto Maple Leafs</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>AC Milan</t>
+  </si>
+  <si>
+    <t>New York Yankees</t>
+  </si>
+  <si>
+    <t>Great Britain</t>
+  </si>
+  <si>
+    <t>Miami Heat</t>
+  </si>
+  <si>
+    <t>Kansas City Chiefs</t>
+  </si>
+  <si>
+    <t>Winnepeg Jets</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Atletico Madrid</t>
+  </si>
+  <si>
+    <t>Alaves</t>
+  </si>
+  <si>
+    <t>Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Minnesota Timberwolves</t>
+  </si>
+  <si>
+    <t>Los Angeles Clippers</t>
+  </si>
+  <si>
+    <t>Northern Ireland</t>
+  </si>
+  <si>
+    <t>Belarus</t>
+  </si>
+  <si>
+    <t>Toronto Raptors</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>San Diego FC</t>
   </si>
 </sst>
 </file>
@@ -1363,10 +1531,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F301"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1385,8 +1553,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1405,8 +1576,11 @@
       <c r="F2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1425,8 +1599,11 @@
       <c r="F3">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1445,8 +1622,11 @@
       <c r="F4">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1465,8 +1645,11 @@
       <c r="F5">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1485,8 +1668,11 @@
       <c r="F6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1505,8 +1691,11 @@
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1525,8 +1714,11 @@
       <c r="F8">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1545,8 +1737,11 @@
       <c r="F9">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1565,8 +1760,11 @@
       <c r="F10">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1585,8 +1783,11 @@
       <c r="F11">
         <v>96</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1605,8 +1806,11 @@
       <c r="F12">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1625,8 +1829,11 @@
       <c r="F13">
         <v>76</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1645,8 +1852,11 @@
       <c r="F14">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1665,8 +1875,11 @@
       <c r="F15">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1685,8 +1898,11 @@
       <c r="F16">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1705,8 +1921,11 @@
       <c r="F17">
         <v>101</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1725,8 +1944,11 @@
       <c r="F18">
         <v>101</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1745,8 +1967,11 @@
       <c r="F19">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1765,8 +1990,11 @@
       <c r="F20">
         <v>72</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1785,8 +2013,11 @@
       <c r="F21">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1805,8 +2036,11 @@
       <c r="F22">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1825,8 +2059,11 @@
       <c r="F23">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1845,8 +2082,11 @@
       <c r="F24">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1865,8 +2105,11 @@
       <c r="F25">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1885,8 +2128,11 @@
       <c r="F26">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1905,8 +2151,11 @@
       <c r="F27">
         <v>71</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1925,8 +2174,11 @@
       <c r="F28">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1945,8 +2197,11 @@
       <c r="F29">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1965,8 +2220,11 @@
       <c r="F30">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1985,8 +2243,11 @@
       <c r="F31">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2005,8 +2266,11 @@
       <c r="F32">
         <v>76</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -2025,8 +2289,11 @@
       <c r="F33">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2045,8 +2312,11 @@
       <c r="F34">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2065,8 +2335,11 @@
       <c r="F35">
         <v>200</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2085,8 +2358,11 @@
       <c r="F36">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>254</v>
       </c>
@@ -2105,8 +2381,11 @@
       <c r="F37">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2125,8 +2404,11 @@
       <c r="F38">
         <v>25</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2145,8 +2427,11 @@
       <c r="F39">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2165,8 +2450,11 @@
       <c r="F40">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2185,8 +2473,11 @@
       <c r="F41">
         <v>200</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2205,8 +2496,11 @@
       <c r="F42">
         <v>51</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G42" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2225,8 +2519,11 @@
       <c r="F43">
         <v>61</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2245,8 +2542,11 @@
       <c r="F44">
         <v>36</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2265,8 +2565,11 @@
       <c r="F45">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2285,8 +2588,11 @@
       <c r="F46">
         <v>200</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G46" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2305,8 +2611,11 @@
       <c r="F47">
         <v>22</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2325,8 +2634,11 @@
       <c r="F48">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2345,8 +2657,11 @@
       <c r="F49">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2365,8 +2680,11 @@
       <c r="F50">
         <v>24</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2385,8 +2703,11 @@
       <c r="F51">
         <v>25</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G51" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2405,8 +2726,11 @@
       <c r="F52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>83</v>
       </c>
@@ -2425,8 +2749,11 @@
       <c r="F53">
         <v>50</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G53" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -2445,8 +2772,11 @@
       <c r="F54">
         <v>30</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G54" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2465,8 +2795,11 @@
       <c r="F55">
         <v>15</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G55" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -2485,8 +2818,11 @@
       <c r="F56">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -2505,8 +2841,11 @@
       <c r="F57">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G57" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -2525,8 +2864,11 @@
       <c r="F58">
         <v>50</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G58" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -2545,8 +2887,11 @@
       <c r="F59">
         <v>25</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G59" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -2565,8 +2910,11 @@
       <c r="F60">
         <v>25</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -2585,8 +2933,11 @@
       <c r="F61">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G61" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -2605,8 +2956,11 @@
       <c r="F62">
         <v>100</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G62" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -2625,8 +2979,11 @@
       <c r="F63">
         <v>50</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G63" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -2645,8 +3002,11 @@
       <c r="F64">
         <v>50</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G64" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -2665,8 +3025,11 @@
       <c r="F65">
         <v>150</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G65" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -2685,8 +3048,11 @@
       <c r="F66">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G66" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -2705,8 +3071,11 @@
       <c r="F67">
         <v>20</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G67" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -2725,8 +3094,11 @@
       <c r="F68">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G68" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -2745,8 +3117,11 @@
       <c r="F69">
         <v>25</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G69" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2765,8 +3140,11 @@
       <c r="F70">
         <v>25</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G70" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2785,8 +3163,11 @@
       <c r="F71">
         <v>20</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G71" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2805,8 +3186,11 @@
       <c r="F72">
         <v>50</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G72" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2825,8 +3209,11 @@
       <c r="F73">
         <v>25</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2845,8 +3232,11 @@
       <c r="F74">
         <v>25</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G74" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2865,8 +3255,11 @@
       <c r="F75">
         <v>100</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G75" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2885,8 +3278,11 @@
       <c r="F76">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G76" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2905,8 +3301,11 @@
       <c r="F77">
         <v>15</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G77" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2925,8 +3324,11 @@
       <c r="F78">
         <v>50</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G78" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2945,8 +3347,11 @@
       <c r="F79">
         <v>5</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G79" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2965,8 +3370,11 @@
       <c r="F80">
         <v>75</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2985,8 +3393,11 @@
       <c r="F81">
         <v>45</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G81" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -3005,8 +3416,11 @@
       <c r="F82">
         <v>25</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G82" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -3025,8 +3439,11 @@
       <c r="F83">
         <v>15</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G83" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -3045,8 +3462,11 @@
       <c r="F84">
         <v>50</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G84" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -3065,8 +3485,11 @@
       <c r="F85">
         <v>20</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -3085,8 +3508,11 @@
       <c r="F86">
         <v>20</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G86" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3105,8 +3531,11 @@
       <c r="F87">
         <v>10</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G87" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -3125,8 +3554,11 @@
       <c r="F88">
         <v>50</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G88" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -3145,8 +3577,11 @@
       <c r="F89">
         <v>50</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G89" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3165,8 +3600,11 @@
       <c r="F90">
         <v>70</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G90" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3185,8 +3623,11 @@
       <c r="F91">
         <v>30</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G91" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3205,8 +3646,11 @@
       <c r="F92">
         <v>60</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G92" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3225,8 +3669,11 @@
       <c r="F93">
         <v>10</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G93" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3245,8 +3692,11 @@
       <c r="F94">
         <v>100</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G94" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3265,8 +3715,11 @@
       <c r="F95">
         <v>50</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G95" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3285,8 +3738,11 @@
       <c r="F96">
         <v>90</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G96" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3305,8 +3761,11 @@
       <c r="F97">
         <v>5</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G97" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3325,8 +3784,11 @@
       <c r="F98">
         <v>25</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G98" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3345,8 +3807,11 @@
       <c r="F99">
         <v>200</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3365,8 +3830,11 @@
       <c r="F100">
         <v>15</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G100" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3385,8 +3853,11 @@
       <c r="F101">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G101" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3405,8 +3876,11 @@
       <c r="F102">
         <v>125</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G102" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3425,8 +3899,11 @@
       <c r="F103">
         <v>75</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G103" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3445,8 +3922,11 @@
       <c r="F104">
         <v>50</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G104" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3465,8 +3945,11 @@
       <c r="F105">
         <v>50</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G105" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>138</v>
       </c>
@@ -3485,8 +3968,11 @@
       <c r="F106">
         <v>30</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G106" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>138</v>
       </c>
@@ -3505,8 +3991,11 @@
       <c r="F107">
         <v>20</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G107" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>138</v>
       </c>
@@ -3525,8 +4014,11 @@
       <c r="F108">
         <v>12</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G108" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>138</v>
       </c>
@@ -3545,8 +4037,11 @@
       <c r="F109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G109" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -3565,8 +4060,11 @@
       <c r="F110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G110" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -3585,8 +4083,11 @@
       <c r="F111">
         <v>90</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G111" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>138</v>
       </c>
@@ -3605,8 +4106,11 @@
       <c r="F112">
         <v>25</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G112" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>138</v>
       </c>
@@ -3625,8 +4129,11 @@
       <c r="F113">
         <v>17</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G113" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>138</v>
       </c>
@@ -3645,8 +4152,11 @@
       <c r="F114">
         <v>8</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G114" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>254</v>
       </c>
@@ -3665,8 +4175,11 @@
       <c r="F115">
         <v>38</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G115" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>138</v>
       </c>
@@ -3685,8 +4198,11 @@
       <c r="F116">
         <v>200</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G116" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>138</v>
       </c>
@@ -3705,8 +4221,11 @@
       <c r="F117">
         <v>10</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G117" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>138</v>
       </c>
@@ -3725,8 +4244,11 @@
       <c r="F118">
         <v>20</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G118" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>138</v>
       </c>
@@ -3745,8 +4267,11 @@
       <c r="F119">
         <v>15</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G119" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>138</v>
       </c>
@@ -3765,8 +4290,11 @@
       <c r="F120">
         <v>5</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G120" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>138</v>
       </c>
@@ -3785,8 +4313,11 @@
       <c r="F121">
         <v>5</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G121" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>138</v>
       </c>
@@ -3805,8 +4336,11 @@
       <c r="F122">
         <v>90</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G122" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>138</v>
       </c>
@@ -3825,8 +4359,11 @@
       <c r="F123">
         <v>25</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G123" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>138</v>
       </c>
@@ -3845,8 +4382,11 @@
       <c r="F124">
         <v>10</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G124" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>138</v>
       </c>
@@ -3865,8 +4405,11 @@
       <c r="F125">
         <v>4</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G125" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>138</v>
       </c>
@@ -3885,8 +4428,11 @@
       <c r="F126">
         <v>80</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G126" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>138</v>
       </c>
@@ -3905,8 +4451,11 @@
       <c r="F127">
         <v>15</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G127" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -3925,8 +4474,11 @@
       <c r="F128">
         <v>11</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G128" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>138</v>
       </c>
@@ -3945,8 +4497,11 @@
       <c r="F129">
         <v>11</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G129" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>138</v>
       </c>
@@ -3965,8 +4520,11 @@
       <c r="F130">
         <v>2</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G130" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>138</v>
       </c>
@@ -3985,8 +4543,11 @@
       <c r="F131">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G131" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>138</v>
       </c>
@@ -4005,8 +4566,11 @@
       <c r="F132">
         <v>170</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G132" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>138</v>
       </c>
@@ -4025,8 +4589,11 @@
       <c r="F133">
         <v>169</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G133" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>138</v>
       </c>
@@ -4045,8 +4612,11 @@
       <c r="F134">
         <v>30</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G134" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>138</v>
       </c>
@@ -4065,8 +4635,11 @@
       <c r="F135">
         <v>15</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G135" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>138</v>
       </c>
@@ -4085,8 +4658,11 @@
       <c r="F136">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G136" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>138</v>
       </c>
@@ -4105,8 +4681,11 @@
       <c r="F137">
         <v>90</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G137" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>138</v>
       </c>
@@ -4125,8 +4704,11 @@
       <c r="F138">
         <v>141</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G138" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -4145,8 +4727,11 @@
       <c r="F139">
         <v>12</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G139" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>138</v>
       </c>
@@ -4165,8 +4750,11 @@
       <c r="F140">
         <v>20</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G140" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>138</v>
       </c>
@@ -4185,8 +4773,11 @@
       <c r="F141">
         <v>24</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G141" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>138</v>
       </c>
@@ -4205,8 +4796,11 @@
       <c r="F142">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G142" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>138</v>
       </c>
@@ -4225,8 +4819,11 @@
       <c r="F143">
         <v>20</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G143" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>138</v>
       </c>
@@ -4245,8 +4842,11 @@
       <c r="F144">
         <v>150</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G144" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>138</v>
       </c>
@@ -4265,8 +4865,11 @@
       <c r="F145">
         <v>9</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G145" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>138</v>
       </c>
@@ -4285,8 +4888,11 @@
       <c r="F146">
         <v>8</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G146" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>138</v>
       </c>
@@ -4305,8 +4911,11 @@
       <c r="F147">
         <v>37</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G147" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>138</v>
       </c>
@@ -4325,8 +4934,11 @@
       <c r="F148">
         <v>5</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G148" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>138</v>
       </c>
@@ -4345,8 +4957,11 @@
       <c r="F149">
         <v>175</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G149" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>138</v>
       </c>
@@ -4365,8 +4980,11 @@
       <c r="F150">
         <v>5</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G150" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>138</v>
       </c>
@@ -4385,8 +5003,11 @@
       <c r="F151">
         <v>60</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G151" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>138</v>
       </c>
@@ -4405,8 +5026,11 @@
       <c r="F152">
         <v>5</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G152" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>138</v>
       </c>
@@ -4425,8 +5049,11 @@
       <c r="F153">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G153" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>138</v>
       </c>
@@ -4445,8 +5072,11 @@
       <c r="F154">
         <v>11</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G154" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>138</v>
       </c>
@@ -4465,8 +5095,11 @@
       <c r="F155">
         <v>2</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G155" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>138</v>
       </c>
@@ -4485,8 +5118,11 @@
       <c r="F156">
         <v>170</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G156" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>138</v>
       </c>
@@ -4505,8 +5141,11 @@
       <c r="F157">
         <v>5</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G157" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>138</v>
       </c>
@@ -4525,8 +5164,11 @@
       <c r="F158">
         <v>2</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G158" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>138</v>
       </c>
@@ -4545,8 +5187,11 @@
       <c r="F159">
         <v>30</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G159" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>138</v>
       </c>
@@ -4565,8 +5210,11 @@
       <c r="F160">
         <v>11</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G160" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>138</v>
       </c>
@@ -4585,8 +5233,11 @@
       <c r="F161">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G161" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>138</v>
       </c>
@@ -4605,8 +5256,11 @@
       <c r="F162">
         <v>141</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G162" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>138</v>
       </c>
@@ -4625,8 +5279,11 @@
       <c r="F163">
         <v>40</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G163" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>138</v>
       </c>
@@ -4645,8 +5302,11 @@
       <c r="F164">
         <v>5</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G164" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>198</v>
       </c>
@@ -4665,8 +5325,11 @@
       <c r="F165">
         <v>100</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G165" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>198</v>
       </c>
@@ -4685,8 +5348,11 @@
       <c r="F166">
         <v>100</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G166" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>198</v>
       </c>
@@ -4705,8 +5371,11 @@
       <c r="F167">
         <v>75</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G167" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>198</v>
       </c>
@@ -4725,8 +5394,11 @@
       <c r="F168">
         <v>30</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G168" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>198</v>
       </c>
@@ -4745,8 +5417,11 @@
       <c r="F169">
         <v>30</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G169" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>198</v>
       </c>
@@ -4765,8 +5440,11 @@
       <c r="F170">
         <v>70</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G170" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>198</v>
       </c>
@@ -4785,8 +5463,11 @@
       <c r="F171">
         <v>50</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G171" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>198</v>
       </c>
@@ -4805,8 +5486,11 @@
       <c r="F172">
         <v>2</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G172" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>198</v>
       </c>
@@ -4825,8 +5509,11 @@
       <c r="F173">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G173" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>198</v>
       </c>
@@ -4845,8 +5532,11 @@
       <c r="F174">
         <v>50</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G174" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>198</v>
       </c>
@@ -4865,8 +5555,11 @@
       <c r="F175">
         <v>80</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G175" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>198</v>
       </c>
@@ -4885,8 +5578,11 @@
       <c r="F176">
         <v>80</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G176" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>198</v>
       </c>
@@ -4905,8 +5601,11 @@
       <c r="F177">
         <v>40</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G177" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>198</v>
       </c>
@@ -4925,8 +5624,11 @@
       <c r="F178">
         <v>25</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G178" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>198</v>
       </c>
@@ -4945,8 +5647,11 @@
       <c r="F179">
         <v>30</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G179" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>198</v>
       </c>
@@ -4965,8 +5670,11 @@
       <c r="F180">
         <v>25</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G180" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>198</v>
       </c>
@@ -4985,8 +5693,11 @@
       <c r="F181">
         <v>35</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G181" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>198</v>
       </c>
@@ -5005,8 +5716,11 @@
       <c r="F182">
         <v>30</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G182" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>198</v>
       </c>
@@ -5025,8 +5739,11 @@
       <c r="F183">
         <v>40</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G183" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>198</v>
       </c>
@@ -5045,8 +5762,11 @@
       <c r="F184">
         <v>80</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G184" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>198</v>
       </c>
@@ -5065,8 +5785,11 @@
       <c r="F185">
         <v>70</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G185" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>198</v>
       </c>
@@ -5085,8 +5808,11 @@
       <c r="F186">
         <v>30</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G186" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>198</v>
       </c>
@@ -5105,8 +5831,11 @@
       <c r="F187">
         <v>25</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G187" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>198</v>
       </c>
@@ -5125,8 +5854,11 @@
       <c r="F188">
         <v>35</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G188" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>198</v>
       </c>
@@ -5145,8 +5877,11 @@
       <c r="F189">
         <v>30</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G189" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>198</v>
       </c>
@@ -5165,8 +5900,11 @@
       <c r="F190">
         <v>30</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G190" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>198</v>
       </c>
@@ -5185,8 +5923,11 @@
       <c r="F191">
         <v>10</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G191" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>198</v>
       </c>
@@ -5205,8 +5946,11 @@
       <c r="F192">
         <v>30</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G192" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>198</v>
       </c>
@@ -5225,8 +5969,11 @@
       <c r="F193">
         <v>10</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G193" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>198</v>
       </c>
@@ -5245,8 +5992,11 @@
       <c r="F194">
         <v>75</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G194" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>198</v>
       </c>
@@ -5265,8 +6015,11 @@
       <c r="F195">
         <v>25</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G195" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -5285,8 +6038,11 @@
       <c r="F196">
         <v>15</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G196" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>198</v>
       </c>
@@ -5305,8 +6061,11 @@
       <c r="F197">
         <v>20</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G197" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>198</v>
       </c>
@@ -5325,8 +6084,11 @@
       <c r="F198">
         <v>20</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G198" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>198</v>
       </c>
@@ -5345,8 +6107,11 @@
       <c r="F199">
         <v>100</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G199" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -5365,8 +6130,11 @@
       <c r="F200">
         <v>75</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G200" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>198</v>
       </c>
@@ -5385,8 +6153,11 @@
       <c r="F201">
         <v>300</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G201" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>198</v>
       </c>
@@ -5405,8 +6176,11 @@
       <c r="F202">
         <v>100</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G202" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>198</v>
       </c>
@@ -5425,8 +6199,11 @@
       <c r="F203">
         <v>75</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G203" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>198</v>
       </c>
@@ -5445,8 +6222,11 @@
       <c r="F204">
         <v>55</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G204" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>198</v>
       </c>
@@ -5465,8 +6245,11 @@
       <c r="F205">
         <v>80</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G205" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>198</v>
       </c>
@@ -5485,8 +6268,11 @@
       <c r="F206">
         <v>20</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G206" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>198</v>
       </c>
@@ -5505,8 +6291,11 @@
       <c r="F207">
         <v>30</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G207" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>198</v>
       </c>
@@ -5525,8 +6314,11 @@
       <c r="F208">
         <v>25</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G208" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>198</v>
       </c>
@@ -5545,8 +6337,11 @@
       <c r="F209">
         <v>25</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G209" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>198</v>
       </c>
@@ -5565,8 +6360,11 @@
       <c r="F210">
         <v>50</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G210" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>198</v>
       </c>
@@ -5585,8 +6383,11 @@
       <c r="F211">
         <v>40</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G211" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>198</v>
       </c>
@@ -5605,8 +6406,11 @@
       <c r="F212">
         <v>10</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G212" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>198</v>
       </c>
@@ -5625,8 +6429,11 @@
       <c r="F213">
         <v>10</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G213" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>198</v>
       </c>
@@ -5645,8 +6452,11 @@
       <c r="F214">
         <v>10</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G214" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>198</v>
       </c>
@@ -5665,8 +6475,11 @@
       <c r="F215">
         <v>100</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G215" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>198</v>
       </c>
@@ -5685,8 +6498,11 @@
       <c r="F216">
         <v>75</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G216" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>198</v>
       </c>
@@ -5705,8 +6521,11 @@
       <c r="F217">
         <v>60</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G217" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>198</v>
       </c>
@@ -5725,8 +6544,11 @@
       <c r="F218">
         <v>40</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G218" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>198</v>
       </c>
@@ -5745,8 +6567,11 @@
       <c r="F219">
         <v>40</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G219" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>198</v>
       </c>
@@ -5765,8 +6590,11 @@
       <c r="F220">
         <v>40</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G220" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>254</v>
       </c>
@@ -5785,8 +6613,11 @@
       <c r="F221">
         <v>33</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G221" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>254</v>
       </c>
@@ -5805,8 +6636,11 @@
       <c r="F222">
         <v>27</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G222" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>254</v>
       </c>
@@ -5825,8 +6659,11 @@
       <c r="F223">
         <v>13</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G223" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>254</v>
       </c>
@@ -5845,8 +6682,11 @@
       <c r="F224">
         <v>7</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G224" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>254</v>
       </c>
@@ -5865,8 +6705,11 @@
       <c r="F225">
         <v>175</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G225" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>254</v>
       </c>
@@ -5885,8 +6728,11 @@
       <c r="F226">
         <v>42</v>
       </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G226" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>254</v>
       </c>
@@ -5905,8 +6751,11 @@
       <c r="F227">
         <v>33</v>
       </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G227" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>254</v>
       </c>
@@ -5925,8 +6774,11 @@
       <c r="F228">
         <v>125</v>
       </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G228" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>254</v>
       </c>
@@ -5945,8 +6797,11 @@
       <c r="F229">
         <v>16</v>
       </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G229" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>254</v>
       </c>
@@ -5965,8 +6820,11 @@
       <c r="F230">
         <v>3</v>
       </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G230" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>254</v>
       </c>
@@ -5985,8 +6843,11 @@
       <c r="F231">
         <v>2</v>
       </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G231" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>254</v>
       </c>
@@ -6005,8 +6866,11 @@
       <c r="F232">
         <v>2</v>
       </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G232" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>254</v>
       </c>
@@ -6025,8 +6889,11 @@
       <c r="F233">
         <v>18</v>
       </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G233" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>254</v>
       </c>
@@ -6045,8 +6912,11 @@
       <c r="F234">
         <v>175</v>
       </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G234" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>254</v>
       </c>
@@ -6065,8 +6935,11 @@
       <c r="F235">
         <v>99</v>
       </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G235" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>254</v>
       </c>
@@ -6085,8 +6958,11 @@
       <c r="F236">
         <v>11</v>
       </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G236" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>254</v>
       </c>
@@ -6105,8 +6981,11 @@
       <c r="F237">
         <v>4</v>
       </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G237" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>254</v>
       </c>
@@ -6125,8 +7004,11 @@
       <c r="F238">
         <v>2</v>
       </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G238" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>254</v>
       </c>
@@ -6145,8 +7027,11 @@
       <c r="F239">
         <v>69</v>
       </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G239" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>254</v>
       </c>
@@ -6165,8 +7050,11 @@
       <c r="F240">
         <v>8</v>
       </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G240" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>254</v>
       </c>
@@ -6185,8 +7073,11 @@
       <c r="F241">
         <v>68</v>
       </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G241" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>254</v>
       </c>
@@ -6205,8 +7096,11 @@
       <c r="F242">
         <v>11</v>
       </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G242" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>254</v>
       </c>
@@ -6225,8 +7119,11 @@
       <c r="F243">
         <v>55</v>
       </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G243" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>254</v>
       </c>
@@ -6245,8 +7142,11 @@
       <c r="F244">
         <v>11</v>
       </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G244" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>254</v>
       </c>
@@ -6265,8 +7165,11 @@
       <c r="F245">
         <v>4</v>
       </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G245" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>254</v>
       </c>
@@ -6285,8 +7188,11 @@
       <c r="F246">
         <v>1</v>
       </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G246" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>254</v>
       </c>
@@ -6305,8 +7211,11 @@
       <c r="F247">
         <v>87</v>
       </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G247" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>254</v>
       </c>
@@ -6325,8 +7234,11 @@
       <c r="F248">
         <v>2</v>
       </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G248" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>254</v>
       </c>
@@ -6345,8 +7257,11 @@
       <c r="F249">
         <v>175</v>
       </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G249" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>254</v>
       </c>
@@ -6365,8 +7280,11 @@
       <c r="F250">
         <v>139</v>
       </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G250" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>254</v>
       </c>
@@ -6385,8 +7303,11 @@
       <c r="F251">
         <v>58</v>
       </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G251" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>254</v>
       </c>
@@ -6405,8 +7326,11 @@
       <c r="F252">
         <v>44</v>
       </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G252" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>254</v>
       </c>
@@ -6425,8 +7349,11 @@
       <c r="F253">
         <v>57</v>
       </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G253" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>254</v>
       </c>
@@ -6445,8 +7372,11 @@
       <c r="F254">
         <v>49</v>
       </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G254" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>254</v>
       </c>
@@ -6465,8 +7395,11 @@
       <c r="F255">
         <v>27</v>
       </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G255" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>254</v>
       </c>
@@ -6485,8 +7418,11 @@
       <c r="F256">
         <v>16</v>
       </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G256" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>254</v>
       </c>
@@ -6505,8 +7441,11 @@
       <c r="F257">
         <v>51</v>
       </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G257" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>254</v>
       </c>
@@ -6525,8 +7464,11 @@
       <c r="F258">
         <v>92</v>
       </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G258" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>254</v>
       </c>
@@ -6545,8 +7487,11 @@
       <c r="F259">
         <v>98</v>
       </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G259" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>254</v>
       </c>
@@ -6565,8 +7510,11 @@
       <c r="F260">
         <v>3</v>
       </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G260" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>254</v>
       </c>
@@ -6585,8 +7533,11 @@
       <c r="F261">
         <v>8</v>
       </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G261" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>254</v>
       </c>
@@ -6605,8 +7556,11 @@
       <c r="F262">
         <v>3</v>
       </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G262" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>254</v>
       </c>
@@ -6625,8 +7579,11 @@
       <c r="F263">
         <v>13</v>
       </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G263" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>254</v>
       </c>
@@ -6645,8 +7602,11 @@
       <c r="F264">
         <v>4</v>
       </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G264" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>254</v>
       </c>
@@ -6665,8 +7625,11 @@
       <c r="F265">
         <v>23</v>
       </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G265" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>254</v>
       </c>
@@ -6685,8 +7648,11 @@
       <c r="F266">
         <v>5</v>
       </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G266" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>254</v>
       </c>
@@ -6705,8 +7671,11 @@
       <c r="F267">
         <v>47</v>
       </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G267" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>254</v>
       </c>
@@ -6725,8 +7694,11 @@
       <c r="F268">
         <v>6</v>
       </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G268" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>254</v>
       </c>
@@ -6745,8 +7717,11 @@
       <c r="F269">
         <v>18</v>
       </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G269" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>254</v>
       </c>
@@ -6765,8 +7740,11 @@
       <c r="F270">
         <v>17</v>
       </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G270" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>254</v>
       </c>
@@ -6785,8 +7763,11 @@
       <c r="F271">
         <v>4</v>
       </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G271" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>254</v>
       </c>
@@ -6805,8 +7786,11 @@
       <c r="F272">
         <v>1</v>
       </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G272" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>254</v>
       </c>
@@ -6825,8 +7809,11 @@
       <c r="F273">
         <v>1</v>
       </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G273" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>254</v>
       </c>
@@ -6845,8 +7832,11 @@
       <c r="F274">
         <v>1</v>
       </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G274" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>254</v>
       </c>
@@ -6865,8 +7855,11 @@
       <c r="F275">
         <v>6</v>
       </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G275" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>254</v>
       </c>
@@ -6885,8 +7878,11 @@
       <c r="F276">
         <v>5</v>
       </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G276" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>138</v>
       </c>
@@ -6905,8 +7901,11 @@
       <c r="F277">
         <v>0</v>
       </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G277" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>198</v>
       </c>
@@ -6925,8 +7924,11 @@
       <c r="F278">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G278" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>198</v>
       </c>
@@ -6945,8 +7947,11 @@
       <c r="F279">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G279" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>198</v>
       </c>
@@ -6965,8 +7970,11 @@
       <c r="F280">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G280" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -6985,8 +7993,11 @@
       <c r="F281">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G281" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -7005,8 +8016,11 @@
       <c r="F282">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G282" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>6</v>
       </c>
@@ -7025,8 +8039,11 @@
       <c r="F283">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G283" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -7045,8 +8062,11 @@
       <c r="F284">
         <v>0</v>
       </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G284" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -7065,8 +8085,11 @@
       <c r="F285">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G285" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>83</v>
       </c>
@@ -7085,8 +8108,11 @@
       <c r="F286">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G286" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>83</v>
       </c>
@@ -7105,8 +8131,11 @@
       <c r="F287">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G287" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>83</v>
       </c>
@@ -7125,8 +8154,11 @@
       <c r="F288">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G288" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>83</v>
       </c>
@@ -7145,8 +8177,11 @@
       <c r="F289">
         <v>0</v>
       </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G289" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>254</v>
       </c>
@@ -7165,8 +8200,11 @@
       <c r="F290">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G290" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>254</v>
       </c>
@@ -7185,8 +8223,11 @@
       <c r="F291">
         <v>0</v>
       </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G291" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -7205,8 +8246,11 @@
       <c r="F292">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G292" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -7225,8 +8269,11 @@
       <c r="F293">
         <v>0</v>
       </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G293" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>138</v>
       </c>
@@ -7245,8 +8292,11 @@
       <c r="F294">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G294" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -7265,8 +8315,11 @@
       <c r="F295">
         <v>0</v>
       </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G295" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>198</v>
       </c>
@@ -7285,8 +8338,11 @@
       <c r="F296">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G296" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>83</v>
       </c>
@@ -7305,8 +8361,11 @@
       <c r="F297">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G297" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>83</v>
       </c>
@@ -7325,8 +8384,11 @@
       <c r="F298">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G298" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>83</v>
       </c>
@@ -7345,8 +8407,11 @@
       <c r="F299">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G299" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -7365,8 +8430,11 @@
       <c r="F300">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G300" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -7384,6 +8452,9 @@
       </c>
       <c r="F301">
         <v>0</v>
+      </c>
+      <c r="G301" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{629A3109-DBA0-4781-8032-901187BEA1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{A41D0ED1-49CF-41C8-84C9-7F2930438C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1152,9 +1152,6 @@
     <t>Kansas City Chiefs</t>
   </si>
   <si>
-    <t>Winnepeg Jets</t>
-  </si>
-  <si>
     <t>Greece</t>
   </si>
   <si>
@@ -1198,6 +1195,9 @@
   </si>
   <si>
     <t>San Diego FC</t>
+  </si>
+  <si>
+    <t>Winnipeg Jets</t>
   </si>
 </sst>
 </file>
@@ -5924,7 +5924,7 @@
         <v>10</v>
       </c>
       <c r="G191" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
@@ -6039,7 +6039,7 @@
         <v>15</v>
       </c>
       <c r="G196" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
@@ -6683,7 +6683,7 @@
         <v>7</v>
       </c>
       <c r="G224" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -6706,7 +6706,7 @@
         <v>175</v>
       </c>
       <c r="G225" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
@@ -6729,7 +6729,7 @@
         <v>42</v>
       </c>
       <c r="G226" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
@@ -6752,7 +6752,7 @@
         <v>33</v>
       </c>
       <c r="G227" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -6775,7 +6775,7 @@
         <v>125</v>
       </c>
       <c r="G228" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
@@ -6798,7 +6798,7 @@
         <v>16</v>
       </c>
       <c r="G229" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
@@ -6844,7 +6844,7 @@
         <v>2</v>
       </c>
       <c r="G231" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
@@ -6959,7 +6959,7 @@
         <v>11</v>
       </c>
       <c r="G236" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -6982,7 +6982,7 @@
         <v>4</v>
       </c>
       <c r="G237" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7212,7 +7212,7 @@
         <v>87</v>
       </c>
       <c r="G247" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
@@ -7304,7 +7304,7 @@
         <v>58</v>
       </c>
       <c r="G251" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
@@ -8109,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
@@ -8431,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{A41D0ED1-49CF-41C8-84C9-7F2930438C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{04996141-9810-4DFC-B393-8EC5F7C79486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1176,9 +1176,6 @@
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
-    <t>Los Angeles Clippers</t>
-  </si>
-  <si>
     <t>Northern Ireland</t>
   </si>
   <si>
@@ -1198,6 +1195,9 @@
   </si>
   <si>
     <t>Winnipeg Jets</t>
+  </si>
+  <si>
+    <t>LA Clippers</t>
   </si>
 </sst>
 </file>
@@ -5924,7 +5924,7 @@
         <v>10</v>
       </c>
       <c r="G191" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
@@ -6982,7 +6982,7 @@
         <v>4</v>
       </c>
       <c r="G237" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7212,7 +7212,7 @@
         <v>87</v>
       </c>
       <c r="G247" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
@@ -7304,7 +7304,7 @@
         <v>58</v>
       </c>
       <c r="G251" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
@@ -8109,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
@@ -8431,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
